--- a/inputs/en/template_input.xlsx
+++ b/inputs/en/template_input.xlsx
@@ -5,12 +5,12 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nick.scott\Desktop\GitHub\Nutrition\inputs\en\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\Nutrition\inputs\en\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76E07AE-141C-49E6-A413-2F6746FD50E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2A8914-34FE-4044-A414-03DC7E849494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15630" yWindow="-18120" windowWidth="29040" windowHeight="17520" tabRatio="961" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline year population inputs" sheetId="1" r:id="rId1"/>
@@ -3020,12 +3020,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{7A6BFA19-43CD-4FE5-89AA-3029846AB614}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{610733DC-C5A0-477F-8779-3D5E978ECE77}">
       <text>
         <r>
           <rPr>
@@ -3045,12 +3044,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N10" authorId="0" shapeId="0" xr:uid="{6B098F08-0C63-4983-81B6-D16CB8D74153}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N10" authorId="0" shapeId="0" xr:uid="{EE403504-DD2F-44B3-9A8E-DF158FE53E17}">
       <text>
         <r>
           <rPr>
@@ -3070,12 +3068,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O10" authorId="0" shapeId="0" xr:uid="{D723FF2D-4BEA-4F1C-BDB9-B0864B0FCE6F}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O10" authorId="0" shapeId="0" xr:uid="{CE2D5E10-5A45-4DC2-A353-819F7441B3A1}">
       <text>
         <r>
           <rPr>
@@ -3095,8 +3092,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -4140,7 +4136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{61BA3D80-7CEA-4E7F-88D4-EAD51A7E0CB1}">
+    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{6F2BF4C1-4CC5-4E05-B9F0-97D1912529C9}">
       <text>
         <r>
           <rPr>
@@ -4160,8 +4156,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -4185,12 +4180,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N33" authorId="0" shapeId="0" xr:uid="{081BEA4A-411A-4050-A5D1-BDE0D98EA7CC}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N33" authorId="0" shapeId="0" xr:uid="{C18686B2-EEAE-4B6B-86D9-E5A53F241AD3}">
       <text>
         <r>
           <rPr>
@@ -4210,12 +4204,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O33" authorId="0" shapeId="0" xr:uid="{EA0F0E8B-EC09-4E8C-A118-919A7C3B64C8}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O33" authorId="0" shapeId="0" xr:uid="{99B9577F-5A08-419B-9D4B-DBCE0A829734}">
       <text>
         <r>
           <rPr>
@@ -4235,8 +4228,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -5322,12 +5314,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{E75C05A1-9808-4ABF-8AEC-100352B492F9}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{11F73239-626A-4DF9-9812-819843340AA8}">
       <text>
         <r>
           <rPr>
@@ -5347,12 +5338,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{9FC1941B-B36F-4D2E-A978-64D95D336CFB}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{10B00C10-8E38-486A-8681-EAB2DB52644B}">
       <text>
         <r>
           <rPr>
@@ -5372,12 +5362,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{16580F86-9664-481C-8346-573E716AA139}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{9166A6F0-10A1-4B50-8BAA-C182F31FA14A}">
       <text>
         <r>
           <rPr>
@@ -5397,8 +5386,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -7762,7 +7750,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -8940,7 +8928,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -10118,7 +10106,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -12635,7 +12623,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{EF97059A-88CD-43C7-9247-D17B80D2BA53}">
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{050856FA-F87E-4097-B0CD-476075F203E6}">
       <text>
         <r>
           <rPr>
@@ -12660,7 +12648,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{B43DB696-18D2-4F4E-954F-3B1B8C221179}">
+    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{138FF691-DDF2-4B53-A0A8-D4C96E1CA2D6}">
       <text>
         <r>
           <rPr>
@@ -17596,14 +17584,14 @@
     <tabColor rgb="FF007600"/>
   </sheetPr>
   <dimension ref="A1:E63"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="38.6640625" style="11" customWidth="1"/>
-    <col min="3" max="16384" width="14.44140625" style="8"/>
+    <col min="1" max="1" width="27.6328125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="38.6328125" style="11" customWidth="1"/>
+    <col min="3" max="16384" width="14.453125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
@@ -17614,32 +17602,32 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>186</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
     </row>
-    <row r="3" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="5" t="s">
         <v>188</v>
       </c>
       <c r="C3" s="49">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>187</v>
       </c>
       <c r="C4" s="50">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="31"/>
       <c r="C5" s="31"/>
@@ -17677,13 +17665,17 @@
       <c r="B11" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C11" s="53"/>
+      <c r="C11" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="53"/>
+      <c r="C12" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
@@ -17694,7 +17686,7 @@
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="8"/>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>30</v>
       </c>
@@ -17801,7 +17793,7 @@
       </c>
       <c r="C32" s="116"/>
     </row>
-    <row r="33" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="13" x14ac:dyDescent="0.25">
       <c r="B33" s="27" t="s">
         <v>124</v>
       </c>
@@ -17811,7 +17803,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>130</v>
       </c>
@@ -17979,7 +17971,7 @@
       </c>
       <c r="C62" s="52"/>
     </row>
-    <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
     </row>
   </sheetData>
@@ -17996,25 +17988,25 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56" style="40" customWidth="1"/>
     <col min="2" max="2" width="20" style="28" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" style="28" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" style="28" customWidth="1"/>
-    <col min="5" max="5" width="36.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.453125" style="28" customWidth="1"/>
+    <col min="4" max="4" width="20.08984375" style="28" customWidth="1"/>
+    <col min="5" max="5" width="36.36328125" style="28" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.6640625" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="14.44140625" style="28"/>
+    <col min="7" max="7" width="22.6328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="14.453125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
         <v>69</v>
       </c>
       <c r="B1" s="41" t="str">
         <f>"Baseline ("&amp;start_year&amp;") coverage"</f>
-        <v>Baseline (2021) coverage</v>
+        <v>Baseline (2024) coverage</v>
       </c>
       <c r="C1" s="41" t="s">
         <v>195</v>
@@ -18809,15 +18801,15 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53" style="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="47.88671875" style="28" customWidth="1"/>
-    <col min="3" max="3" width="42.44140625" style="28" customWidth="1"/>
-    <col min="4" max="16384" width="11.44140625" style="28"/>
+    <col min="2" max="2" width="47.90625" style="28" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" style="28" customWidth="1"/>
+    <col min="4" max="16384" width="11.453125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>69</v>
       </c>
@@ -18953,13 +18945,13 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:A19"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.109375" style="28" customWidth="1"/>
-    <col min="2" max="16384" width="11.44140625" style="28"/>
+    <col min="1" max="1" width="30.08984375" style="28" customWidth="1"/>
+    <col min="2" max="16384" width="11.453125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>69</v>
       </c>
@@ -19046,7 +19038,7 @@
     <tabColor theme="0" tint="-0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
@@ -19155,19 +19147,19 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.90625" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="15.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
@@ -19214,7 +19206,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>31</v>
       </c>
@@ -19596,19 +19588,19 @@
       </c>
       <c r="D10" s="70">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="70">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="70">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="70">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="71">
         <v>0</v>
@@ -19775,7 +19767,7 @@
     <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="9"/>
     </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>32</v>
       </c>
@@ -19826,7 +19818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="5" t="s">
         <v>86</v>
@@ -19871,7 +19863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="5" t="s">
         <v>182</v>
@@ -19920,7 +19912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="5" t="s">
         <v>202</v>
@@ -19942,19 +19934,19 @@
       </c>
       <c r="H18" s="70">
         <f>frac_PW_health_facility</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="70">
         <f>frac_PW_health_facility</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="70">
         <f>frac_PW_health_facility</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="70">
         <f>frac_PW_health_facility</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="71">
         <v>0</v>
@@ -20156,7 +20148,7 @@
     <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="9"/>
     </row>
-    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>37</v>
       </c>
@@ -20406,7 +20398,7 @@
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
     </row>
-    <row r="30" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>35</v>
       </c>
@@ -20911,7 +20903,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
@@ -20944,16 +20936,16 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.6640625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" style="28" customWidth="1"/>
-    <col min="3" max="4" width="11.44140625" style="28"/>
-    <col min="5" max="5" width="17.44140625" style="28" customWidth="1"/>
-    <col min="6" max="16384" width="11.44140625" style="28"/>
+    <col min="1" max="1" width="33.6328125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" style="28" customWidth="1"/>
+    <col min="3" max="4" width="11.453125" style="28"/>
+    <col min="5" max="5" width="17.453125" style="28" customWidth="1"/>
+    <col min="6" max="16384" width="11.453125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>158</v>
       </c>
@@ -20970,7 +20962,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="14" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
         <v>153</v>
       </c>
@@ -20988,7 +20980,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="14" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
         <v>152</v>
       </c>
@@ -21006,7 +20998,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
         <v>151</v>
       </c>
@@ -21024,7 +21016,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="14" x14ac:dyDescent="0.3">
       <c r="A5" s="29" t="s">
         <v>150</v>
       </c>
@@ -21042,7 +21034,7 @@
         <v>0.126</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="14" x14ac:dyDescent="0.3">
       <c r="A6" s="29" t="s">
         <v>149</v>
       </c>
@@ -21060,7 +21052,7 @@
         <v>1.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="14" x14ac:dyDescent="0.3">
       <c r="A7" s="29" t="s">
         <v>148</v>
       </c>
@@ -21078,7 +21070,7 @@
         <v>0.40500000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="14" x14ac:dyDescent="0.3">
       <c r="A8" s="29" t="s">
         <v>147</v>
       </c>
@@ -21096,7 +21088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="14" x14ac:dyDescent="0.3">
       <c r="A9" s="29" t="s">
         <v>146</v>
       </c>
@@ -21114,7 +21106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="14" x14ac:dyDescent="0.3">
       <c r="A10" s="29" t="s">
         <v>145</v>
       </c>
@@ -21145,20 +21137,20 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:P42"/>
-  <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="16.08984375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.21875" style="43" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.88671875" style="43" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.44140625" style="43" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.1796875" style="43" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.90625" style="43" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.453125" style="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.08984375" style="43" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" style="43" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" style="43" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="15.33203125" style="43" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="16.88671875" style="43" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="16.109375" style="43"/>
+    <col min="6" max="7" width="13.08984375" style="43" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="15.36328125" style="43" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="16.90625" style="43" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="16.08984375" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="44" t="s">
         <v>33</v>
       </c>
@@ -21205,7 +21197,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="44" t="s">
         <v>31</v>
       </c>
@@ -21252,7 +21244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="40" t="s">
         <v>144</v>
       </c>
@@ -21296,7 +21288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="40" t="s">
         <v>168</v>
       </c>
@@ -21340,7 +21332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
         <v>193</v>
       </c>
@@ -21384,7 +21376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
         <v>194</v>
       </c>
@@ -21428,7 +21420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="40" t="s">
         <v>190</v>
       </c>
@@ -21472,7 +21464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
         <v>131</v>
       </c>
@@ -21516,7 +21508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
         <v>132</v>
       </c>
@@ -21560,7 +21552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
         <v>84</v>
       </c>
@@ -21604,7 +21596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
         <v>58</v>
       </c>
@@ -21648,7 +21640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="40" t="s">
         <v>337</v>
       </c>
@@ -21692,7 +21684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -21736,7 +21728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
         <v>28</v>
       </c>
@@ -21780,7 +21772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="40" t="s">
         <v>85</v>
       </c>
@@ -21824,7 +21816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="40" t="s">
         <v>60</v>
       </c>
@@ -21868,7 +21860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="40"/>
       <c r="C17" s="99"/>
       <c r="D17" s="99"/>
@@ -21884,7 +21876,7 @@
       <c r="N17" s="99"/>
       <c r="O17" s="99"/>
     </row>
-    <row r="18" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="44" t="s">
         <v>32</v>
       </c>
@@ -21931,7 +21923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="44"/>
       <c r="B19" s="40" t="s">
         <v>86</v>
@@ -21976,7 +21968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="73" t="s">
         <v>182</v>
       </c>
@@ -22020,7 +22012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="73" t="s">
         <v>202</v>
       </c>
@@ -22064,7 +22056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="74" t="s">
         <v>57</v>
       </c>
@@ -22108,7 +22100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="40" t="s">
         <v>88</v>
       </c>
@@ -22152,7 +22144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="40" t="s">
         <v>87</v>
       </c>
@@ -22196,7 +22188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="40" t="s">
         <v>59</v>
       </c>
@@ -22240,7 +22232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="40"/>
       <c r="C26" s="99"/>
       <c r="D26" s="99"/>
@@ -22256,7 +22248,7 @@
       <c r="N26" s="99"/>
       <c r="O26" s="99"/>
     </row>
-    <row r="27" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="44" t="s">
         <v>37</v>
       </c>
@@ -22304,7 +22296,7 @@
       </c>
       <c r="P27" s="75"/>
     </row>
-    <row r="28" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="46" t="s">
         <v>183</v>
       </c>
@@ -22348,7 +22340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="44"/>
       <c r="B29" s="46" t="s">
         <v>201</v>
@@ -22393,7 +22385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="46" t="s">
         <v>184</v>
       </c>
@@ -22437,7 +22429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="46" t="s">
         <v>185</v>
       </c>
@@ -22481,7 +22473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="40"/>
       <c r="C32" s="100"/>
       <c r="D32" s="100"/>
@@ -22497,7 +22489,7 @@
       <c r="N32" s="99"/>
       <c r="O32" s="99"/>
     </row>
-    <row r="33" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="44" t="s">
         <v>35</v>
       </c>
@@ -22544,7 +22536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="40" t="s">
         <v>64</v>
       </c>
@@ -22588,7 +22580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="40" t="s">
         <v>62</v>
       </c>
@@ -22632,7 +22624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="40" t="s">
         <v>47</v>
       </c>
@@ -22676,7 +22668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="40" t="s">
         <v>34</v>
       </c>
@@ -22720,7 +22712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="40" t="s">
         <v>83</v>
       </c>
@@ -22764,7 +22756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="40" t="s">
         <v>82</v>
       </c>
@@ -22808,7 +22800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="40" t="s">
         <v>81</v>
       </c>
@@ -22852,7 +22844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="40" t="s">
         <v>79</v>
       </c>
@@ -22896,7 +22888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="40" t="s">
         <v>80</v>
       </c>
@@ -22952,22 +22944,22 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="58.88671875" style="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" style="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="28" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" style="28" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="12.77734375" style="28"/>
+    <col min="1" max="1" width="58.90625" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.36328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.90625" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.36328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="12.81640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>69</v>
       </c>
@@ -23703,7 +23695,7 @@
       <c r="K39" s="102"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="r5uzVyzuX2cUXRUCd1eCp2cRQdoXMaTi7+j4lrtBEgwzDwwg07iN9Zvo/tiwSsVCYAFkOMHpp89HQAzExnqtEg==" saltValue="Yl6vtKysPUoNlkWylvJDXA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="IvQDIxW99fzq1Zy0EhkbKUzL+Oo6JppYFJRusT7f1RK58axANCQbQrXBA4I5Zda1hiQSlfJ6FnKfxlkgJRWRpg==" saltValue="tOfPnYqP3Wy6+yrctBxWkQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -23714,22 +23706,22 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" style="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" style="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="28" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" style="28" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="12.77734375" style="28"/>
+    <col min="1" max="1" width="16.90625" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.36328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.90625" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.36328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="12.81640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>211</v>
       </c>
@@ -24083,14 +24075,14 @@
     <tabColor rgb="FF007600"/>
   </sheetPr>
   <dimension ref="A1:I40"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" style="8" customWidth="1"/>
-    <col min="2" max="9" width="16.88671875" style="8" customWidth="1"/>
-    <col min="10" max="16384" width="14.44140625" style="8"/>
+    <col min="1" max="1" width="8.453125" style="8" customWidth="1"/>
+    <col min="2" max="9" width="16.90625" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="14.453125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -24122,7 +24114,7 @@
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>start_year</f>
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B2" s="57"/>
       <c r="C2" s="57"/>
@@ -24145,7 +24137,7 @@
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f t="shared" ref="A3:A40" si="3">IF($A$2+ROW(A3)-2&lt;=end_year,A2+1,"")</f>
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B3" s="57"/>
       <c r="C3" s="58"/>
@@ -24168,7 +24160,7 @@
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f t="shared" si="3"/>
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B4" s="57"/>
       <c r="C4" s="58"/>
@@ -24191,7 +24183,7 @@
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f t="shared" si="3"/>
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="B5" s="57"/>
       <c r="C5" s="58"/>
@@ -24214,7 +24206,7 @@
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="3"/>
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="B6" s="57"/>
       <c r="C6" s="58"/>
@@ -24237,7 +24229,7 @@
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f t="shared" si="3"/>
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="B7" s="57"/>
       <c r="C7" s="58"/>
@@ -24260,7 +24252,7 @@
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="3"/>
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="B8" s="57"/>
       <c r="C8" s="58"/>
@@ -24283,7 +24275,7 @@
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f t="shared" si="3"/>
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="B9" s="57"/>
       <c r="C9" s="58"/>
@@ -24306,7 +24298,7 @@
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="3"/>
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="B10" s="57"/>
       <c r="C10" s="58"/>
@@ -24329,7 +24321,7 @@
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f t="shared" si="3"/>
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="B11" s="57"/>
       <c r="C11" s="58"/>
@@ -24350,32 +24342,50 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="str">
+      <c r="A12" s="5">
         <f t="shared" si="3"/>
-        <v/>
+        <v>2034</v>
       </c>
       <c r="B12" s="57"/>
       <c r="C12" s="58"/>
       <c r="D12" s="58"/>
       <c r="E12" s="58"/>
       <c r="F12" s="58"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
+      <c r="G12" s="17">
+        <f t="shared" ref="G12:G13" si="4">C12+D12+E12+F12</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="17">
+        <f t="shared" ref="H12:H13" si="5">(B12 + stillbirth*B12/(1000-stillbirth))/(1-abortion)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="17">
+        <f t="shared" ref="I12:I13" si="6">G12-H12</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="str">
+      <c r="A13" s="5">
         <f t="shared" si="3"/>
-        <v/>
+        <v>2035</v>
       </c>
       <c r="B13" s="57"/>
       <c r="C13" s="58"/>
       <c r="D13" s="58"/>
       <c r="E13" s="58"/>
       <c r="F13" s="58"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
+      <c r="G13" s="17">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="17">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="17">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
@@ -24723,15 +24733,15 @@
       <c r="E38" s="58"/>
       <c r="F38" s="58"/>
       <c r="G38" s="17">
-        <f t="shared" ref="G38:G40" si="4">C38+D38+E38+F38</f>
+        <f t="shared" ref="G38:G40" si="7">C38+D38+E38+F38</f>
         <v>0</v>
       </c>
       <c r="H38" s="17">
-        <f t="shared" ref="H38:H40" si="5">(B38 + stillbirth*B38/(1000-stillbirth))/(1-abortion)</f>
+        <f t="shared" ref="H38:H40" si="8">(B38 + stillbirth*B38/(1000-stillbirth))/(1-abortion)</f>
         <v>0</v>
       </c>
       <c r="I38" s="17">
-        <f t="shared" ref="I38:I40" si="6">G38-H38</f>
+        <f t="shared" ref="I38:I40" si="9">G38-H38</f>
         <v>0</v>
       </c>
     </row>
@@ -24746,15 +24756,15 @@
       <c r="E39" s="58"/>
       <c r="F39" s="58"/>
       <c r="G39" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H39" s="17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I39" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -24769,20 +24779,20 @@
       <c r="E40" s="58"/>
       <c r="F40" s="58"/>
       <c r="G40" s="17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H40" s="17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I40" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="b3zuR9hAPFKmhyUPgxSBwpwr0L8i4PvaW2CunfDaw9hwq0s+u3YPrQFKBT82DJ5eJ424U2PP38ojcCo53DV0Pw==" saltValue="mehRfJSA9N1k+XdaDNGXRA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wKxEoWv7nnHIidhOP9O7yQQ4/tikEcXr6gTA2GrtyLYFAb1ix6Ln3irIlHONZ8I1dXNIh1a5t0Hcu3pPb5ZHrw==" saltValue="PZemEz5qyqkMYDJdSEC/KA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -24800,15 +24810,15 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:J157"/>
-  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.109375" style="28" customWidth="1"/>
+    <col min="1" max="1" width="48.08984375" style="28" customWidth="1"/>
     <col min="2" max="2" width="15" style="28" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="28" customWidth="1"/>
-    <col min="4" max="16384" width="12.77734375" style="28"/>
+    <col min="3" max="3" width="14.6328125" style="28" customWidth="1"/>
+    <col min="4" max="16384" width="12.81640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>212</v>
       </c>
@@ -24834,7 +24844,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
         <v>213</v>
       </c>
@@ -24912,8 +24922,6 @@
         <v>171</v>
       </c>
       <c r="D5" s="103">
-        <f>IFERROR((MIN(1,1.56*'Breastfeeding distribution'!$C$2)/(1-MIN(1,1.56*'Breastfeeding distribution'!$C$2))) /
-('Breastfeeding distribution'!$C$2/(1-'Breastfeeding distribution'!$C$2)), 1.56)</f>
         <v>1.56</v>
       </c>
       <c r="E5" s="103">
@@ -24935,8 +24943,6 @@
         <v>170</v>
       </c>
       <c r="D6" s="103">
-        <f>IFERROR((MIN(1,1.56*'Breastfeeding distribution'!$C$2)/(1-MIN(1,1.56*'Breastfeeding distribution'!$C$2))) /
-('Breastfeeding distribution'!$C$2/(1-'Breastfeeding distribution'!$C$2)), 1.56)</f>
         <v>1.56</v>
       </c>
       <c r="E6" s="103">
@@ -24984,8 +24990,6 @@
         <v>1</v>
       </c>
       <c r="E8" s="103">
-        <f>IFERROR((MIN(1,1.56*'Breastfeeding distribution'!$D$2)/(1-MIN(1,1.56*'Breastfeeding distribution'!$D$2))) /
-('Breastfeeding distribution'!$D$2/(1-'Breastfeeding distribution'!$D$2)), 1.56)</f>
         <v>1.56</v>
       </c>
       <c r="F8" s="103">
@@ -25007,8 +25011,6 @@
         <v>1</v>
       </c>
       <c r="E9" s="103">
-        <f>IFERROR((MIN(1,1.56*'Breastfeeding distribution'!$D$2)/(1-MIN(1,1.56*'Breastfeeding distribution'!$D$2))) /
-('Breastfeeding distribution'!$D$2/(1-'Breastfeeding distribution'!$D$2)), 1.56)</f>
         <v>1.56</v>
       </c>
       <c r="F9" s="103">
@@ -25172,7 +25174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="13" x14ac:dyDescent="0.25">
       <c r="B17" s="77" t="s">
         <v>167</v>
       </c>
@@ -25202,7 +25204,7 @@
       <c r="G18" s="101"/>
       <c r="H18" s="101"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" s="30" t="s">
         <v>214</v>
       </c>
@@ -25530,7 +25532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="13" x14ac:dyDescent="0.25">
       <c r="B34" s="77" t="s">
         <v>167</v>
       </c>
@@ -25560,7 +25562,7 @@
       <c r="G35" s="101"/>
       <c r="H35" s="101"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A36" s="78" t="s">
         <v>215</v>
       </c>
@@ -25888,7 +25890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="13" x14ac:dyDescent="0.25">
       <c r="B51" s="77" t="s">
         <v>167</v>
       </c>
@@ -25911,7 +25913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A53" s="107" t="s">
         <v>267</v>
       </c>
@@ -25923,7 +25925,7 @@
       <c r="G53" s="107"/>
       <c r="H53" s="107"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A54" s="30" t="s">
         <v>212</v>
       </c>
@@ -25949,7 +25951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A55" s="30" t="s">
         <v>311</v>
       </c>
@@ -26040,8 +26042,6 @@
         <v>171</v>
       </c>
       <c r="D58" s="103">
-        <f>IFERROR((MIN(1,1.37*'Breastfeeding distribution'!$C$2)/(1-MIN(1,1.37*'Breastfeeding distribution'!$C$2))) /
-('Breastfeeding distribution'!$C$2/(1-'Breastfeeding distribution'!$C$2)), 1.37)</f>
         <v>1.37</v>
       </c>
       <c r="E58" s="103">
@@ -26067,8 +26067,6 @@
         <v>170</v>
       </c>
       <c r="D59" s="103">
-        <f>IFERROR((MIN(1,1.37*'Breastfeeding distribution'!$C$2)/(1-MIN(1,1.37*'Breastfeeding distribution'!$C$2))) /
-('Breastfeeding distribution'!$C$2/(1-'Breastfeeding distribution'!$C$2)), 1.37)</f>
         <v>1.37</v>
       </c>
       <c r="E59" s="103">
@@ -26126,8 +26124,6 @@
         <v>1</v>
       </c>
       <c r="E61" s="103">
-        <f>IFERROR((MIN(1,1.37*'Breastfeeding distribution'!$D$2)/(1-MIN(1,1.37*'Breastfeeding distribution'!$D$2))) /
-('Breastfeeding distribution'!$D$2/(1-'Breastfeeding distribution'!$D$2)), 1.37)</f>
         <v>1.37</v>
       </c>
       <c r="F61" s="103">
@@ -26153,8 +26149,6 @@
         <v>1</v>
       </c>
       <c r="E62" s="103">
-        <f>IFERROR((MIN(1,1.37*'Breastfeeding distribution'!$D$2)/(1-MIN(1,1.37*'Breastfeeding distribution'!$D$2))) /
-('Breastfeeding distribution'!$D$2/(1-'Breastfeeding distribution'!$D$2)), 1.37)</f>
         <v>1.37</v>
       </c>
       <c r="F62" s="103">
@@ -26352,7 +26346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="13" x14ac:dyDescent="0.25">
       <c r="B70" s="77" t="s">
         <v>167</v>
       </c>
@@ -26387,7 +26381,7 @@
       <c r="G71" s="101"/>
       <c r="H71" s="101"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A72" s="30" t="s">
         <v>312</v>
       </c>
@@ -26790,7 +26784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="13" x14ac:dyDescent="0.25">
       <c r="B87" s="77" t="s">
         <v>167</v>
       </c>
@@ -26825,7 +26819,7 @@
       <c r="G88" s="101"/>
       <c r="H88" s="101"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A89" s="78" t="s">
         <v>313</v>
       </c>
@@ -27228,7 +27222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" ht="13" x14ac:dyDescent="0.25">
       <c r="B104" s="77" t="s">
         <v>167</v>
       </c>
@@ -27256,7 +27250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A106" s="107" t="s">
         <v>268</v>
       </c>
@@ -27268,7 +27262,7 @@
       <c r="G106" s="107"/>
       <c r="H106" s="107"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A107" s="30" t="s">
         <v>212</v>
       </c>
@@ -27294,7 +27288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A108" s="30" t="s">
         <v>314</v>
       </c>
@@ -27385,8 +27379,6 @@
         <v>171</v>
       </c>
       <c r="D111" s="103">
-        <f>IFERROR((MIN(1,1.77*'Breastfeeding distribution'!$C$2)/(1-MIN(1,1.77*'Breastfeeding distribution'!$C$2))) /
-('Breastfeeding distribution'!$C$2/(1-'Breastfeeding distribution'!$C$2)), 1.77)</f>
         <v>1.77</v>
       </c>
       <c r="E111" s="103">
@@ -27412,8 +27404,6 @@
         <v>170</v>
       </c>
       <c r="D112" s="103">
-        <f>IFERROR((MIN(1,1.77*'Breastfeeding distribution'!$C$2)/(1-MIN(1,1.77*'Breastfeeding distribution'!$C$2))) /
-('Breastfeeding distribution'!$C$2/(1-'Breastfeeding distribution'!$C$2)), 1.77)</f>
         <v>1.77</v>
       </c>
       <c r="E112" s="103">
@@ -27471,8 +27461,6 @@
         <v>1</v>
       </c>
       <c r="E114" s="103">
-        <f>IFERROR((MIN(1,1.77*'Breastfeeding distribution'!$D$2)/(1-MIN(1,1.77*'Breastfeeding distribution'!$D$2))) /
-('Breastfeeding distribution'!$D$2/(1-'Breastfeeding distribution'!$D$2)), 1.77)</f>
         <v>1.77</v>
       </c>
       <c r="F114" s="103">
@@ -27498,8 +27486,6 @@
         <v>1</v>
       </c>
       <c r="E115" s="103">
-        <f>IFERROR((MIN(1,1.77*'Breastfeeding distribution'!$D$2)/(1-MIN(1,1.77*'Breastfeeding distribution'!$D$2))) /
-('Breastfeeding distribution'!$D$2/(1-'Breastfeeding distribution'!$D$2)), 1.77)</f>
         <v>1.77</v>
       </c>
       <c r="F115" s="103">
@@ -27697,7 +27683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" ht="13" x14ac:dyDescent="0.25">
       <c r="B123" s="77" t="s">
         <v>167</v>
       </c>
@@ -27732,7 +27718,7 @@
       <c r="G124" s="101"/>
       <c r="H124" s="101"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A125" s="30" t="s">
         <v>315</v>
       </c>
@@ -28135,7 +28121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ht="13" x14ac:dyDescent="0.25">
       <c r="B140" s="77" t="s">
         <v>167</v>
       </c>
@@ -28170,7 +28156,7 @@
       <c r="G141" s="101"/>
       <c r="H141" s="101"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A142" s="78" t="s">
         <v>316</v>
       </c>
@@ -28573,7 +28559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:8" ht="13" x14ac:dyDescent="0.25">
       <c r="B157" s="77" t="s">
         <v>167</v>
       </c>
@@ -28602,7 +28588,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1IUQIPGO8A+lS5t9zmQeExgWOE7Hq9s+LMwGp5ZzK7cP6BPM6Y+s1H4DuDLssE5RfO3cDfuZkDwFgb68EXGf1A==" saltValue="EhqwdEStb6jxlKMHBUWr7g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="riIqDHxQDNIc95k8WEEMlpv2yK5yRhEl3GZr9d21PG7QnhNwxgtjaWmZN+9widROwyhXiwQ4XZiTM/cZ2Cl95g==" saltValue="b1Xx0XPjIcbtdUQJGdoNkQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="45">
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B2:B4"/>
@@ -28664,22 +28650,22 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:F79"/>
-  <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="16.08984375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.88671875" style="28" customWidth="1"/>
-    <col min="2" max="2" width="34.109375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" style="28" customWidth="1"/>
+    <col min="1" max="1" width="23.90625" style="28" customWidth="1"/>
+    <col min="2" max="2" width="34.08984375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="11.36328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" style="28" customWidth="1"/>
     <col min="5" max="6" width="15" style="28" customWidth="1"/>
-    <col min="7" max="16384" width="16.109375" style="28"/>
+    <col min="7" max="16384" width="16.08984375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="80" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="80" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="79" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="81"/>
       <c r="C2" s="82" t="s">
         <v>26</v>
@@ -28694,7 +28680,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
         <v>217</v>
       </c>
@@ -28778,7 +28764,7 @@
       <c r="E8" s="76"/>
       <c r="F8" s="76"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="30" t="s">
         <v>218</v>
       </c>
@@ -28801,7 +28787,7 @@
       <c r="E10" s="76"/>
       <c r="F10" s="76"/>
     </row>
-    <row r="11" spans="1:6" s="80" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="80" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="79" t="s">
         <v>219</v>
       </c>
@@ -28810,7 +28796,7 @@
       <c r="E11" s="89"/>
       <c r="F11" s="89"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="30" t="s">
         <v>220</v>
       </c>
@@ -28870,7 +28856,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="30"/>
       <c r="B16" s="46"/>
       <c r="C16" s="90"/>
@@ -28878,7 +28864,7 @@
       <c r="E16" s="76"/>
       <c r="F16" s="76"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
         <v>224</v>
       </c>
@@ -29027,7 +29013,7 @@
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="46"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="107" t="s">
         <v>267</v>
       </c>
@@ -29037,12 +29023,12 @@
       <c r="E27" s="110"/>
       <c r="F27" s="110"/>
     </row>
-    <row r="28" spans="1:6" s="80" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" s="80" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="79" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="81"/>
       <c r="C29" s="82" t="s">
         <v>26</v>
@@ -29057,7 +29043,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="30" t="s">
         <v>297</v>
       </c>
@@ -29157,7 +29143,7 @@
       <c r="E35" s="76"/>
       <c r="F35" s="76"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="30" t="s">
         <v>304</v>
       </c>
@@ -29178,7 +29164,7 @@
         <v>1.377</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="79" t="s">
         <v>219</v>
       </c>
@@ -29188,7 +29174,7 @@
       <c r="E38" s="89"/>
       <c r="F38" s="89"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="30" t="s">
         <v>298</v>
       </c>
@@ -29260,7 +29246,7 @@
         <v>3.7710000000000004</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="30"/>
       <c r="B43" s="46"/>
       <c r="C43" s="90"/>
@@ -29268,7 +29254,7 @@
       <c r="E43" s="76"/>
       <c r="F43" s="76"/>
     </row>
-    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="30" t="s">
         <v>302</v>
       </c>
@@ -29446,7 +29432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="107" t="s">
         <v>268</v>
       </c>
@@ -29456,12 +29442,12 @@
       <c r="E54" s="110"/>
       <c r="F54" s="110"/>
     </row>
-    <row r="55" spans="1:6" s="80" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" s="80" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="79" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="81"/>
       <c r="C56" s="82" t="s">
         <v>26</v>
@@ -29476,7 +29462,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="30" t="s">
         <v>303</v>
       </c>
@@ -29576,7 +29562,7 @@
       <c r="E62" s="76"/>
       <c r="F62" s="76"/>
     </row>
-    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="30" t="s">
         <v>305</v>
       </c>
@@ -29597,7 +29583,7 @@
         <v>1.6830000000000003</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="79" t="s">
         <v>219</v>
       </c>
@@ -29607,7 +29593,7 @@
       <c r="E65" s="89"/>
       <c r="F65" s="89"/>
     </row>
-    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="30" t="s">
         <v>306</v>
       </c>
@@ -29679,7 +29665,7 @@
         <v>4.6090000000000009</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="30"/>
       <c r="B70" s="46"/>
       <c r="C70" s="90"/>
@@ -29687,7 +29673,7 @@
       <c r="E70" s="76"/>
       <c r="F70" s="76"/>
     </row>
-    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="30" t="s">
         <v>310</v>
       </c>
@@ -29882,23 +29868,23 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:P328"/>
-  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.21875" style="28" customWidth="1"/>
-    <col min="2" max="2" width="26.88671875" style="28" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" style="28" customWidth="1"/>
-    <col min="4" max="8" width="14.77734375" style="28" customWidth="1"/>
-    <col min="9" max="12" width="15.33203125" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="16.88671875" style="28" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="12.77734375" style="28"/>
+    <col min="1" max="1" width="27.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="26.90625" style="28" customWidth="1"/>
+    <col min="3" max="3" width="18.36328125" style="28" customWidth="1"/>
+    <col min="4" max="8" width="14.81640625" style="28" customWidth="1"/>
+    <col min="9" max="12" width="15.36328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="16.90625" style="28" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="12.81640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="80" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="79" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="93" t="s">
         <v>206</v>
       </c>
@@ -29932,7 +29918,7 @@
       <c r="O2" s="94"/>
       <c r="P2" s="94"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A3" s="30"/>
       <c r="B3" s="28" t="s">
         <v>71</v>
@@ -30365,7 +30351,7 @@
       <c r="O17" s="93"/>
       <c r="P17" s="93"/>
     </row>
-    <row r="18" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="32" t="s">
         <v>231</v>
       </c>
@@ -30623,12 +30609,12 @@
       <c r="O26" s="93"/>
       <c r="P26" s="93"/>
     </row>
-    <row r="28" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" s="80" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A28" s="79" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A29" s="93" t="s">
         <v>233</v>
       </c>
@@ -30662,7 +30648,7 @@
       <c r="O29" s="94"/>
       <c r="P29" s="94"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A30" s="30"/>
       <c r="B30" s="28" t="s">
         <v>71</v>
@@ -31357,12 +31343,12 @@
       <c r="C54" s="32"/>
       <c r="D54" s="32"/>
     </row>
-    <row r="55" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" s="80" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A55" s="79" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" ht="26" x14ac:dyDescent="0.3">
       <c r="A56" s="93" t="s">
         <v>70</v>
       </c>
@@ -31390,7 +31376,7 @@
       <c r="O56" s="94"/>
       <c r="P56" s="94"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A57" s="30"/>
       <c r="B57" s="28" t="s">
         <v>38</v>
@@ -31536,12 +31522,12 @@
       <c r="C63" s="32"/>
       <c r="D63" s="32"/>
     </row>
-    <row r="64" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" s="80" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A64" s="79" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" ht="26" x14ac:dyDescent="0.3">
       <c r="A65" s="93" t="s">
         <v>24</v>
       </c>
@@ -31575,7 +31561,7 @@
       <c r="O65" s="94"/>
       <c r="P65" s="94"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A66" s="97"/>
       <c r="B66" s="28" t="s">
         <v>73</v>
@@ -32611,12 +32597,12 @@
       <c r="O101" s="93"/>
       <c r="P101" s="93"/>
     </row>
-    <row r="103" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" s="80" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A103" s="79" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" ht="26" x14ac:dyDescent="0.3">
       <c r="A104" s="93" t="s">
         <v>71</v>
       </c>
@@ -32650,7 +32636,7 @@
       <c r="O104" s="94"/>
       <c r="P104" s="94"/>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A105" s="30"/>
       <c r="C105" s="32" t="s">
         <v>161</v>
@@ -32763,13 +32749,13 @@
       <c r="O108" s="93"/>
       <c r="P108" s="93"/>
     </row>
-    <row r="110" spans="1:16" s="108" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" s="108" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A110" s="107" t="s">
         <v>267</v>
       </c>
       <c r="H110" s="107"/>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A111" s="79" t="s">
         <v>225</v>
       </c>
@@ -32781,7 +32767,7 @@
       <c r="G111" s="80"/>
       <c r="H111" s="80"/>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A112" s="93" t="s">
         <v>206</v>
       </c>
@@ -32807,7 +32793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A113" s="30"/>
       <c r="B113" s="28" t="s">
         <v>71</v>
@@ -33426,7 +33412,7 @@
         <v>2.7090000000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A138" s="79" t="s">
         <v>232</v>
       </c>
@@ -33438,7 +33424,7 @@
       <c r="G138" s="80"/>
       <c r="H138" s="80"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A139" s="93" t="s">
         <v>233</v>
       </c>
@@ -33464,7 +33450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A140" s="30"/>
       <c r="B140" s="28" t="s">
         <v>71</v>
@@ -34087,7 +34073,7 @@
       <c r="C164" s="32"/>
       <c r="D164" s="32"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A165" s="79" t="s">
         <v>235</v>
       </c>
@@ -34099,7 +34085,7 @@
       <c r="G165" s="80"/>
       <c r="H165" s="80"/>
     </row>
-    <row r="166" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" ht="26" x14ac:dyDescent="0.3">
       <c r="A166" s="93" t="s">
         <v>70</v>
       </c>
@@ -34123,7 +34109,7 @@
       </c>
       <c r="H166" s="94"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A167" s="30"/>
       <c r="B167" s="28" t="s">
         <v>38</v>
@@ -34269,7 +34255,7 @@
       <c r="C173" s="32"/>
       <c r="D173" s="32"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A174" s="79" t="s">
         <v>239</v>
       </c>
@@ -34281,7 +34267,7 @@
       <c r="G174" s="80"/>
       <c r="H174" s="80"/>
     </row>
-    <row r="175" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" ht="26" x14ac:dyDescent="0.3">
       <c r="A175" s="93" t="s">
         <v>24</v>
       </c>
@@ -34307,7 +34293,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A176" s="97"/>
       <c r="B176" s="28" t="s">
         <v>73</v>
@@ -35199,7 +35185,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A213" s="79" t="s">
         <v>241</v>
       </c>
@@ -35211,7 +35197,7 @@
       <c r="G213" s="80"/>
       <c r="H213" s="80"/>
     </row>
-    <row r="214" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" ht="26" x14ac:dyDescent="0.3">
       <c r="A214" s="93" t="s">
         <v>71</v>
       </c>
@@ -35237,7 +35223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A215" s="30"/>
       <c r="C215" s="32" t="s">
         <v>161</v>
@@ -35334,13 +35320,13 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="220" spans="1:9" s="108" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" s="108" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A220" s="107" t="s">
         <v>268</v>
       </c>
       <c r="H220" s="107"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A221" s="79" t="s">
         <v>225</v>
       </c>
@@ -35353,7 +35339,7 @@
       <c r="H221" s="80"/>
       <c r="I221" s="80"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A222" s="93" t="s">
         <v>206</v>
       </c>
@@ -35380,7 +35366,7 @@
       </c>
       <c r="I222" s="94"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A223" s="30"/>
       <c r="B223" s="28" t="s">
         <v>71</v>
@@ -36023,7 +36009,7 @@
       </c>
       <c r="I246" s="93"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A248" s="79" t="s">
         <v>232</v>
       </c>
@@ -36036,7 +36022,7 @@
       <c r="H248" s="80"/>
       <c r="I248" s="80"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A249" s="93" t="s">
         <v>233</v>
       </c>
@@ -36063,7 +36049,7 @@
       </c>
       <c r="I249" s="94"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A250" s="30"/>
       <c r="B250" s="28" t="s">
         <v>71</v>
@@ -36710,7 +36696,7 @@
       <c r="C274" s="32"/>
       <c r="D274" s="32"/>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A275" s="79" t="s">
         <v>235</v>
       </c>
@@ -36723,7 +36709,7 @@
       <c r="H275" s="80"/>
       <c r="I275" s="80"/>
     </row>
-    <row r="276" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" ht="26" x14ac:dyDescent="0.3">
       <c r="A276" s="93" t="s">
         <v>70</v>
       </c>
@@ -36747,7 +36733,7 @@
       </c>
       <c r="H276" s="94"/>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A277" s="30"/>
       <c r="B277" s="28" t="s">
         <v>38</v>
@@ -36893,7 +36879,7 @@
       <c r="C283" s="32"/>
       <c r="D283" s="32"/>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A284" s="79" t="s">
         <v>239</v>
       </c>
@@ -36906,7 +36892,7 @@
       <c r="H284" s="80"/>
       <c r="I284" s="80"/>
     </row>
-    <row r="285" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" ht="26" x14ac:dyDescent="0.3">
       <c r="A285" s="93" t="s">
         <v>24</v>
       </c>
@@ -36933,7 +36919,7 @@
       </c>
       <c r="I285" s="94"/>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A286" s="97"/>
       <c r="B286" s="28" t="s">
         <v>73</v>
@@ -37861,7 +37847,7 @@
       </c>
       <c r="I321" s="93"/>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A323" s="79" t="s">
         <v>241</v>
       </c>
@@ -37874,7 +37860,7 @@
       <c r="H323" s="80"/>
       <c r="I323" s="80"/>
     </row>
-    <row r="324" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" ht="26" x14ac:dyDescent="0.3">
       <c r="A324" s="93" t="s">
         <v>71</v>
       </c>
@@ -37901,7 +37887,7 @@
       </c>
       <c r="I324" s="94"/>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A325" s="30"/>
       <c r="C325" s="32" t="s">
         <v>161</v>
@@ -38019,24 +38005,24 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G67"/>
-  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.88671875" style="28" customWidth="1"/>
-    <col min="2" max="2" width="44.44140625" style="28" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" style="28" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" style="28" customWidth="1"/>
-    <col min="5" max="5" width="17.21875" style="28" customWidth="1"/>
+    <col min="1" max="1" width="44.90625" style="28" customWidth="1"/>
+    <col min="2" max="2" width="44.453125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" style="28" customWidth="1"/>
+    <col min="4" max="4" width="17.54296875" style="28" customWidth="1"/>
+    <col min="5" max="5" width="17.1796875" style="28" customWidth="1"/>
     <col min="6" max="6" width="15" style="28" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" style="28" customWidth="1"/>
-    <col min="8" max="16384" width="12.77734375" style="28"/>
+    <col min="7" max="7" width="13.6328125" style="28" customWidth="1"/>
+    <col min="8" max="16384" width="12.81640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="79" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="97" t="s">
         <v>25</v>
       </c>
@@ -38077,7 +38063,7 @@
         <v>174.7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="30"/>
       <c r="B4" s="73" t="s">
         <v>245</v>
@@ -38098,7 +38084,7 @@
         <v>1.0249999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="84" t="s">
         <v>246</v>
       </c>
@@ -38114,12 +38100,9 @@
         <v>1</v>
       </c>
       <c r="E6" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!$E$4),0.64, (0.64*SUM('Nutritional status distribution'!$E$4:$E$5)/(1-0.64*SUM('Nutritional status distribution'!$E$4:$E$5)))
-/ (SUM('Nutritional status distribution'!$E$4:$E$5)/(1-SUM('Nutritional status distribution'!$E$4:$E$5))))</f>
         <v>0.64</v>
       </c>
       <c r="F6" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!$F$4),0.64, (0.64*SUM('Nutritional status distribution'!$F$4:$F$5)/(1-0.64*SUM('Nutritional status distribution'!$F$4:$F$5)))/ (SUM('Nutritional status distribution'!$F$4:$F$5)/(1-SUM('Nutritional status distribution'!$F$4:$F$5))))</f>
         <v>0.64</v>
       </c>
       <c r="G6" s="105">
@@ -38137,11 +38120,9 @@
         <v>1</v>
       </c>
       <c r="E7" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!$E$4),0.88, (0.88*SUM('Nutritional status distribution'!$E$4:$E$5)/(1-0.88*SUM('Nutritional status distribution'!$E$4:$E$5)))/ (SUM('Nutritional status distribution'!$E$4:$E$5)/(1-SUM('Nutritional status distribution'!$E$4:$E$5))))</f>
         <v>0.88</v>
       </c>
       <c r="F7" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!$F$4),0.88, (0.88*SUM('Nutritional status distribution'!$F$4:$F$5)/(1-0.88*SUM('Nutritional status distribution'!$F$4:$F$5)))/ (SUM('Nutritional status distribution'!$F$4:$F$5)/(1-SUM('Nutritional status distribution'!$F$4:$F$5))))</f>
         <v>0.88</v>
       </c>
       <c r="G7" s="105">
@@ -38159,11 +38140,9 @@
         <v>1</v>
       </c>
       <c r="E8" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!$E$4),0.88, (0.88*SUM('Nutritional status distribution'!$E$4:$E$5)/(1-0.88*SUM('Nutritional status distribution'!$E$4:$E$5)))/ (SUM('Nutritional status distribution'!$E$4:$E$5)/(1-SUM('Nutritional status distribution'!$E$4:$E$5))))</f>
         <v>0.88</v>
       </c>
       <c r="F8" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!$F$4),0.88, (0.88*SUM('Nutritional status distribution'!$F$4:$F$5)/(1-0.88*SUM('Nutritional status distribution'!$F$4:$F$5)))/ (SUM('Nutritional status distribution'!$F$4:$F$5)/(1-SUM('Nutritional status distribution'!$F$4:$F$5))))</f>
         <v>0.88</v>
       </c>
       <c r="G8" s="105">
@@ -38198,12 +38177,12 @@
       <c r="F10" s="73"/>
       <c r="G10" s="73"/>
     </row>
-    <row r="11" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="79" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="84"/>
       <c r="B12" s="46" t="s">
         <v>190</v>
@@ -38224,16 +38203,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="84"/>
       <c r="B13" s="46"/>
     </row>
-    <row r="14" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="79" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="97" t="s">
         <v>233</v>
       </c>
@@ -38256,7 +38235,7 @@
         <v>1.0249999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="30"/>
       <c r="B16" s="73" t="s">
         <v>250</v>
@@ -38277,7 +38256,7 @@
         <v>1.0249999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="97" t="s">
         <v>70</v>
       </c>
@@ -38301,12 +38280,12 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="79" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="84" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" s="84" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="44" t="s">
         <v>49</v>
       </c>
@@ -38337,12 +38316,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="107" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A23" s="107" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A24" s="79" t="s">
         <v>242</v>
       </c>
@@ -38353,7 +38332,7 @@
       <c r="F24" s="80"/>
       <c r="G24" s="80"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A25" s="97" t="s">
         <v>25</v>
       </c>
@@ -38398,7 +38377,7 @@
         <v>157.22999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A27" s="30"/>
       <c r="B27" s="73" t="s">
         <v>278</v>
@@ -38424,7 +38403,7 @@
         <v>0.92249999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A28" s="84" t="s">
         <v>319</v>
       </c>
@@ -38442,11 +38421,9 @@
         <v>1</v>
       </c>
       <c r="E29" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$4),0.44, (0.44*SUM('Nutritional status distribution'!E$4:E$5)/(1-0.44*SUM('Nutritional status distribution'!E$4:E$5)))/ (SUM('Nutritional status distribution'!E$4:E$5)/(1-SUM('Nutritional status distribution'!E$4:E$5))))</f>
         <v>0.44</v>
       </c>
       <c r="F29" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$4),0.44, (0.44*SUM('Nutritional status distribution'!F$4:F$5)/(1-0.44*SUM('Nutritional status distribution'!F$4:F$5)))/ (SUM('Nutritional status distribution'!F$4:F$5)/(1-SUM('Nutritional status distribution'!F$4:F$5))))</f>
         <v>0.44</v>
       </c>
       <c r="G29" s="105">
@@ -38467,11 +38444,9 @@
         <v>1</v>
       </c>
       <c r="E30" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$4),0.85, (0.85*SUM('Nutritional status distribution'!E$4:E$5)/(1-0.85*SUM('Nutritional status distribution'!E$4:E$5)))/ (SUM('Nutritional status distribution'!E$4:E$5)/(1-SUM('Nutritional status distribution'!E$4:E$5))))</f>
         <v>0.85</v>
       </c>
       <c r="F30" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$4),0.85, (0.85*SUM('Nutritional status distribution'!F$4:F$5)/(1-0.85*SUM('Nutritional status distribution'!F$4:F$5)))/ (SUM('Nutritional status distribution'!F$4:F$5)/(1-SUM('Nutritional status distribution'!F$4:F$5))))</f>
         <v>0.85</v>
       </c>
       <c r="G30" s="105">
@@ -38492,11 +38467,9 @@
         <v>1</v>
       </c>
       <c r="E31" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$4),0.85, (0.85*SUM('Nutritional status distribution'!E$4:E$5)/(1-0.85*SUM('Nutritional status distribution'!E$4:E$5)))/ (SUM('Nutritional status distribution'!E$4:E$5)/(1-SUM('Nutritional status distribution'!E$4:E$5))))</f>
         <v>0.85</v>
       </c>
       <c r="F31" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$4),0.85, (0.85*SUM('Nutritional status distribution'!F$4:F$5)/(1-0.85*SUM('Nutritional status distribution'!F$4:F$5)))/ (SUM('Nutritional status distribution'!F$4:F$5)/(1-SUM('Nutritional status distribution'!F$4:F$5))))</f>
         <v>0.85</v>
       </c>
       <c r="G31" s="105">
@@ -38537,7 +38510,7 @@
       <c r="F33" s="73"/>
       <c r="G33" s="73"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A34" s="79" t="s">
         <v>320</v>
       </c>
@@ -38548,18 +38521,16 @@
       <c r="F34" s="80"/>
       <c r="G34" s="80"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A35" s="84"/>
       <c r="B35" s="46" t="s">
         <v>282</v>
       </c>
       <c r="C35" s="105">
-        <f>C12*0.9</f>
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="D35" s="105">
-        <f t="shared" ref="D35" si="6">D12*0.9</f>
-        <v>1.2509999999999999</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="E35" s="105">
         <v>1</v>
@@ -38571,11 +38542,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A36" s="84"/>
       <c r="B36" s="46"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A37" s="79" t="s">
         <v>248</v>
       </c>
@@ -38586,7 +38557,7 @@
       <c r="F37" s="80"/>
       <c r="G37" s="80"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A38" s="97" t="s">
         <v>233</v>
       </c>
@@ -38598,49 +38569,49 @@
         <v>0.92249999999999999</v>
       </c>
       <c r="D38" s="105">
-        <f t="shared" ref="D38:G38" si="7">IF(D15=1,1,D15*0.9)</f>
+        <f t="shared" ref="D38:G38" si="6">IF(D15=1,1,D15*0.9)</f>
         <v>0.92249999999999999</v>
       </c>
       <c r="E38" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="F38" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="G38" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0.92249999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A39" s="30"/>
       <c r="B39" s="73" t="s">
         <v>284</v>
       </c>
       <c r="C39" s="105">
-        <f t="shared" ref="C39:G39" si="8">IF(C16=1,1,C16*0.9)</f>
+        <f t="shared" ref="C39:G39" si="7">IF(C16=1,1,C16*0.9)</f>
         <v>0.92249999999999999</v>
       </c>
       <c r="D39" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="E39" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="F39" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.92249999999999999</v>
       </c>
       <c r="G39" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.92249999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A40" s="97" t="s">
         <v>70</v>
       </c>
@@ -38648,27 +38619,27 @@
         <v>285</v>
       </c>
       <c r="C40" s="105">
-        <f t="shared" ref="C40:G40" si="9">IF(C17=1,1,C17*0.9)</f>
+        <f t="shared" ref="C40:G40" si="8">IF(C17=1,1,C17*0.9)</f>
         <v>1</v>
       </c>
       <c r="D40" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E40" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="F40" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="G40" s="105">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A42" s="79" t="s">
         <v>321</v>
       </c>
@@ -38679,7 +38650,7 @@
       <c r="F42" s="80"/>
       <c r="G42" s="80"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A43" s="84"/>
       <c r="B43" s="84"/>
       <c r="C43" s="44" t="s">
@@ -38714,12 +38685,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="107" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A46" s="107" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A47" s="79" t="s">
         <v>242</v>
       </c>
@@ -38730,7 +38701,7 @@
       <c r="F47" s="80"/>
       <c r="G47" s="80"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A48" s="97" t="s">
         <v>25</v>
       </c>
@@ -38759,23 +38730,23 @@
         <v>244</v>
       </c>
       <c r="D49" s="105">
-        <f t="shared" ref="D49:G50" si="10">D3*1.05</f>
+        <f t="shared" ref="D49:G50" si="9">D3*1.05</f>
         <v>47.25</v>
       </c>
       <c r="E49" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>379.68000000000006</v>
       </c>
       <c r="F49" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>183.435</v>
       </c>
       <c r="G49" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>183.435</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A50" s="30"/>
       <c r="B50" s="73" t="s">
         <v>288</v>
@@ -38785,23 +38756,23 @@
         <v>1.0762499999999999</v>
       </c>
       <c r="D50" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1.0762499999999999</v>
       </c>
       <c r="E50" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1.0762499999999999</v>
       </c>
       <c r="F50" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1.0762499999999999</v>
       </c>
       <c r="G50" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1.0762499999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A51" s="84" t="s">
         <v>324</v>
       </c>
@@ -38815,19 +38786,17 @@
         <v>1</v>
       </c>
       <c r="D52" s="105">
-        <f t="shared" ref="D52:G52" si="11">IF(D6=1,1,D6*1.1)</f>
+        <f t="shared" ref="D52:G52" si="10">IF(D6=1,1,D6*1.1)</f>
         <v>1</v>
       </c>
       <c r="E52" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$4),0.92, (0.92*SUM('Nutritional status distribution'!E$4:E$5)/(1-0.92*SUM('Nutritional status distribution'!E$4:E$5)))/ (SUM('Nutritional status distribution'!E$4:E$5)/(1-SUM('Nutritional status distribution'!E$4:E$5))))</f>
         <v>0.92</v>
       </c>
       <c r="F52" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$4),0.92, (0.92*SUM('Nutritional status distribution'!F$4:F$5)/(1-0.92*SUM('Nutritional status distribution'!F$4:F$5)))/ (SUM('Nutritional status distribution'!F$4:F$5)/(1-SUM('Nutritional status distribution'!F$4:F$5))))</f>
         <v>0.92</v>
       </c>
       <c r="G52" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -38836,23 +38805,21 @@
         <v>290</v>
       </c>
       <c r="C53" s="105">
-        <f t="shared" ref="C53:G53" si="12">IF(C7=1,1,C7*1.1)</f>
+        <f t="shared" ref="C53:G53" si="11">IF(C7=1,1,C7*1.1)</f>
         <v>1</v>
       </c>
       <c r="D53" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="E53" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$4),0.91, (0.91*SUM('Nutritional status distribution'!E$4:E$5)/(1-0.91*SUM('Nutritional status distribution'!E$4:E$5)))/ (SUM('Nutritional status distribution'!E$4:E$5)/(1-SUM('Nutritional status distribution'!E$4:E$5))))</f>
         <v>0.91</v>
       </c>
       <c r="F53" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$4),0.91, (0.91*SUM('Nutritional status distribution'!F$4:F$5)/(1-0.91*SUM('Nutritional status distribution'!F$4:F$5)))/ (SUM('Nutritional status distribution'!F$4:F$5)/(1-SUM('Nutritional status distribution'!F$4:F$5))))</f>
         <v>0.91</v>
       </c>
       <c r="G53" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -38861,23 +38828,21 @@
         <v>339</v>
       </c>
       <c r="C54" s="105">
-        <f t="shared" ref="C54:G54" si="13">IF(C8=1,1,C8*1.1)</f>
+        <f t="shared" ref="C54:G54" si="12">IF(C8=1,1,C8*1.1)</f>
         <v>1</v>
       </c>
       <c r="D54" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E54" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$4),0.91, (0.91*SUM('Nutritional status distribution'!E$4:E$5)/(1-0.91*SUM('Nutritional status distribution'!E$4:E$5)))/ (SUM('Nutritional status distribution'!E$4:E$5)/(1-SUM('Nutritional status distribution'!E$4:E$5))))</f>
         <v>0.91</v>
       </c>
       <c r="F54" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$4),0.91, (0.91*SUM('Nutritional status distribution'!F$4:F$5)/(1-0.91*SUM('Nutritional status distribution'!F$4:F$5)))/ (SUM('Nutritional status distribution'!F$4:F$5)/(1-SUM('Nutritional status distribution'!F$4:F$5))))</f>
         <v>0.91</v>
       </c>
       <c r="G54" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -38886,23 +38851,23 @@
         <v>291</v>
       </c>
       <c r="C55" s="105">
-        <f t="shared" ref="C55:G55" si="14">IF(C9=1,1,C9*1.1)</f>
+        <f t="shared" ref="C55:G55" si="13">IF(C9=1,1,C9*1.1)</f>
         <v>1</v>
       </c>
       <c r="D55" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E55" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F55" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G55" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -38914,7 +38879,7 @@
       <c r="F56" s="73"/>
       <c r="G56" s="73"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A57" s="79" t="s">
         <v>322</v>
       </c>
@@ -38925,18 +38890,16 @@
       <c r="F57" s="80"/>
       <c r="G57" s="80"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A58" s="84"/>
       <c r="B58" s="46" t="s">
         <v>292</v>
       </c>
       <c r="C58" s="105">
-        <f>C12*1.1</f>
-        <v>1.6500000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="D58" s="105">
-        <f t="shared" ref="D58" si="15">D12*1.1</f>
-        <v>1.5289999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="E58" s="105">
         <v>1</v>
@@ -38948,11 +38911,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A59" s="84"/>
       <c r="B59" s="46"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A60" s="79" t="s">
         <v>248</v>
       </c>
@@ -38963,7 +38926,7 @@
       <c r="F60" s="80"/>
       <c r="G60" s="80"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A61" s="97" t="s">
         <v>233</v>
       </c>
@@ -38975,49 +38938,49 @@
         <v>1.1274999999999999</v>
       </c>
       <c r="D61" s="105">
-        <f t="shared" ref="D61:G61" si="16">IF(D15=1,1,D15*1.1)</f>
+        <f t="shared" ref="D61:G61" si="14">IF(D15=1,1,D15*1.1)</f>
         <v>1.1274999999999999</v>
       </c>
       <c r="E61" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="F61" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="G61" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1.1274999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A62" s="30"/>
       <c r="B62" s="73" t="s">
         <v>294</v>
       </c>
       <c r="C62" s="105">
-        <f t="shared" ref="C62:G62" si="17">IF(C16=1,1,C16*1.1)</f>
+        <f t="shared" ref="C62:G62" si="15">IF(C16=1,1,C16*1.1)</f>
         <v>1.1274999999999999</v>
       </c>
       <c r="D62" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="E62" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="F62" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>1.1274999999999999</v>
       </c>
       <c r="G62" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>1.1274999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A63" s="97" t="s">
         <v>70</v>
       </c>
@@ -39025,27 +38988,27 @@
         <v>295</v>
       </c>
       <c r="C63" s="105">
-        <f t="shared" ref="C63:G63" si="18">IF(C17=1,1,C17*1.1)</f>
+        <f t="shared" ref="C63:G63" si="16">IF(C17=1,1,C17*1.1)</f>
         <v>1</v>
       </c>
       <c r="D63" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E63" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="F63" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="G63" s="105">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A65" s="79" t="s">
         <v>323</v>
       </c>
@@ -39056,7 +39019,7 @@
       <c r="F65" s="80"/>
       <c r="G65" s="80"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A66" s="84"/>
       <c r="B66" s="84"/>
       <c r="C66" s="44" t="s">
@@ -39096,7 +39059,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
-    <ignoredError sqref="D26:G26 C44 C50:G50 D49:G49 C35:D35 C58:D58 C61:G63 C27:G28 C38:G40 C52:D52 C32:G32 C30:D30 G30 C31:D31 G31 C55:G55 C53:D53 G53 C54:D54 G54 C29:D29 G29 G52" unlockedFormula="1"/>
+    <ignoredError sqref="D26:G26 C44 C50:G50 D49:G49 C61:G63 C27:G28 C38:G40 C52:D52 C32:G32 C30:D30 G30 C31:D31 G31 C55:G55 C53:D53 G53 C54:D54 G54 C29:D29 G29 G52" unlockedFormula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -39108,16 +39071,16 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="16.08984375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.21875" style="28" customWidth="1"/>
-    <col min="2" max="6" width="16.109375" style="28"/>
-    <col min="7" max="7" width="17.21875" style="28" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" style="28" customWidth="1"/>
-    <col min="9" max="16384" width="16.109375" style="28"/>
+    <col min="1" max="1" width="52.1796875" style="28" customWidth="1"/>
+    <col min="2" max="6" width="16.08984375" style="28"/>
+    <col min="7" max="7" width="17.1796875" style="28" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" style="28" customWidth="1"/>
+    <col min="9" max="16384" width="16.08984375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
         <v>69</v>
       </c>
@@ -39365,12 +39328,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" s="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="107" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="42" t="s">
         <v>69</v>
       </c>
@@ -39640,12 +39603,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" s="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="107" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="42" t="s">
         <v>69</v>
       </c>
@@ -39932,15 +39895,15 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:O67"/>
-  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.5546875" style="28" customWidth="1"/>
-    <col min="2" max="2" width="58.88671875" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.54296875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="58.90625" style="28" bestFit="1" customWidth="1"/>
     <col min="3" max="15" width="15" style="28" customWidth="1"/>
-    <col min="16" max="16384" width="12.77734375" style="28"/>
+    <col min="16" max="16384" width="12.81640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="30"/>
       <c r="B1" s="30"/>
       <c r="C1" s="83" t="s">
@@ -39983,7 +39946,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
         <v>255</v>
       </c>
@@ -40328,16 +40291,16 @@
         <v>1</v>
       </c>
       <c r="L10" s="105">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="M10" s="105">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="N10" s="105">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="O10" s="105">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -40428,7 +40391,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="46" t="s">
         <v>132</v>
       </c>
@@ -40560,7 +40523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="13" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
         <v>256</v>
       </c>
@@ -40621,58 +40584,47 @@
         <v>1</v>
       </c>
       <c r="E19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$14),0.72,(0.72*'Nutritional status distribution'!E$14/(1-0.72*'Nutritional status distribution'!E$14))
-/ ('Nutritional status distribution'!E$14/(1-'Nutritional status distribution'!E$14)))</f>
+        <f>0.72</f>
         <v>0.72</v>
       </c>
       <c r="F19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$14),0.72,(0.72*'Nutritional status distribution'!F$14/(1-0.72*'Nutritional status distribution'!F$14))
-/ ('Nutritional status distribution'!F$14/(1-'Nutritional status distribution'!F$14)))</f>
+        <f t="shared" ref="F19:O19" si="0">0.72</f>
         <v>0.72</v>
       </c>
       <c r="G19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!G$14),0.72,(0.72*'Nutritional status distribution'!G$14/(1-0.72*'Nutritional status distribution'!G$14))
-/ ('Nutritional status distribution'!G$14/(1-'Nutritional status distribution'!G$14)))</f>
+        <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
       <c r="H19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!H$14),0.72,(0.72*'Nutritional status distribution'!H$14/(1-0.72*'Nutritional status distribution'!H$14))
-/ ('Nutritional status distribution'!H$14/(1-'Nutritional status distribution'!H$14)))</f>
+        <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
       <c r="I19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!I$14),0.72,(0.72*'Nutritional status distribution'!I$14/(1-0.72*'Nutritional status distribution'!I$14))
-/ ('Nutritional status distribution'!I$14/(1-'Nutritional status distribution'!I$14)))</f>
+        <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
       <c r="J19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!J$14),0.72,(0.72*'Nutritional status distribution'!J$14/(1-0.72*'Nutritional status distribution'!J$14))
-/ ('Nutritional status distribution'!J$14/(1-'Nutritional status distribution'!J$14)))</f>
+        <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
       <c r="K19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!K$14),0.72,(0.72*'Nutritional status distribution'!K$14/(1-0.72*'Nutritional status distribution'!K$14))
-/ ('Nutritional status distribution'!K$14/(1-'Nutritional status distribution'!K$14)))</f>
+        <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
       <c r="L19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!L$14),0.72,(0.72*'Nutritional status distribution'!L$14/(1-0.72*'Nutritional status distribution'!L$14))
-/ ('Nutritional status distribution'!L$14/(1-'Nutritional status distribution'!L$14)))</f>
+        <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
       <c r="M19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!M$14),0.72,(0.72*'Nutritional status distribution'!M$14/(1-0.72*'Nutritional status distribution'!M$14))
-/ ('Nutritional status distribution'!M$14/(1-'Nutritional status distribution'!M$14)))</f>
+        <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
       <c r="N19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!N$14),0.72,(0.72*'Nutritional status distribution'!N$14/(1-0.72*'Nutritional status distribution'!N$14))
-/ ('Nutritional status distribution'!N$14/(1-'Nutritional status distribution'!N$14)))</f>
+        <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
       <c r="O19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!O$14),0.72,(0.72*'Nutritional status distribution'!O$14/(1-0.72*'Nutritional status distribution'!O$14))
-/ ('Nutritional status distribution'!O$14/(1-'Nutritional status distribution'!O$14)))</f>
+        <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
     </row>
@@ -40731,67 +40683,45 @@
         <v>1</v>
       </c>
       <c r="E21" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$14),0.8,(0.8*'Nutritional status distribution'!E$14/(1-0.8*'Nutritional status distribution'!E$14))
-/ ('Nutritional status distribution'!E$14/(1-'Nutritional status distribution'!E$14)))</f>
         <v>0.8</v>
       </c>
       <c r="F21" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$14),0.8,(0.8*'Nutritional status distribution'!F$14/(1-0.8*'Nutritional status distribution'!F$14))
-/ ('Nutritional status distribution'!F$14/(1-'Nutritional status distribution'!F$14)))</f>
         <v>0.8</v>
       </c>
       <c r="G21" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!G$14),0.8,(0.8*'Nutritional status distribution'!G$14/(1-0.8*'Nutritional status distribution'!G$14))
-/ ('Nutritional status distribution'!G$14/(1-'Nutritional status distribution'!G$14)))</f>
         <v>0.8</v>
       </c>
       <c r="H21" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!H$14),0.8,(0.8*'Nutritional status distribution'!H$14/(1-0.8*'Nutritional status distribution'!H$14))
-/ ('Nutritional status distribution'!H$14/(1-'Nutritional status distribution'!H$14)))</f>
         <v>0.8</v>
       </c>
       <c r="I21" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!I$14),0.8,(0.8*'Nutritional status distribution'!I$14/(1-0.8*'Nutritional status distribution'!I$14))
-/ ('Nutritional status distribution'!I$14/(1-'Nutritional status distribution'!I$14)))</f>
         <v>0.8</v>
       </c>
       <c r="J21" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!J$14),0.8,(0.8*'Nutritional status distribution'!J$14/(1-0.8*'Nutritional status distribution'!J$14))
-/ ('Nutritional status distribution'!J$14/(1-'Nutritional status distribution'!J$14)))</f>
         <v>0.8</v>
       </c>
       <c r="K21" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!K$14),0.8,(0.8*'Nutritional status distribution'!K$14/(1-0.8*'Nutritional status distribution'!K$14))
-/ ('Nutritional status distribution'!K$14/(1-'Nutritional status distribution'!K$14)))</f>
         <v>0.8</v>
       </c>
       <c r="L21" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!L$14),0.8,(0.8*'Nutritional status distribution'!L$14/(1-0.8*'Nutritional status distribution'!L$14))
-/ ('Nutritional status distribution'!L$14/(1-'Nutritional status distribution'!L$14)))</f>
         <v>0.8</v>
       </c>
       <c r="M21" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!M$14),0.8,(0.8*'Nutritional status distribution'!M$14/(1-0.8*'Nutritional status distribution'!M$14))
-/ ('Nutritional status distribution'!M$14/(1-'Nutritional status distribution'!M$14)))</f>
         <v>0.8</v>
       </c>
       <c r="N21" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!N$14),0.8,(0.8*'Nutritional status distribution'!N$14/(1-0.8*'Nutritional status distribution'!N$14))
-/ ('Nutritional status distribution'!N$14/(1-'Nutritional status distribution'!N$14)))</f>
         <v>0.8</v>
       </c>
       <c r="O21" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!O$14),0.8,(0.8*'Nutritional status distribution'!O$14/(1-0.8*'Nutritional status distribution'!O$14))
-/ ('Nutritional status distribution'!O$14/(1-'Nutritional status distribution'!O$14)))</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="107" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A23" s="107" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="26" x14ac:dyDescent="0.3">
       <c r="A24" s="30"/>
       <c r="B24" s="30"/>
       <c r="C24" s="83" t="s">
@@ -40834,7 +40764,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="13" x14ac:dyDescent="0.3">
       <c r="A25" s="30" t="s">
         <v>271</v>
       </c>
@@ -40850,47 +40780,47 @@
         <v>0.4</v>
       </c>
       <c r="E26" s="105">
-        <f t="shared" ref="E26:O26" si="0">IF(E3=1,1,E3*0.9)</f>
+        <f t="shared" ref="E26:O26" si="1">IF(E3=1,1,E3*0.9)</f>
         <v>1</v>
       </c>
       <c r="F26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="O26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -40899,23 +40829,23 @@
         <v>183</v>
       </c>
       <c r="C27" s="105">
-        <f t="shared" ref="C27:O27" si="1">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:O27" si="2">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H27" s="105">
@@ -40931,19 +40861,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -40952,23 +40882,23 @@
         <v>201</v>
       </c>
       <c r="C28" s="105">
-        <f t="shared" ref="C28:O28" si="2">IF(C5=1,1,C5*0.9)</f>
+        <f t="shared" ref="C28:O28" si="3">IF(C5=1,1,C5*0.9)</f>
         <v>1</v>
       </c>
       <c r="D28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H28" s="105">
@@ -40984,19 +40914,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -41005,23 +40935,23 @@
         <v>184</v>
       </c>
       <c r="C29" s="105">
-        <f t="shared" ref="C29:O29" si="3">IF(C6=1,1,C6*0.9)</f>
+        <f t="shared" ref="C29:O29" si="4">IF(C6=1,1,C6*0.9)</f>
         <v>1</v>
       </c>
       <c r="D29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="F29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H29" s="105">
@@ -41037,19 +40967,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="M29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="N29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -41058,23 +40988,23 @@
         <v>185</v>
       </c>
       <c r="C30" s="105">
-        <f t="shared" ref="C30:O30" si="4">IF(C7=1,1,C7*0.9)</f>
+        <f t="shared" ref="C30:O30" si="5">IF(C7=1,1,C7*0.9)</f>
         <v>1</v>
       </c>
       <c r="D30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H30" s="105">
@@ -41090,19 +41020,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="M30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="N30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="O30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -41111,39 +41041,39 @@
         <v>182</v>
       </c>
       <c r="C31" s="105">
-        <f t="shared" ref="C31:K31" si="5">IF(C8=1,1,C8*0.9)</f>
+        <f t="shared" ref="C31:K31" si="6">IF(C8=1,1,C8*0.9)</f>
         <v>1</v>
       </c>
       <c r="D31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L31" s="105">
@@ -41164,39 +41094,39 @@
         <v>202</v>
       </c>
       <c r="C32" s="105">
-        <f t="shared" ref="C32:K32" si="6">IF(C9=1,1,C9*0.9)</f>
+        <f t="shared" ref="C32:K32" si="7">IF(C9=1,1,C9*0.9)</f>
         <v>1</v>
       </c>
       <c r="D32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L32" s="105">
@@ -41217,39 +41147,39 @@
         <v>57</v>
       </c>
       <c r="C33" s="105">
-        <f t="shared" ref="C33:K33" si="7">IF(C10=1,1,C10*0.9)</f>
+        <f t="shared" ref="C33:K33" si="8">IF(C10=1,1,C10*0.9)</f>
         <v>1</v>
       </c>
       <c r="D33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="F33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="G33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L33" s="105">
@@ -41270,11 +41200,11 @@
         <v>131</v>
       </c>
       <c r="C34" s="105">
-        <f t="shared" ref="C34:O34" si="8">IF(C11=1,1,C11*0.9)</f>
+        <f t="shared" ref="C34:O34" si="9">IF(C11=1,1,C11*0.9)</f>
         <v>1</v>
       </c>
       <c r="D34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="E34" s="105">
@@ -41287,35 +41217,35 @@
         <v>1</v>
       </c>
       <c r="H34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="I34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="L34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="M34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="N34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="O34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -41368,11 +41298,11 @@
         <v>132</v>
       </c>
       <c r="C36" s="105">
-        <f t="shared" ref="C36:O36" si="9">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:O36" si="10">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E36" s="105">
@@ -41385,35 +41315,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="I36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="L36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="M36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="N36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="O36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -41422,39 +41352,39 @@
         <v>59</v>
       </c>
       <c r="C37" s="105">
-        <f t="shared" ref="C37:K37" si="10">IF(C14=1,1,C14*0.9)</f>
+        <f t="shared" ref="C37:K37" si="11">IF(C14=1,1,C14*0.9)</f>
         <v>1</v>
       </c>
       <c r="D37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="E37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="F37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="G37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="I37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="J37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="K37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="L37" s="105">
@@ -41462,15 +41392,15 @@
         <v>0.38</v>
       </c>
       <c r="M37" s="105">
-        <f t="shared" ref="M37:O37" si="11">M32</f>
+        <f t="shared" ref="M37:O37" si="12">M32</f>
         <v>0.38</v>
       </c>
       <c r="N37" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.38</v>
       </c>
       <c r="O37" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.38</v>
       </c>
     </row>
@@ -41479,11 +41409,11 @@
         <v>337</v>
       </c>
       <c r="C38" s="105">
-        <f t="shared" ref="C38:O38" si="12">IF(C15=1,1,C15*0.9)</f>
+        <f t="shared" ref="C38:O38" si="13">IF(C15=1,1,C15*0.9)</f>
         <v>1</v>
       </c>
       <c r="D38" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E38" s="105">
@@ -41493,43 +41423,43 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H38" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="I38" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="J38" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="K38" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="L38" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="M38" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="N38" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="O38" s="105">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="13" x14ac:dyDescent="0.3">
       <c r="A40" s="30" t="s">
         <v>272</v>
       </c>
@@ -41540,55 +41470,55 @@
         <v>63</v>
       </c>
       <c r="C41" s="105">
-        <f t="shared" ref="C41:O41" si="13">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:O41" si="14">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="E41" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="F41" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="G41" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="H41" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="I41" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="J41" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="K41" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="L41" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M41" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N41" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O41" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -41597,66 +41527,44 @@
         <v>64</v>
       </c>
       <c r="C42" s="105">
-        <f t="shared" ref="C42:D44" si="14">IF(C19=1,1,C19*0.9)</f>
+        <f t="shared" ref="C42:D44" si="15">IF(C19=1,1,C19*0.9)</f>
         <v>1</v>
       </c>
       <c r="D42" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E42" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$14),0.54,(0.54*'Nutritional status distribution'!E$14/(1-0.54*'Nutritional status distribution'!E$14))
-/ ('Nutritional status distribution'!E$14/(1-'Nutritional status distribution'!E$14)))</f>
         <v>0.54</v>
       </c>
       <c r="F42" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$14),0.54,(0.54*'Nutritional status distribution'!F$14/(1-0.54*'Nutritional status distribution'!F$14))
-/ ('Nutritional status distribution'!F$14/(1-'Nutritional status distribution'!F$14)))</f>
         <v>0.54</v>
       </c>
       <c r="G42" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!G$14),0.54,(0.54*'Nutritional status distribution'!G$14/(1-0.54*'Nutritional status distribution'!G$14))
-/ ('Nutritional status distribution'!G$14/(1-'Nutritional status distribution'!G$14)))</f>
         <v>0.54</v>
       </c>
       <c r="H42" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!H$14),0.54,(0.54*'Nutritional status distribution'!H$14/(1-0.54*'Nutritional status distribution'!H$14))
-/ ('Nutritional status distribution'!H$14/(1-'Nutritional status distribution'!H$14)))</f>
         <v>0.54</v>
       </c>
       <c r="I42" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!I$14),0.54,(0.54*'Nutritional status distribution'!I$14/(1-0.54*'Nutritional status distribution'!I$14))
-/ ('Nutritional status distribution'!I$14/(1-'Nutritional status distribution'!I$14)))</f>
         <v>0.54</v>
       </c>
       <c r="J42" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!J$14),0.54,(0.54*'Nutritional status distribution'!J$14/(1-0.54*'Nutritional status distribution'!J$14))
-/ ('Nutritional status distribution'!J$14/(1-'Nutritional status distribution'!J$14)))</f>
         <v>0.54</v>
       </c>
       <c r="K42" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!K$14),0.54,(0.54*'Nutritional status distribution'!K$14/(1-0.54*'Nutritional status distribution'!K$14))
-/ ('Nutritional status distribution'!K$14/(1-'Nutritional status distribution'!K$14)))</f>
         <v>0.54</v>
       </c>
       <c r="L42" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!L$14),0.54,(0.54*'Nutritional status distribution'!L$14/(1-0.54*'Nutritional status distribution'!L$14))
-/ ('Nutritional status distribution'!L$14/(1-'Nutritional status distribution'!L$14)))</f>
         <v>0.54</v>
       </c>
       <c r="M42" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!M$14),0.54,(0.54*'Nutritional status distribution'!M$14/(1-0.54*'Nutritional status distribution'!M$14))
-/ ('Nutritional status distribution'!M$14/(1-'Nutritional status distribution'!M$14)))</f>
         <v>0.54</v>
       </c>
       <c r="N42" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!N$14),0.54,(0.54*'Nutritional status distribution'!N$14/(1-0.54*'Nutritional status distribution'!N$14))
-/ ('Nutritional status distribution'!N$14/(1-'Nutritional status distribution'!N$14)))</f>
         <v>0.54</v>
       </c>
       <c r="O42" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!O$14),0.54,(0.54*'Nutritional status distribution'!O$14/(1-0.54*'Nutritional status distribution'!O$14))
-/ ('Nutritional status distribution'!O$14/(1-'Nutritional status distribution'!O$14)))</f>
         <v>0.54</v>
       </c>
     </row>
@@ -41665,55 +41573,55 @@
         <v>62</v>
       </c>
       <c r="C43" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="D43" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E43" s="105">
-        <f t="shared" ref="E43:O43" si="15">IF(E20=1,1,E20*0.9)</f>
+        <f t="shared" ref="E43:O43" si="16">IF(E20=1,1,E20*0.9)</f>
         <v>1</v>
       </c>
       <c r="F43" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="G43" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="H43" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="I43" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="J43" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="K43" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="L43" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="M43" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="N43" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O43" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
     </row>
@@ -41722,75 +41630,53 @@
         <v>47</v>
       </c>
       <c r="C44" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="D44" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E44" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$14),0.7,(0.7*'Nutritional status distribution'!E$14/(1-0.7*'Nutritional status distribution'!E$14))
-/ ('Nutritional status distribution'!E$14/(1-'Nutritional status distribution'!E$14)))</f>
         <v>0.7</v>
       </c>
       <c r="F44" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$14),0.7,(0.7*'Nutritional status distribution'!F$14/(1-0.7*'Nutritional status distribution'!F$14))
-/ ('Nutritional status distribution'!F$14/(1-'Nutritional status distribution'!F$14)))</f>
         <v>0.7</v>
       </c>
       <c r="G44" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!G$14),0.7,(0.7*'Nutritional status distribution'!G$14/(1-0.7*'Nutritional status distribution'!G$14))
-/ ('Nutritional status distribution'!G$14/(1-'Nutritional status distribution'!G$14)))</f>
         <v>0.7</v>
       </c>
       <c r="H44" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!H$14),0.7,(0.7*'Nutritional status distribution'!H$14/(1-0.7*'Nutritional status distribution'!H$14))
-/ ('Nutritional status distribution'!H$14/(1-'Nutritional status distribution'!H$14)))</f>
         <v>0.7</v>
       </c>
       <c r="I44" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!I$14),0.7,(0.7*'Nutritional status distribution'!I$14/(1-0.7*'Nutritional status distribution'!I$14))
-/ ('Nutritional status distribution'!I$14/(1-'Nutritional status distribution'!I$14)))</f>
         <v>0.7</v>
       </c>
       <c r="J44" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!J$14),0.7,(0.7*'Nutritional status distribution'!J$14/(1-0.7*'Nutritional status distribution'!J$14))
-/ ('Nutritional status distribution'!J$14/(1-'Nutritional status distribution'!J$14)))</f>
         <v>0.7</v>
       </c>
       <c r="K44" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!K$14),0.7,(0.7*'Nutritional status distribution'!K$14/(1-0.7*'Nutritional status distribution'!K$14))
-/ ('Nutritional status distribution'!K$14/(1-'Nutritional status distribution'!K$14)))</f>
         <v>0.7</v>
       </c>
       <c r="L44" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!L$14),0.7,(0.7*'Nutritional status distribution'!L$14/(1-0.7*'Nutritional status distribution'!L$14))
-/ ('Nutritional status distribution'!L$14/(1-'Nutritional status distribution'!L$14)))</f>
         <v>0.7</v>
       </c>
       <c r="M44" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!M$14),0.7,(0.7*'Nutritional status distribution'!M$14/(1-0.7*'Nutritional status distribution'!M$14))
-/ ('Nutritional status distribution'!M$14/(1-'Nutritional status distribution'!M$14)))</f>
         <v>0.7</v>
       </c>
       <c r="N44" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!N$14),0.7,(0.7*'Nutritional status distribution'!N$14/(1-0.7*'Nutritional status distribution'!N$14))
-/ ('Nutritional status distribution'!N$14/(1-'Nutritional status distribution'!N$14)))</f>
         <v>0.7</v>
       </c>
       <c r="O44" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!O$14),0.7,(0.7*'Nutritional status distribution'!O$14/(1-0.7*'Nutritional status distribution'!O$14))
-/ ('Nutritional status distribution'!O$14/(1-'Nutritional status distribution'!O$14)))</f>
         <v>0.7</v>
       </c>
     </row>
-    <row r="46" spans="1:15" s="107" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A46" s="107" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="26" x14ac:dyDescent="0.3">
       <c r="A47" s="30"/>
       <c r="B47" s="30"/>
       <c r="C47" s="83" t="s">
@@ -41833,7 +41719,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="13" x14ac:dyDescent="0.3">
       <c r="A48" s="30" t="s">
         <v>273</v>
       </c>
@@ -41849,47 +41735,47 @@
         <v>0.7</v>
       </c>
       <c r="E49" s="105">
-        <f t="shared" ref="E49:O49" si="16">IF(E3=1,1,E3*1.05)</f>
+        <f t="shared" ref="E49:O49" si="17">IF(E3=1,1,E3*1.05)</f>
         <v>1</v>
       </c>
       <c r="F49" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G49" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H49" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="I49" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="J49" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="K49" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L49" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M49" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N49" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O49" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -41898,23 +41784,23 @@
         <v>183</v>
       </c>
       <c r="C50" s="105">
-        <f t="shared" ref="C50:O50" si="17">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:O50" si="18">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E50" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="F50" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G50" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H50" s="105">
@@ -41930,19 +41816,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="M50" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="N50" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="O50" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
@@ -41951,23 +41837,23 @@
         <v>201</v>
       </c>
       <c r="C51" s="105">
-        <f t="shared" ref="C51:O51" si="18">IF(C5=1,1,C5*1.05)</f>
+        <f t="shared" ref="C51:O51" si="19">IF(C5=1,1,C5*1.05)</f>
         <v>1</v>
       </c>
       <c r="D51" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E51" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F51" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G51" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H51" s="105">
@@ -41983,19 +41869,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M51" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="N51" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="O51" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
@@ -42004,23 +41890,23 @@
         <v>184</v>
       </c>
       <c r="C52" s="105">
-        <f t="shared" ref="C52:O52" si="19">IF(C6=1,1,C6*1.05)</f>
+        <f t="shared" ref="C52:O52" si="20">IF(C6=1,1,C6*1.05)</f>
         <v>1</v>
       </c>
       <c r="D52" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E52" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F52" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G52" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H52" s="105">
@@ -42036,19 +41922,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="M52" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="N52" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="O52" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -42057,23 +41943,23 @@
         <v>185</v>
       </c>
       <c r="C53" s="105">
-        <f t="shared" ref="C53:O53" si="20">IF(C7=1,1,C7*1.05)</f>
+        <f t="shared" ref="C53:O53" si="21">IF(C7=1,1,C7*1.05)</f>
         <v>1</v>
       </c>
       <c r="D53" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E53" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="F53" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="G53" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="H53" s="105">
@@ -42089,19 +41975,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="M53" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="N53" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="O53" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
     </row>
@@ -42110,39 +41996,39 @@
         <v>182</v>
       </c>
       <c r="C54" s="105">
-        <f t="shared" ref="C54:K54" si="21">IF(C8=1,1,C8*1.05)</f>
+        <f t="shared" ref="C54:K54" si="22">IF(C8=1,1,C8*1.05)</f>
         <v>1</v>
       </c>
       <c r="D54" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="E54" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="F54" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="G54" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="H54" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="I54" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="J54" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="K54" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="L54" s="105">
@@ -42163,39 +42049,39 @@
         <v>202</v>
       </c>
       <c r="C55" s="105">
-        <f t="shared" ref="C55:K55" si="22">IF(C9=1,1,C9*1.05)</f>
+        <f t="shared" ref="C55:K55" si="23">IF(C9=1,1,C9*1.05)</f>
         <v>1</v>
       </c>
       <c r="D55" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="E55" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="F55" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="G55" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="H55" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="I55" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="J55" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="K55" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="L55" s="105">
@@ -42216,52 +42102,52 @@
         <v>57</v>
       </c>
       <c r="C56" s="105">
-        <f t="shared" ref="C56:K56" si="23">IF(C10=1,1,C10*1.05)</f>
+        <f t="shared" ref="C56:K56" si="24">IF(C10=1,1,C10*1.05)</f>
         <v>1</v>
       </c>
       <c r="D56" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="E56" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="F56" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="G56" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="H56" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="I56" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="J56" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="K56" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="L56" s="105">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="M56" s="105">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="N56" s="105">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="O56" s="105">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -42269,11 +42155,11 @@
         <v>131</v>
       </c>
       <c r="C57" s="105">
-        <f t="shared" ref="C57:O57" si="24">IF(C11=1,1,C11*1.05)</f>
+        <f t="shared" ref="C57:O57" si="25">IF(C11=1,1,C11*1.05)</f>
         <v>1</v>
       </c>
       <c r="D57" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="E57" s="105">
@@ -42283,39 +42169,39 @@
         <v>0.77</v>
       </c>
       <c r="G57" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="H57" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="I57" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="J57" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="K57" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="L57" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="M57" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="N57" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="O57" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
     </row>
@@ -42368,11 +42254,11 @@
         <v>132</v>
       </c>
       <c r="C59" s="105">
-        <f t="shared" ref="C59:O59" si="25">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:O59" si="26">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="E59" s="105">
@@ -42385,35 +42271,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="I59" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="J59" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="K59" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="L59" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="M59" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="N59" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="O59" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
     </row>
@@ -42422,39 +42308,39 @@
         <v>59</v>
       </c>
       <c r="C60" s="105">
-        <f t="shared" ref="C60:K60" si="26">IF(C14=1,1,C14*1.05)</f>
+        <f t="shared" ref="C60:K60" si="27">IF(C14=1,1,C14*1.05)</f>
         <v>1</v>
       </c>
       <c r="D60" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="E60" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="F60" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G60" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="H60" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="I60" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="J60" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="K60" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="L60" s="105">
@@ -42462,15 +42348,15 @@
         <v>0.7</v>
       </c>
       <c r="M60" s="105">
-        <f t="shared" ref="M60:O60" si="27">M54</f>
+        <f t="shared" ref="M60:O60" si="28">M54</f>
         <v>0.7</v>
       </c>
       <c r="N60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.7</v>
       </c>
       <c r="O60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.7</v>
       </c>
     </row>
@@ -42479,11 +42365,11 @@
         <v>337</v>
       </c>
       <c r="C61" s="105">
-        <f t="shared" ref="C61:O61" si="28">IF(C15=1,1,C15*1.05)</f>
+        <f t="shared" ref="C61:O61" si="29">IF(C15=1,1,C15*1.05)</f>
         <v>1</v>
       </c>
       <c r="D61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="E61" s="105">
@@ -42493,43 +42379,43 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="I61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="J61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="K61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="L61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="M61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="N61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="O61" s="105">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="13" x14ac:dyDescent="0.3">
       <c r="A63" s="30" t="s">
         <v>274</v>
       </c>
@@ -42540,55 +42426,55 @@
         <v>63</v>
       </c>
       <c r="C64" s="105">
-        <f t="shared" ref="C64:O64" si="29">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:O64" si="30">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="E64" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F64" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G64" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="H64" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="I64" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="J64" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="K64" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="L64" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="M64" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="N64" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="O64" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
     </row>
@@ -42597,66 +42483,44 @@
         <v>64</v>
       </c>
       <c r="C65" s="105">
-        <f t="shared" ref="C65:D67" si="30">IF(C19=1,1,C19*1.05)</f>
+        <f t="shared" ref="C65:D67" si="31">IF(C19=1,1,C19*1.05)</f>
         <v>1</v>
       </c>
       <c r="D65" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="E65" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$14),0.97,(0.97*'Nutritional status distribution'!E$14/(1-0.97*'Nutritional status distribution'!E$14))
-/ ('Nutritional status distribution'!E$14/(1-'Nutritional status distribution'!E$14)))</f>
         <v>0.97</v>
       </c>
       <c r="F65" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$14),0.97,(0.97*'Nutritional status distribution'!F$14/(1-0.97*'Nutritional status distribution'!F$14))
-/ ('Nutritional status distribution'!F$14/(1-'Nutritional status distribution'!F$14)))</f>
         <v>0.97</v>
       </c>
       <c r="G65" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!G$14),0.97,(0.97*'Nutritional status distribution'!G$14/(1-0.97*'Nutritional status distribution'!G$14))
-/ ('Nutritional status distribution'!G$14/(1-'Nutritional status distribution'!G$14)))</f>
         <v>0.97</v>
       </c>
       <c r="H65" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!H$14),0.97,(0.97*'Nutritional status distribution'!H$14/(1-0.97*'Nutritional status distribution'!H$14))
-/ ('Nutritional status distribution'!H$14/(1-'Nutritional status distribution'!H$14)))</f>
         <v>0.97</v>
       </c>
       <c r="I65" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!I$14),0.97,(0.97*'Nutritional status distribution'!I$14/(1-0.97*'Nutritional status distribution'!I$14))
-/ ('Nutritional status distribution'!I$14/(1-'Nutritional status distribution'!I$14)))</f>
         <v>0.97</v>
       </c>
       <c r="J65" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!J$14),0.97,(0.97*'Nutritional status distribution'!J$14/(1-0.97*'Nutritional status distribution'!J$14))
-/ ('Nutritional status distribution'!J$14/(1-'Nutritional status distribution'!J$14)))</f>
         <v>0.97</v>
       </c>
       <c r="K65" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!K$14),0.97,(0.97*'Nutritional status distribution'!K$14/(1-0.97*'Nutritional status distribution'!K$14))
-/ ('Nutritional status distribution'!K$14/(1-'Nutritional status distribution'!K$14)))</f>
         <v>0.97</v>
       </c>
       <c r="L65" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!L$14),0.97,(0.97*'Nutritional status distribution'!L$14/(1-0.97*'Nutritional status distribution'!L$14))
-/ ('Nutritional status distribution'!L$14/(1-'Nutritional status distribution'!L$14)))</f>
         <v>0.97</v>
       </c>
       <c r="M65" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!M$14),0.97,(0.97*'Nutritional status distribution'!M$14/(1-0.97*'Nutritional status distribution'!M$14))
-/ ('Nutritional status distribution'!M$14/(1-'Nutritional status distribution'!M$14)))</f>
         <v>0.97</v>
       </c>
       <c r="N65" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!N$14),0.97,(0.97*'Nutritional status distribution'!N$14/(1-0.97*'Nutritional status distribution'!N$14))
-/ ('Nutritional status distribution'!N$14/(1-'Nutritional status distribution'!N$14)))</f>
         <v>0.97</v>
       </c>
       <c r="O65" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!O$14),0.97,(0.97*'Nutritional status distribution'!O$14/(1-0.97*'Nutritional status distribution'!O$14))
-/ ('Nutritional status distribution'!O$14/(1-'Nutritional status distribution'!O$14)))</f>
         <v>0.97</v>
       </c>
     </row>
@@ -42665,55 +42529,55 @@
         <v>62</v>
       </c>
       <c r="C66" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="D66" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="E66" s="105">
-        <f t="shared" ref="E66:O66" si="31">IF(E20=1,1,E20*1.05)</f>
+        <f t="shared" ref="E66:O66" si="32">IF(E20=1,1,E20*1.05)</f>
         <v>1</v>
       </c>
       <c r="F66" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G66" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="H66" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="I66" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="J66" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="K66" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="L66" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="M66" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="N66" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="O66" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
     </row>
@@ -42722,61 +42586,41 @@
         <v>47</v>
       </c>
       <c r="C67" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="D67" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="E67" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$14),0.92,(0.92*'Nutritional status distribution'!E$14/(1-0.92*'Nutritional status distribution'!E$14))
-/ ('Nutritional status distribution'!E$14/(1-'Nutritional status distribution'!E$14)))</f>
         <v>0.92</v>
       </c>
       <c r="F67" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$14),0.92,(0.92*'Nutritional status distribution'!F$14/(1-0.92*'Nutritional status distribution'!F$14))
-/ ('Nutritional status distribution'!F$14/(1-'Nutritional status distribution'!F$14)))</f>
         <v>0.92</v>
       </c>
       <c r="G67" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!G$14),0.92,(0.92*'Nutritional status distribution'!G$14/(1-0.92*'Nutritional status distribution'!G$14))
-/ ('Nutritional status distribution'!G$14/(1-'Nutritional status distribution'!G$14)))</f>
         <v>0.92</v>
       </c>
       <c r="H67" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!H$14),0.92,(0.92*'Nutritional status distribution'!H$14/(1-0.92*'Nutritional status distribution'!H$14))
-/ ('Nutritional status distribution'!H$14/(1-'Nutritional status distribution'!H$14)))</f>
         <v>0.92</v>
       </c>
       <c r="I67" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!I$14),0.92,(0.92*'Nutritional status distribution'!I$14/(1-0.92*'Nutritional status distribution'!I$14))
-/ ('Nutritional status distribution'!I$14/(1-'Nutritional status distribution'!I$14)))</f>
         <v>0.92</v>
       </c>
       <c r="J67" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!J$14),0.92,(0.92*'Nutritional status distribution'!J$14/(1-0.92*'Nutritional status distribution'!J$14))
-/ ('Nutritional status distribution'!J$14/(1-'Nutritional status distribution'!J$14)))</f>
         <v>0.92</v>
       </c>
       <c r="K67" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!K$14),0.92,(0.92*'Nutritional status distribution'!K$14/(1-0.92*'Nutritional status distribution'!K$14))
-/ ('Nutritional status distribution'!K$14/(1-'Nutritional status distribution'!K$14)))</f>
         <v>0.92</v>
       </c>
       <c r="L67" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!L$14),0.92,(0.92*'Nutritional status distribution'!L$14/(1-0.92*'Nutritional status distribution'!L$14))
-/ ('Nutritional status distribution'!L$14/(1-'Nutritional status distribution'!L$14)))</f>
         <v>0.92</v>
       </c>
       <c r="M67" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!M$14),0.92,(0.92*'Nutritional status distribution'!M$14/(1-0.92*'Nutritional status distribution'!M$14))
-/ ('Nutritional status distribution'!M$14/(1-'Nutritional status distribution'!M$14)))</f>
         <v>0.92</v>
       </c>
       <c r="N67" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!N$14),0.92,(0.92*'Nutritional status distribution'!N$14/(1-0.92*'Nutritional status distribution'!N$14))
-/ ('Nutritional status distribution'!N$14/(1-'Nutritional status distribution'!N$14)))</f>
         <v>0.92</v>
       </c>
       <c r="O67" s="105">
@@ -42802,15 +42646,15 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" style="28" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" style="28" customWidth="1"/>
-    <col min="3" max="7" width="15.5546875" style="28" customWidth="1"/>
-    <col min="8" max="16384" width="12.77734375" style="28"/>
+    <col min="1" max="1" width="21.36328125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" style="28" customWidth="1"/>
+    <col min="3" max="7" width="15.54296875" style="28" customWidth="1"/>
+    <col min="8" max="16384" width="12.81640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="30"/>
       <c r="B1" s="42"/>
       <c r="C1" s="30" t="s">
@@ -42829,7 +42673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
         <v>257</v>
       </c>
@@ -42842,27 +42686,23 @@
         <v>1</v>
       </c>
       <c r="D3" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!D$11),(1/1.33),((1/1.33)*'Nutritional status distribution'!D$11/(1-(1/1.33)*'Nutritional status distribution'!D$11))
-/ ('Nutritional status distribution'!D$11/(1-'Nutritional status distribution'!D$11)))</f>
+        <f>1/1.33</f>
         <v>0.75187969924812026</v>
       </c>
       <c r="E3" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$11),(1/1.33),((1/1.33)*'Nutritional status distribution'!E$11/(1-(1/1.33)*'Nutritional status distribution'!E$11))
-/ ('Nutritional status distribution'!E$11/(1-'Nutritional status distribution'!E$11)))</f>
+        <f t="shared" ref="E3:G3" si="0">1/1.33</f>
         <v>0.75187969924812026</v>
       </c>
       <c r="F3" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$11),(1/1.33),((1/1.33)*'Nutritional status distribution'!F$11/(1-(1/1.33)*'Nutritional status distribution'!F$11))
-/ ('Nutritional status distribution'!F$11/(1-'Nutritional status distribution'!F$11)))</f>
+        <f t="shared" si="0"/>
         <v>0.75187969924812026</v>
       </c>
       <c r="G3" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!G$11),(1/1.33),((1/1.33)*'Nutritional status distribution'!G$11/(1-(1/1.33)*'Nutritional status distribution'!G$11))
-/ ('Nutritional status distribution'!G$11/(1-'Nutritional status distribution'!G$11)))</f>
+        <f t="shared" si="0"/>
         <v>0.75187969924812026</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="30" t="s">
         <v>258</v>
       </c>
@@ -42881,32 +42721,28 @@
         <v>1</v>
       </c>
       <c r="D5" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!D$10),(1/1.33),((1/1.33)*'Nutritional status distribution'!D$10/(1-(1/1.33)*'Nutritional status distribution'!D$10))
-/ ('Nutritional status distribution'!D$10/(1-'Nutritional status distribution'!D$10)))</f>
+        <f>1/1.33</f>
         <v>0.75187969924812026</v>
       </c>
       <c r="E5" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$10),(1/1.33),((1/1.33)*'Nutritional status distribution'!E$10/(1-(1/1.33)*'Nutritional status distribution'!E$10))
-/ ('Nutritional status distribution'!E$10/(1-'Nutritional status distribution'!E$10)))</f>
+        <f t="shared" ref="E5:G5" si="1">1/1.33</f>
         <v>0.75187969924812026</v>
       </c>
       <c r="F5" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$10),(1/1.33),((1/1.33)*'Nutritional status distribution'!F$10/(1-(1/1.33)*'Nutritional status distribution'!F$10))
-/ ('Nutritional status distribution'!F$10/(1-'Nutritional status distribution'!F$10)))</f>
+        <f t="shared" si="1"/>
         <v>0.75187969924812026</v>
       </c>
       <c r="G5" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!G$10),(1/1.33),((1/1.33)*'Nutritional status distribution'!G$10/(1-(1/1.33)*'Nutritional status distribution'!G$10))
-/ ('Nutritional status distribution'!G$10/(1-'Nutritional status distribution'!G$10)))</f>
+        <f t="shared" si="1"/>
         <v>0.75187969924812026</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="107" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="107" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="30"/>
       <c r="B8" s="42"/>
       <c r="C8" s="30" t="s">
@@ -42925,7 +42761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="30" t="s">
         <v>317</v>
       </c>
@@ -42938,27 +42774,23 @@
         <v>1</v>
       </c>
       <c r="D10" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!D$11),(1/1.54),((1/1.54)*'Nutritional status distribution'!D$11/(1-(1/1.54)*'Nutritional status distribution'!D$11))
-/ ('Nutritional status distribution'!D$11/(1-'Nutritional status distribution'!D$11)))</f>
+        <f>1/1.54</f>
         <v>0.64935064935064934</v>
       </c>
       <c r="E10" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$11),(1/1.54),((1/1.54)*'Nutritional status distribution'!E$11/(1-(1/1.54)*'Nutritional status distribution'!E$11))
-/ ('Nutritional status distribution'!E$11/(1-'Nutritional status distribution'!E$11)))</f>
+        <f t="shared" ref="E10:G10" si="2">1/1.54</f>
         <v>0.64935064935064934</v>
       </c>
       <c r="F10" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$11),(1/1.54),((1/1.54)*'Nutritional status distribution'!F$11/(1-(1/1.54)*'Nutritional status distribution'!F$11))
-/ ('Nutritional status distribution'!F$11/(1-'Nutritional status distribution'!F$11)))</f>
+        <f t="shared" si="2"/>
         <v>0.64935064935064934</v>
       </c>
       <c r="G10" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!G$11),(1/1.54),((1/1.54)*'Nutritional status distribution'!G$11/(1-(1/1.54)*'Nutritional status distribution'!G$11))
-/ ('Nutritional status distribution'!G$11/(1-'Nutritional status distribution'!G$11)))</f>
+        <f t="shared" si="2"/>
         <v>0.64935064935064934</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A11" s="30" t="s">
         <v>275</v>
       </c>
@@ -42977,32 +42809,28 @@
         <v>1</v>
       </c>
       <c r="D12" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!D$10),(1/1.54),((1/1.54)*'Nutritional status distribution'!D$10/(1-(1/1.54)*'Nutritional status distribution'!D$10))
-/ ('Nutritional status distribution'!D$10/(1-'Nutritional status distribution'!D$10)))</f>
+        <f>1/1.54</f>
         <v>0.64935064935064934</v>
       </c>
       <c r="E12" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$10),(1/1.54),((1/1.54)*'Nutritional status distribution'!E$10/(1-(1/1.54)*'Nutritional status distribution'!E$10))
-/ ('Nutritional status distribution'!E$10/(1-'Nutritional status distribution'!E$10)))</f>
+        <f t="shared" ref="E12:G12" si="3">1/1.54</f>
         <v>0.64935064935064934</v>
       </c>
       <c r="F12" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$10),(1/1.54),((1/1.54)*'Nutritional status distribution'!F$10/(1-(1/1.54)*'Nutritional status distribution'!F$10))
-/ ('Nutritional status distribution'!F$10/(1-'Nutritional status distribution'!F$10)))</f>
+        <f t="shared" si="3"/>
         <v>0.64935064935064934</v>
       </c>
       <c r="G12" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!G$10),(1/1.54),((1/1.54)*'Nutritional status distribution'!G$10/(1-(1/1.54)*'Nutritional status distribution'!G$10))
-/ ('Nutritional status distribution'!G$10/(1-'Nutritional status distribution'!G$10)))</f>
+        <f t="shared" si="3"/>
         <v>0.64935064935064934</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="107" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A14" s="107" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A15" s="30"/>
       <c r="B15" s="42"/>
       <c r="C15" s="30" t="s">
@@ -43021,7 +42849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="30" t="s">
         <v>276</v>
       </c>
@@ -43034,27 +42862,23 @@
         <v>1</v>
       </c>
       <c r="D17" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!D$11),(1/1.16),((1/1.16)*'Nutritional status distribution'!D$11/(1-(1/1.16)*'Nutritional status distribution'!D$11))
-/ ('Nutritional status distribution'!D$11/(1-'Nutritional status distribution'!D$11)))</f>
+        <f>1/1.16</f>
         <v>0.86206896551724144</v>
       </c>
       <c r="E17" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$11),(1/1.16),((1/1.16)*'Nutritional status distribution'!E$11/(1-(1/1.16)*'Nutritional status distribution'!E$11))
-/ ('Nutritional status distribution'!E$11/(1-'Nutritional status distribution'!E$11)))</f>
+        <f t="shared" ref="E17:G17" si="4">1/1.16</f>
         <v>0.86206896551724144</v>
       </c>
       <c r="F17" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$11),(1/1.16),((1/1.16)*'Nutritional status distribution'!F$11/(1-(1/1.16)*'Nutritional status distribution'!F$11))
-/ ('Nutritional status distribution'!F$11/(1-'Nutritional status distribution'!F$11)))</f>
+        <f t="shared" si="4"/>
         <v>0.86206896551724144</v>
       </c>
       <c r="G17" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!G$11),(1/1.16),((1/1.16)*'Nutritional status distribution'!G$11/(1-(1/1.16)*'Nutritional status distribution'!G$11))
-/ ('Nutritional status distribution'!G$11/(1-'Nutritional status distribution'!G$11)))</f>
+        <f t="shared" si="4"/>
         <v>0.86206896551724144</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A18" s="30" t="s">
         <v>277</v>
       </c>
@@ -43073,23 +42897,19 @@
         <v>1</v>
       </c>
       <c r="D19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!D$10),(1/1.16),((1/1.16)*'Nutritional status distribution'!D$10/(1-(1/1.16)*'Nutritional status distribution'!D$10))
-/ ('Nutritional status distribution'!D$10/(1-'Nutritional status distribution'!D$10)))</f>
+        <f>1/1.16</f>
         <v>0.86206896551724144</v>
       </c>
       <c r="E19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!E$10),(1/1.16),((1/1.16)*'Nutritional status distribution'!E$10/(1-(1/1.16)*'Nutritional status distribution'!E$10))
-/ ('Nutritional status distribution'!E$10/(1-'Nutritional status distribution'!E$10)))</f>
+        <f t="shared" ref="E19:G19" si="5">1/1.16</f>
         <v>0.86206896551724144</v>
       </c>
       <c r="F19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!F$10),(1/1.16),((1/1.16)*'Nutritional status distribution'!F$10/(1-(1/1.16)*'Nutritional status distribution'!F$10))
-/ ('Nutritional status distribution'!F$10/(1-'Nutritional status distribution'!F$10)))</f>
+        <f t="shared" si="5"/>
         <v>0.86206896551724144</v>
       </c>
       <c r="G19" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!G$10),(1/1.16),((1/1.16)*'Nutritional status distribution'!G$10/(1-(1/1.16)*'Nutritional status distribution'!G$10))
-/ ('Nutritional status distribution'!G$10/(1-'Nutritional status distribution'!G$10)))</f>
+        <f t="shared" si="5"/>
         <v>0.86206896551724144</v>
       </c>
     </row>
@@ -43107,20 +42927,20 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:H163"/>
-  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53" style="40" customWidth="1"/>
-    <col min="2" max="2" width="30.5546875" style="40" customWidth="1"/>
-    <col min="3" max="3" width="24.77734375" style="40" customWidth="1"/>
+    <col min="2" max="2" width="30.54296875" style="40" customWidth="1"/>
+    <col min="3" max="3" width="24.81640625" style="40" customWidth="1"/>
     <col min="4" max="4" width="15" style="28" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="28" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" style="28" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" style="28"/>
-    <col min="8" max="8" width="17.5546875" style="28" customWidth="1"/>
-    <col min="9" max="16384" width="12.77734375" style="28"/>
+    <col min="5" max="5" width="13.6328125" style="28" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" style="28" customWidth="1"/>
+    <col min="7" max="7" width="12.81640625" style="28"/>
+    <col min="8" max="8" width="17.54296875" style="28" customWidth="1"/>
+    <col min="9" max="16384" width="12.81640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>69</v>
       </c>
@@ -44288,7 +44108,7 @@
         <v>262</v>
       </c>
       <c r="D53" s="105">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="E53" s="105">
         <v>0</v>
@@ -44303,14 +44123,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" s="108" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" s="108" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A55" s="111" t="s">
         <v>269</v>
       </c>
       <c r="B55" s="112"/>
       <c r="C55" s="112"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A56" s="30" t="s">
         <v>69</v>
       </c>
@@ -45544,7 +45364,7 @@
         <v>262</v>
       </c>
       <c r="D108" s="105">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E108" s="105">
         <v>0</v>
@@ -45559,14 +45379,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" s="108" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" s="108" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A110" s="111" t="s">
         <v>270</v>
       </c>
       <c r="B110" s="112"/>
       <c r="C110" s="112"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A111" s="30" t="s">
         <v>69</v>
       </c>
@@ -46805,7 +46625,7 @@
         <v>262</v>
       </c>
       <c r="D163" s="105">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="E163" s="105">
         <v>0</v>
@@ -46837,16 +46657,16 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" style="28" customWidth="1"/>
-    <col min="2" max="2" width="27.44140625" style="28" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" style="28" customWidth="1"/>
-    <col min="4" max="7" width="17.21875" style="28" customWidth="1"/>
-    <col min="8" max="16384" width="12.77734375" style="28"/>
+    <col min="2" max="2" width="27.453125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="23.6328125" style="28" customWidth="1"/>
+    <col min="4" max="7" width="17.1796875" style="28" customWidth="1"/>
+    <col min="8" max="16384" width="12.81640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="42" t="s">
         <v>69</v>
       </c>
@@ -46994,12 +46814,12 @@
       </c>
       <c r="H7" s="32"/>
     </row>
-    <row r="9" spans="1:8" s="107" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="107" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="42" t="s">
         <v>69</v>
       </c>
@@ -47160,12 +46980,12 @@
         <v>0.53100000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="107" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A18" s="107" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" s="42" t="s">
         <v>69</v>
       </c>
@@ -47342,17 +47162,17 @@
     <tabColor rgb="FF007600"/>
   </sheetPr>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" customWidth="1"/>
-    <col min="2" max="2" width="31.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.08984375" customWidth="1"/>
+    <col min="2" max="2" width="31.36328125" customWidth="1"/>
     <col min="3" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="str">
         <f>"Percentage of deaths in baseline year ("&amp;start_year&amp;") attributable to cause"</f>
-        <v>Percentage of deaths in baseline year (2021) attributable to cause</v>
+        <v>Percentage of deaths in baseline year (2024) attributable to cause</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
@@ -47360,7 +47180,7 @@
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
     </row>
-    <row r="2" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>204</v>
       </c>
@@ -47443,7 +47263,7 @@
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>31</v>
       </c>
@@ -47577,7 +47397,7 @@
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -47671,16 +47491,16 @@
     <tabColor rgb="FF007600"/>
   </sheetPr>
   <dimension ref="A1:O17"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" customWidth="1"/>
+    <col min="1" max="1" width="31.453125" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="str">
         <f>"Percentage of population in each category in baseline year ("&amp;start_year&amp;")"</f>
-        <v>Percentage of population in each category in baseline year (2021)</v>
+        <v>Percentage of population in each category in baseline year (2024)</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>6</v>
@@ -48025,16 +47845,16 @@
     <tabColor rgb="FF007600"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.88671875" customWidth="1"/>
-    <col min="2" max="7" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="28.90625" customWidth="1"/>
+    <col min="2" max="7" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="str">
         <f>"Percentage of children in each category in baseline year ("&amp;start_year&amp;")"</f>
-        <v>Percentage of children in each category in baseline year (2021)</v>
+        <v>Percentage of children in each category in baseline year (2024)</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>6</v>
@@ -48064,9 +47884,15 @@
       </c>
       <c r="C2" s="53"/>
       <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
+      <c r="E2" s="61">
+        <v>0</v>
+      </c>
+      <c r="F2" s="61">
+        <v>0</v>
+      </c>
+      <c r="G2" s="61">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="32" t="s">
@@ -48074,9 +47900,15 @@
       </c>
       <c r="C3" s="61"/>
       <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
+      <c r="E3" s="61">
+        <v>0</v>
+      </c>
+      <c r="F3" s="61">
+        <v>0</v>
+      </c>
+      <c r="G3" s="61">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="32" t="s">
@@ -48086,7 +47918,9 @@
       <c r="D4" s="61"/>
       <c r="E4" s="61"/>
       <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
+      <c r="G4" s="61">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="s">
@@ -48126,13 +47960,13 @@
     <tabColor rgb="FF007600"/>
   </sheetPr>
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>133</v>
       </c>
@@ -48326,13 +48160,13 @@
     <tabColor rgb="FF007600"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" customWidth="1"/>
+    <col min="1" max="1" width="36.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>326</v>
       </c>
@@ -48401,15 +48235,15 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" style="28" customWidth="1"/>
-    <col min="2" max="2" width="19.109375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" style="28" customWidth="1"/>
-    <col min="4" max="16384" width="11.44140625" style="28"/>
+    <col min="2" max="2" width="19.08984375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" style="28" customWidth="1"/>
+    <col min="4" max="16384" width="11.453125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
         <v>173</v>
       </c>
@@ -48426,7 +48260,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="37" t="s">
         <v>168</v>
       </c>
@@ -48496,7 +48330,7 @@
       <c r="D7" s="33"/>
       <c r="E7" s="64"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="37" t="s">
         <v>193</v>
       </c>
@@ -48566,7 +48400,7 @@
       <c r="D14" s="33"/>
       <c r="E14" s="64"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="37" t="s">
         <v>194</v>
       </c>
@@ -48655,15 +48489,15 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" customWidth="1"/>
+    <col min="4" max="4" width="12.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="47" t="s">
         <v>159</v>
       </c>
@@ -48677,7 +48511,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="48" t="s">
         <v>69</v>
       </c>
@@ -48689,7 +48523,7 @@
       </c>
       <c r="D2" s="64"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A3" s="48" t="s">
         <v>180</v>
       </c>

--- a/inputs/en/template_input.xlsx
+++ b/inputs/en/template_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\Nutrition\inputs\en\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\LiST Optima bridge\App\ModData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2A8914-34FE-4044-A414-03DC7E849494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E67A13A-5BCC-4675-83A8-1B50EF48FA73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline year population inputs" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Causes of death" sheetId="4" r:id="rId3"/>
     <sheet name="Nutritional status distribution" sheetId="5" r:id="rId4"/>
     <sheet name="Breastfeeding distribution" sheetId="50" r:id="rId5"/>
-    <sheet name="Time trends" sheetId="51" state="hidden" r:id="rId6"/>
+    <sheet name="Time trends" sheetId="51" r:id="rId6"/>
     <sheet name="Economic loss" sheetId="74" r:id="rId7"/>
     <sheet name="IYCF packages" sheetId="55" r:id="rId8"/>
     <sheet name="Treatment of SAM" sheetId="60" r:id="rId9"/>
@@ -1130,12 +1130,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{F85A0966-F382-4AC3-AEB1-A32E1690E667}">
+OR = 0.89 for stunting [Panjwani et al. 2017 J Nutr</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{188B7364-7947-4FE2-9F55-D5489196772E}">
       <text>
         <r>
           <rPr>
@@ -1155,8 +1154,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
+OR = 0.89 for stunting [Panjwani et al. 2017 J Nutr</t>
         </r>
       </text>
     </comment>
@@ -1407,56 +1405,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="1" shapeId="0" xr:uid="{CDFA4A87-08F8-4FAE-9A20-B20AA4E79B7A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F29" authorId="1" shapeId="0" xr:uid="{076B3E7F-0616-462A-8D35-79DBDE58463A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="B30" authorId="0" shapeId="0" xr:uid="{0EB42B00-FE3E-4EC5-BFC7-BDF1DBAB0415}">
       <text>
         <r>
@@ -1649,56 +1597,6 @@
           </rPr>
           <t xml:space="preserve">
 This assumes PPCF is delivered with education to the fraction below the poverty line</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E52" authorId="1" shapeId="0" xr:uid="{3AAE6D59-06E8-4F12-9949-24D16F55347E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F52" authorId="1" shapeId="0" xr:uid="{949D0873-1B10-4DE9-86B8-996E56ACF556}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
         </r>
       </text>
     </comment>
@@ -2706,8 +2604,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -3721,15 +3618,15 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{92C59C49-236F-4A88-BC2E-8E169B417731}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
+    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{5390859E-08D5-4789-B28E-CAFBB78FDAC4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:</t>
         </r>
@@ -3738,11 +3635,10 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Peña‐Rosas et al 2019, anemia RR 0.72 (0.54-0.97)
-If no data for anaemia prev. the use RR otherwise convert RR to OR using prev.</t>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -3770,15 +3666,15 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{6FDC07E4-2811-4181-9797-978156C28DDB}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{5FC15E95-60C4-42A6-9A1C-847300FEA7A0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:</t>
         </r>
@@ -3787,11 +3683,10 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Larson et al 2021, RR 0.80 (0.70-0.92)
-If no data for anaemia prev. the use RR otherwise convert RR to OR using prev.</t>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -3839,8 +3734,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -4677,6 +4571,54 @@
         </r>
       </text>
     </comment>
+    <comment ref="E42" authorId="0" shapeId="0" xr:uid="{2D128182-DACE-428A-9973-2C830923549B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{0C3E6647-06D5-44EF-8FE5-59B1329FE276}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="C49" authorId="0" shapeId="0" xr:uid="{0F186CC8-6BE9-43A0-8E16-F53C8B65D3DA}">
       <text>
         <r>
@@ -4697,8 +4639,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -5832,6 +5773,54 @@
           </rPr>
           <t xml:space="preserve">
 Wessells et al 2022, iron deficiency anemia), PR 0.36 (0.30-0.44) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E65" authorId="0" shapeId="0" xr:uid="{4B855F12-6C36-4B60-815A-EB7307931232}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E67" authorId="0" shapeId="0" xr:uid="{EEA06EE3-AFCE-460D-A7E1-AEE9D27AECE3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -12273,12 +12262,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{695349C9-DC3A-4988-B509-C748CE291342}">
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{4763D3C6-2461-434E-A9CE-8176C3AEEEC0}">
       <text>
         <r>
           <rPr>
@@ -12298,12 +12286,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{D5BD5909-BA19-4A55-BCEF-C90FE7E12CF1}">
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{D2793965-226C-4498-9C0C-8763958E0A0E}">
       <text>
         <r>
           <rPr>
@@ -12323,12 +12310,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{7F108112-2A44-49C5-ACE9-3731A187C628}">
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{70344548-3959-4495-A5BD-FC2105C0CA4C}">
       <text>
         <r>
           <rPr>
@@ -12348,8 +12334,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -12573,7 +12558,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{12A87525-2B0D-4F70-84D5-4E25DDC554D0}">
+    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{3F0FEEEB-825A-4110-B4FF-9A53AA391466}">
       <text>
         <r>
           <rPr>
@@ -12593,12 +12578,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{DCB559FF-6A2C-48DA-9C20-C70B099FF45D}">
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{C9172DAA-EA75-4BC3-8012-7E92325DB83B}">
       <text>
         <r>
           <rPr>
@@ -12618,12 +12602,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{050856FA-F87E-4097-B0CD-476075F203E6}">
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{D43067D2-2309-4597-85D8-BAFDF8E5791E}">
       <text>
         <r>
           <rPr>
@@ -12643,12 +12626,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{138FF691-DDF2-4B53-A0A8-D4C96E1CA2D6}">
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{F39039B9-7D81-47CF-B3A8-351139B676C9}">
       <text>
         <r>
           <rPr>
@@ -12668,8 +12650,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -12793,7 +12774,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D111" authorId="0" shapeId="0" xr:uid="{E2E07AF9-EA98-4B4C-A78C-C829E540CB47}">
+    <comment ref="D111" authorId="0" shapeId="0" xr:uid="{8646C2BC-114A-44B6-910E-A63844A6CAA3}">
       <text>
         <r>
           <rPr>
@@ -12813,12 +12794,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D112" authorId="0" shapeId="0" xr:uid="{A289D11B-EF43-4AB5-B328-20A4EC971B96}">
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D112" authorId="0" shapeId="0" xr:uid="{F27C32B5-B3C2-41D1-973D-A09E1B24FC8F}">
       <text>
         <r>
           <rPr>
@@ -12838,12 +12818,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E114" authorId="0" shapeId="0" xr:uid="{629118D8-06DA-4C5F-A790-8C0AAC5F189C}">
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E114" authorId="0" shapeId="0" xr:uid="{C40AF175-9B94-403A-96D8-12E3FCC112CA}">
       <text>
         <r>
           <rPr>
@@ -12863,12 +12842,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E115" authorId="0" shapeId="0" xr:uid="{B172F927-A597-4694-9034-537B5C5C8316}">
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E115" authorId="0" shapeId="0" xr:uid="{4799B878-EEA1-4273-B476-A4A0B739A2A7}">
       <text>
         <r>
           <rPr>
@@ -12888,8 +12866,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -13042,7 +13019,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="341">
   <si>
     <t>year</t>
   </si>
@@ -24922,7 +24899,7 @@
         <v>171</v>
       </c>
       <c r="D5" s="103">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="E5" s="103">
         <v>1</v>
@@ -24943,7 +24920,7 @@
         <v>170</v>
       </c>
       <c r="D6" s="103">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="E6" s="103">
         <v>1</v>
@@ -24990,7 +24967,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="103">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="F8" s="103">
         <v>1</v>
@@ -25011,7 +24988,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="103">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="F9" s="103">
         <v>1</v>
@@ -26042,7 +26019,7 @@
         <v>171</v>
       </c>
       <c r="D58" s="103">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="E58" s="103">
         <f t="shared" ref="E58:H58" si="3">IF(E5=1,1,E5*0.9)</f>
@@ -26067,7 +26044,7 @@
         <v>170</v>
       </c>
       <c r="D59" s="103">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="E59" s="103">
         <f t="shared" ref="E59:H59" si="4">IF(E6=1,1,E6*0.9)</f>
@@ -26124,7 +26101,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="103">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="F61" s="103">
         <f t="shared" si="6"/>
@@ -26149,7 +26126,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="103">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="F62" s="103">
         <f t="shared" si="7"/>
@@ -27379,7 +27356,7 @@
         <v>171</v>
       </c>
       <c r="D111" s="103">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="E111" s="103">
         <f t="shared" ref="E111:H111" si="51">IF(E5=1,1,E5*1.05)</f>
@@ -27404,7 +27381,7 @@
         <v>170</v>
       </c>
       <c r="D112" s="103">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="E112" s="103">
         <f t="shared" ref="E112:H112" si="52">IF(E6=1,1,E6*1.05)</f>
@@ -27461,7 +27438,7 @@
         <v>1</v>
       </c>
       <c r="E114" s="103">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="F114" s="103">
         <f t="shared" si="54"/>
@@ -27486,7 +27463,7 @@
         <v>1</v>
       </c>
       <c r="E115" s="103">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="F115" s="103">
         <f t="shared" si="55"/>
@@ -28588,7 +28565,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="riIqDHxQDNIc95k8WEEMlpv2yK5yRhEl3GZr9d21PG7QnhNwxgtjaWmZN+9widROwyhXiwQ4XZiTM/cZ2Cl95g==" saltValue="b1Xx0XPjIcbtdUQJGdoNkQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kNott2FY10++7LpzvuSEUUgvKblMKWlWyTJLQ7V3mUE+D/qQXgkJjdadeNqQ4e0dbATNIZiaZUbYZr3uwCKttQ==" saltValue="MboHEiRAGE0wfo213ZYZVw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="45">
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B2:B4"/>
@@ -29852,7 +29829,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OEa5xq8Dht0iRzVx1fQ1EOJdDm09uSIzQRujIfp/VJ8GNGNECqE8Uut2U6j1omy5Y9ajcKxMUHwzsTWrCb+nAw==" saltValue="Poj67khbkyqhF7WVYd6CsA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="a0aX2VfGYRJWLRZcCd5z7lhlUmGJO/EzN4cg0Snhkl/IJQUK1zIL/9W0H+8Dtzn8tPzB4mSWxW65xqA1yiTgOA==" saltValue="o1GVWZzk0+60bY16Wxar5Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
@@ -37989,7 +37966,7 @@
       <c r="I328" s="93"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="rzjjr+eUY+zLxtgvRuigrXBCYk8ZjZeKkvy/Wu7lqFGhk7GKsrVngS9i2Jt2gxX9Fn0pC2b9tyB7+BxRGGivEA==" saltValue="vsQDJsypwJz22iUc18xJ6w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1gEiboypgN1VYdmLYuHEsviiXDH91vsC32xKqzOEbclcsh2pOXs0vX071vry3NRJsC+T2/BNfpXbXWW7dldjVQ==" saltValue="XZihSWmo245BlR0GYalydw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
@@ -38100,10 +38077,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="105">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="F6" s="105">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="G6" s="105">
         <v>1</v>
@@ -38421,10 +38398,12 @@
         <v>1</v>
       </c>
       <c r="E29" s="105">
-        <v>0.44</v>
+        <f>E6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="F29" s="105">
-        <v>0.44</v>
+        <f>F6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="G29" s="105">
         <f t="shared" si="2"/>
@@ -38790,10 +38769,12 @@
         <v>1</v>
       </c>
       <c r="E52" s="105">
-        <v>0.92</v>
+        <f>E6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="F52" s="105">
-        <v>0.92</v>
+        <f>F6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="G52" s="105">
         <f t="shared" si="10"/>
@@ -39055,7 +39036,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="uxH3qxfpHv3MxEVFpMF959vuuHVMbjUY0YDJlIXIgHOAA25UaRTm/IIjRx7RzEUfWaTP3eP7cZpYIm+m6J8PbA==" saltValue="wm1A0TwV/0DyOIoqtNvfsQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Z5W0iLQonUXgebQ0oBIAJiknKvZHIMnPuF1vh21+BfR+VnJC7YVzBoFQiTm+hEbHNMOFIRa563Ft7+Jm2vvcKg==" saltValue="MgosxU+mdCbdebb7wBaTKg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
@@ -39879,7 +39860,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="lEvf/7Nn9p0s2t120JFgJzNA1BIMAO9h8EmTziKGX5ZA7K3Y+rQ77oXfzNqKwsdbYQwCY96ujjsdxuDmqt1luA==" saltValue="pZcegXbvW/wKpwHEQP8pcw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="LnjPs+tiryCjGlxIcCoc9VYZVK7anRAVHCvKud83EfjtgKW0vUQr2FSI3nvdju1neMs4gxoXRQGAXnwHTy0eGQ==" saltValue="uusuOaSrLiI1eiqZNmtU+w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
@@ -39956,7 +39937,7 @@
         <v>144</v>
       </c>
       <c r="C3" s="105">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="D3" s="105">
         <v>0.53</v>
@@ -40467,16 +40448,16 @@
         <v>1</v>
       </c>
       <c r="L14" s="105">
-        <v>0.51</v>
+        <v>1</v>
       </c>
       <c r="M14" s="105">
-        <v>0.51</v>
+        <v>1</v>
       </c>
       <c r="N14" s="105">
-        <v>0.51</v>
+        <v>1</v>
       </c>
       <c r="O14" s="105">
-        <v>0.51</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -40584,48 +40565,37 @@
         <v>1</v>
       </c>
       <c r="E19" s="105">
-        <f>0.72</f>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F19" s="105">
-        <f t="shared" ref="F19:O19" si="0">0.72</f>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G19" s="105">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H19" s="105">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I19" s="105">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J19" s="105">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K19" s="105">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L19" s="105">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M19" s="105">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N19" s="105">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O19" s="105">
-        <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -40683,37 +40653,37 @@
         <v>1</v>
       </c>
       <c r="E21" s="105">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F21" s="105">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G21" s="105">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H21" s="105">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I21" s="105">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J21" s="105">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K21" s="105">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L21" s="105">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M21" s="105">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N21" s="105">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O21" s="105">
-        <v>0.8</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -40774,53 +40744,53 @@
         <v>144</v>
       </c>
       <c r="C26" s="105">
-        <v>0.4</v>
+        <v>0.87</v>
       </c>
       <c r="D26" s="105">
         <v>0.4</v>
       </c>
       <c r="E26" s="105">
-        <f t="shared" ref="E26:O26" si="1">IF(E3=1,1,E3*0.9)</f>
+        <f t="shared" ref="E26:O26" si="0">IF(E3=1,1,E3*0.9)</f>
         <v>1</v>
       </c>
       <c r="F26" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G26" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H26" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I26" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J26" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="K26" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L26" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="M26" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N26" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="O26" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -40829,23 +40799,23 @@
         <v>183</v>
       </c>
       <c r="C27" s="105">
-        <f t="shared" ref="C27:O27" si="2">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:O27" si="1">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E27" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F27" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G27" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H27" s="105">
@@ -40861,19 +40831,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M27" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N27" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="O27" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -40882,23 +40852,23 @@
         <v>201</v>
       </c>
       <c r="C28" s="105">
-        <f t="shared" ref="C28:O28" si="3">IF(C5=1,1,C5*0.9)</f>
+        <f t="shared" ref="C28:O28" si="2">IF(C5=1,1,C5*0.9)</f>
         <v>1</v>
       </c>
       <c r="D28" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E28" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F28" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G28" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H28" s="105">
@@ -40914,19 +40884,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M28" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N28" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O28" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -40935,23 +40905,23 @@
         <v>184</v>
       </c>
       <c r="C29" s="105">
-        <f t="shared" ref="C29:O29" si="4">IF(C6=1,1,C6*0.9)</f>
+        <f t="shared" ref="C29:O29" si="3">IF(C6=1,1,C6*0.9)</f>
         <v>1</v>
       </c>
       <c r="D29" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E29" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F29" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G29" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H29" s="105">
@@ -40967,19 +40937,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M29" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N29" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O29" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -40988,23 +40958,23 @@
         <v>185</v>
       </c>
       <c r="C30" s="105">
-        <f t="shared" ref="C30:O30" si="5">IF(C7=1,1,C7*0.9)</f>
+        <f t="shared" ref="C30:O30" si="4">IF(C7=1,1,C7*0.9)</f>
         <v>1</v>
       </c>
       <c r="D30" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E30" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="F30" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G30" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H30" s="105">
@@ -41020,19 +40990,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="M30" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="N30" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O30" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -41041,39 +41011,39 @@
         <v>182</v>
       </c>
       <c r="C31" s="105">
-        <f t="shared" ref="C31:K31" si="6">IF(C8=1,1,C8*0.9)</f>
+        <f t="shared" ref="C31:K31" si="5">IF(C8=1,1,C8*0.9)</f>
         <v>1</v>
       </c>
       <c r="D31" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E31" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F31" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G31" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H31" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="I31" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="J31" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K31" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="L31" s="105">
@@ -41094,39 +41064,39 @@
         <v>202</v>
       </c>
       <c r="C32" s="105">
-        <f t="shared" ref="C32:K32" si="7">IF(C9=1,1,C9*0.9)</f>
+        <f t="shared" ref="C32:K32" si="6">IF(C9=1,1,C9*0.9)</f>
         <v>1</v>
       </c>
       <c r="D32" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E32" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F32" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G32" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H32" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I32" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J32" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K32" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L32" s="105">
@@ -41147,39 +41117,39 @@
         <v>57</v>
       </c>
       <c r="C33" s="105">
-        <f t="shared" ref="C33:K33" si="8">IF(C10=1,1,C10*0.9)</f>
+        <f t="shared" ref="C33:K33" si="7">IF(C10=1,1,C10*0.9)</f>
         <v>1</v>
       </c>
       <c r="D33" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E33" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F33" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G33" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H33" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I33" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J33" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K33" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L33" s="105">
@@ -41200,11 +41170,11 @@
         <v>131</v>
       </c>
       <c r="C34" s="105">
-        <f t="shared" ref="C34:O34" si="9">IF(C11=1,1,C11*0.9)</f>
+        <f t="shared" ref="C34:O34" si="8">IF(C11=1,1,C11*0.9)</f>
         <v>1</v>
       </c>
       <c r="D34" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E34" s="105">
@@ -41217,35 +41187,35 @@
         <v>1</v>
       </c>
       <c r="H34" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I34" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J34" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K34" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L34" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="M34" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N34" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O34" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -41298,11 +41268,11 @@
         <v>132</v>
       </c>
       <c r="C36" s="105">
-        <f t="shared" ref="C36:O36" si="10">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:O36" si="9">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="E36" s="105">
@@ -41315,35 +41285,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="I36" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J36" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K36" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="L36" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="M36" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="N36" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="O36" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -41352,56 +41322,52 @@
         <v>59</v>
       </c>
       <c r="C37" s="105">
-        <f t="shared" ref="C37:K37" si="11">IF(C14=1,1,C14*0.9)</f>
+        <f t="shared" ref="C37:K37" si="10">IF(C14=1,1,C14*0.9)</f>
         <v>1</v>
       </c>
       <c r="D37" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E37" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F37" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G37" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="H37" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="I37" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J37" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K37" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="L37" s="105">
-        <f>L32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="M37" s="105">
-        <f t="shared" ref="M37:O37" si="12">M32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="N37" s="105">
-        <f t="shared" si="12"/>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="O37" s="105">
-        <f t="shared" si="12"/>
-        <v>0.38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -41409,11 +41375,11 @@
         <v>337</v>
       </c>
       <c r="C38" s="105">
-        <f t="shared" ref="C38:O38" si="13">IF(C15=1,1,C15*0.9)</f>
+        <f t="shared" ref="C38:O38" si="11">IF(C15=1,1,C15*0.9)</f>
         <v>1</v>
       </c>
       <c r="D38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="E38" s="105">
@@ -41423,39 +41389,39 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="I38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="J38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="K38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="L38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="M38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="N38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -41470,55 +41436,55 @@
         <v>63</v>
       </c>
       <c r="C41" s="105">
-        <f t="shared" ref="C41:O41" si="14">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:O41" si="12">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E41" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="F41" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G41" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H41" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="I41" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J41" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K41" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="L41" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="M41" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="N41" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="O41" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -41527,45 +41493,45 @@
         <v>64</v>
       </c>
       <c r="C42" s="105">
-        <f t="shared" ref="C42:D44" si="15">IF(C19=1,1,C19*0.9)</f>
+        <f t="shared" ref="C42:D44" si="13">IF(C19=1,1,C19*0.9)</f>
         <v>1</v>
       </c>
       <c r="D42" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E42" s="105">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F42" s="105">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G42" s="105">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H42" s="105">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I42" s="105">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J42" s="105">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K42" s="105">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L42" s="105">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M42" s="105">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N42" s="105">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O42" s="105">
-        <v>0.54</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -41573,55 +41539,55 @@
         <v>62</v>
       </c>
       <c r="C43" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D43" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E43" s="105">
-        <f t="shared" ref="E43:O43" si="16">IF(E20=1,1,E20*0.9)</f>
+        <f t="shared" ref="E43:O43" si="14">IF(E20=1,1,E20*0.9)</f>
         <v>1</v>
       </c>
       <c r="F43" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="G43" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="H43" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="I43" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="J43" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="K43" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="L43" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M43" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N43" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O43" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -41630,45 +41596,45 @@
         <v>47</v>
       </c>
       <c r="C44" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D44" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E44" s="105">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F44" s="105">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G44" s="105">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H44" s="105">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I44" s="105">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J44" s="105">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K44" s="105">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L44" s="105">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M44" s="105">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N44" s="105">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O44" s="105">
-        <v>0.7</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:15" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -41729,53 +41695,53 @@
         <v>144</v>
       </c>
       <c r="C49" s="105">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="D49" s="105">
         <v>0.7</v>
       </c>
       <c r="E49" s="105">
-        <f t="shared" ref="E49:O49" si="17">IF(E3=1,1,E3*1.05)</f>
+        <f t="shared" ref="E49:O49" si="15">IF(E3=1,1,E3*1.05)</f>
         <v>1</v>
       </c>
       <c r="F49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="M49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="N49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="O49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -41784,23 +41750,23 @@
         <v>183</v>
       </c>
       <c r="C50" s="105">
-        <f t="shared" ref="C50:O50" si="18">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:O50" si="16">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="F50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="G50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="H50" s="105">
@@ -41816,19 +41782,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="M50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="N50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="O50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
     </row>
@@ -41837,23 +41803,23 @@
         <v>201</v>
       </c>
       <c r="C51" s="105">
-        <f t="shared" ref="C51:O51" si="19">IF(C5=1,1,C5*1.05)</f>
+        <f t="shared" ref="C51:O51" si="17">IF(C5=1,1,C5*1.05)</f>
         <v>1</v>
       </c>
       <c r="D51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="E51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="F51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H51" s="105">
@@ -41869,19 +41835,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -41890,23 +41856,23 @@
         <v>184</v>
       </c>
       <c r="C52" s="105">
-        <f t="shared" ref="C52:O52" si="20">IF(C6=1,1,C6*1.05)</f>
+        <f t="shared" ref="C52:O52" si="18">IF(C6=1,1,C6*1.05)</f>
         <v>1</v>
       </c>
       <c r="D52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="F52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H52" s="105">
@@ -41922,19 +41888,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="M52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="N52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="O52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
@@ -41943,23 +41909,23 @@
         <v>185</v>
       </c>
       <c r="C53" s="105">
-        <f t="shared" ref="C53:O53" si="21">IF(C7=1,1,C7*1.05)</f>
+        <f t="shared" ref="C53:O53" si="19">IF(C7=1,1,C7*1.05)</f>
         <v>1</v>
       </c>
       <c r="D53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H53" s="105">
@@ -41975,19 +41941,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="N53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="O53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
@@ -41996,39 +41962,39 @@
         <v>182</v>
       </c>
       <c r="C54" s="105">
-        <f t="shared" ref="C54:K54" si="22">IF(C8=1,1,C8*1.05)</f>
+        <f t="shared" ref="C54:K54" si="20">IF(C8=1,1,C8*1.05)</f>
         <v>1</v>
       </c>
       <c r="D54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="I54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="J54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="K54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="L54" s="105">
@@ -42049,39 +42015,39 @@
         <v>202</v>
       </c>
       <c r="C55" s="105">
-        <f t="shared" ref="C55:K55" si="23">IF(C9=1,1,C9*1.05)</f>
+        <f t="shared" ref="C55:K55" si="21">IF(C9=1,1,C9*1.05)</f>
         <v>1</v>
       </c>
       <c r="D55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="F55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="G55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="H55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="I55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="J55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="K55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="L55" s="105">
@@ -42102,39 +42068,39 @@
         <v>57</v>
       </c>
       <c r="C56" s="105">
-        <f t="shared" ref="C56:K56" si="24">IF(C10=1,1,C10*1.05)</f>
+        <f t="shared" ref="C56:K56" si="22">IF(C10=1,1,C10*1.05)</f>
         <v>1</v>
       </c>
       <c r="D56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="E56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="F56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="G56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="H56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="I56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="J56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="K56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="L56" s="105">
@@ -42155,11 +42121,11 @@
         <v>131</v>
       </c>
       <c r="C57" s="105">
-        <f t="shared" ref="C57:O57" si="25">IF(C11=1,1,C11*1.05)</f>
+        <f t="shared" ref="C57:O57" si="23">IF(C11=1,1,C11*1.05)</f>
         <v>1</v>
       </c>
       <c r="D57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="E57" s="105">
@@ -42169,39 +42135,39 @@
         <v>0.77</v>
       </c>
       <c r="G57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="H57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="I57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="J57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="K57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="L57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="M57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="N57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="O57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
     </row>
@@ -42254,11 +42220,11 @@
         <v>132</v>
       </c>
       <c r="C59" s="105">
-        <f t="shared" ref="C59:O59" si="26">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:O59" si="24">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="E59" s="105">
@@ -42271,35 +42237,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="I59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="J59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="K59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="L59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="M59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="N59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="O59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
     </row>
@@ -42308,56 +42274,52 @@
         <v>59</v>
       </c>
       <c r="C60" s="105">
-        <f t="shared" ref="C60:K60" si="27">IF(C14=1,1,C14*1.05)</f>
+        <f t="shared" ref="C60:K60" si="25">IF(C14=1,1,C14*1.05)</f>
         <v>1</v>
       </c>
       <c r="D60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="E60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="F60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="G60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="H60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="I60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="J60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="K60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="L60" s="105">
-        <f>L54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M60" s="105">
-        <f t="shared" ref="M60:O60" si="28">M54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N60" s="105">
-        <f t="shared" si="28"/>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O60" s="105">
-        <f t="shared" si="28"/>
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -42365,11 +42327,11 @@
         <v>337</v>
       </c>
       <c r="C61" s="105">
-        <f t="shared" ref="C61:O61" si="29">IF(C15=1,1,C15*1.05)</f>
+        <f t="shared" ref="C61:O61" si="26">IF(C15=1,1,C15*1.05)</f>
         <v>1</v>
       </c>
       <c r="D61" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="E61" s="105">
@@ -42379,39 +42341,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="H61" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="I61" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="J61" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="K61" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="L61" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="M61" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="N61" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="O61" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
     </row>
@@ -42426,55 +42388,55 @@
         <v>63</v>
       </c>
       <c r="C64" s="105">
-        <f t="shared" ref="C64:O64" si="30">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:O64" si="27">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="E64" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="F64" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G64" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="H64" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="I64" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="J64" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="K64" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="L64" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="M64" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="N64" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="O64" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
     </row>
@@ -42483,45 +42445,45 @@
         <v>64</v>
       </c>
       <c r="C65" s="105">
-        <f t="shared" ref="C65:D67" si="31">IF(C19=1,1,C19*1.05)</f>
+        <f t="shared" ref="C65:D67" si="28">IF(C19=1,1,C19*1.05)</f>
         <v>1</v>
       </c>
       <c r="D65" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="E65" s="105">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F65" s="105">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G65" s="105">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H65" s="105">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I65" s="105">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J65" s="105">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K65" s="105">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L65" s="105">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M65" s="105">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N65" s="105">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O65" s="105">
-        <v>0.97</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.25">
@@ -42529,55 +42491,55 @@
         <v>62</v>
       </c>
       <c r="C66" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="D66" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="E66" s="105">
-        <f t="shared" ref="E66:O66" si="32">IF(E20=1,1,E20*1.05)</f>
+        <f t="shared" ref="E66:O66" si="29">IF(E20=1,1,E20*1.05)</f>
         <v>1</v>
       </c>
       <c r="F66" s="105">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G66" s="105">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H66" s="105">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="I66" s="105">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="J66" s="105">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="K66" s="105">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="L66" s="105">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="M66" s="105">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="N66" s="105">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="O66" s="105">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
     </row>
@@ -42586,51 +42548,49 @@
         <v>47</v>
       </c>
       <c r="C67" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="D67" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="E67" s="105">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F67" s="105">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G67" s="105">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H67" s="105">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I67" s="105">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J67" s="105">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K67" s="105">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L67" s="105">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M67" s="105">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N67" s="105">
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O67" s="105">
-        <f>IF(ISBLANK('Nutritional status distribution'!O$14),0.92,(0.92*'Nutritional status distribution'!O$14/(1-0.92*'Nutritional status distribution'!O$14))
-/ ('Nutritional status distribution'!O$14/(1-'Nutritional status distribution'!O$14)))</f>
-        <v>0.92</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="QTNrTNcX0LQnvnw9OcFIuF8iiKsb7nBsadUCrO1kCxqB4CvEkER3v8YCwNBmR8txM/1IAuOQ/zC/vA8HLWjOhA==" saltValue="f5+QlQPEjGE24L/HhPaCMQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Z+I5w7Zv8b/t9kdTHtfTBlYoSm79UCEUpz3ShmnqEGsFIWvoyqli8qZ/O3UtxFRtNUOisgC6wk7M7CD5q+6g2w==" saltValue="qncMJDCOHin5ZX0oUaABDg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
@@ -42914,7 +42874,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ZIjv20oIFeX8hEAP3JXu7+FjYQdIWvRgXIH4IkxRsMm14MAW5JMg2x9QOPJ7rc+IAMFEDvKO0XCydnz4Atw3VA==" saltValue="eIHIWivrA2mRyU/FI0KAAQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="TSrwgMfue31l5YKH5YC63gNl/EJnr5ZJbUkDIAIpA9VCbqMkKC4yV7Qlzd02MRVNDQ406JZzgd4mO0azU8HKbQ==" saltValue="P3gP/2fV5vANzIL7NniDMg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -46641,7 +46601,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="gIF3gzcRwMevsVP9JM+eFJliWIfkjL6RYnVy29HH1zFwKTB/eJc1NVFGROY84dwrfqcI+B8KpOZ1waT1qDgCXQ==" saltValue="0Itsi1W8Rg+oXl6coWpocw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ogxQtq/9g6OeNkiNBs6ghJq8+LdVqsoK1CbSDtbSeFSK0ebg4cqAnXfIn86tuaNowgHjhLbE7woQSAqVYa5K1w==" saltValue="QFHNUEWTAfsZg09RvHfUXA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
@@ -47147,7 +47107,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="SSCu+FR+SN+siPEoAiap+3g3Z0SGqFtJklZqGSbEJvGKfBY2J7BHBpfevFvAYPx8Hf15tBeGKZdJ4ehQEpyLRg==" saltValue="A0PmMaoo+OfazXy7x4UxVw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bFi4UO/MYSy1ocOot5y7JdpTLSj3VYrhdtuVEmlekdzp7NtFBQZX4yNIi9A9S9nFic+mLseFiB4QMgSz7PmPmQ==" saltValue="0Yi1KsKDfpD+pl5y1FWoHw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="D20:G20 D11:G11 D13:G16 D22:G22 D24:G24" unlockedFormula="1"/>
@@ -48305,7 +48265,9 @@
         <v>3</v>
       </c>
       <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
+      <c r="D5" s="64" t="s">
+        <v>189</v>
+      </c>
       <c r="E5" s="45" t="str">
         <f>IF(E$7="","",E$7)</f>
         <v/>
@@ -48316,7 +48278,9 @@
         <v>4</v>
       </c>
       <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
+      <c r="D6" s="64" t="s">
+        <v>189</v>
+      </c>
       <c r="E6" s="45" t="str">
         <f>IF(E$7="","",E$7)</f>
         <v/>

--- a/inputs/en/template_input.xlsx
+++ b/inputs/en/template_input.xlsx
@@ -5,12 +5,12 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\LiST Optima bridge\App\ModData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\Nutrition\inputs\en\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E67A13A-5BCC-4675-83A8-1B50EF48FA73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D905AA7-4AC3-4BA4-8908-65267A345F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline year population inputs" sheetId="1" r:id="rId1"/>
@@ -28567,12 +28567,36 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="kNott2FY10++7LpzvuSEUUgvKblMKWlWyTJLQ7V3mUE+D/qQXgkJjdadeNqQ4e0dbATNIZiaZUbYZr3uwCKttQ==" saltValue="MboHEiRAGE0wfo213ZYZVw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="45">
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="B148:B150"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B67:B69"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="B48:B50"/>
@@ -28582,36 +28606,12 @@
     <mergeCell ref="B31:B33"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="B148:B150"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="B134:B136"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -40448,16 +40448,20 @@
         <v>1</v>
       </c>
       <c r="L14" s="105">
-        <v>1</v>
+        <f>L8</f>
+        <v>0.51</v>
       </c>
       <c r="M14" s="105">
-        <v>1</v>
+        <f t="shared" ref="M14:O14" si="0">M8</f>
+        <v>0.51</v>
       </c>
       <c r="N14" s="105">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.51</v>
       </c>
       <c r="O14" s="105">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.51</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -40609,37 +40613,48 @@
         <v>1</v>
       </c>
       <c r="E20" s="105">
-        <v>1</v>
+        <f>E19</f>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F20" s="105">
-        <v>1</v>
+        <f t="shared" ref="F20:O20" si="1">F19</f>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G20" s="105">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H20" s="105">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I20" s="105">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J20" s="105">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K20" s="105">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L20" s="105">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M20" s="105">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N20" s="105">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O20" s="105">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -40750,47 +40765,47 @@
         <v>0.4</v>
       </c>
       <c r="E26" s="105">
-        <f t="shared" ref="E26:O26" si="0">IF(E3=1,1,E3*0.9)</f>
+        <f t="shared" ref="E26:O26" si="2">IF(E3=1,1,E3*0.9)</f>
         <v>1</v>
       </c>
       <c r="F26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O26" s="105">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -40799,23 +40814,23 @@
         <v>183</v>
       </c>
       <c r="C27" s="105">
-        <f t="shared" ref="C27:O27" si="1">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:O27" si="3">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H27" s="105">
@@ -40831,19 +40846,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O27" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -40852,23 +40867,23 @@
         <v>201</v>
       </c>
       <c r="C28" s="105">
-        <f t="shared" ref="C28:O28" si="2">IF(C5=1,1,C5*0.9)</f>
+        <f t="shared" ref="C28:O28" si="4">IF(C5=1,1,C5*0.9)</f>
         <v>1</v>
       </c>
       <c r="D28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="F28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="H28" s="105">
@@ -40884,19 +40899,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="M28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="N28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O28" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -40905,23 +40920,23 @@
         <v>184</v>
       </c>
       <c r="C29" s="105">
-        <f t="shared" ref="C29:O29" si="3">IF(C6=1,1,C6*0.9)</f>
+        <f t="shared" ref="C29:O29" si="5">IF(C6=1,1,C6*0.9)</f>
         <v>1</v>
       </c>
       <c r="D29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H29" s="105">
@@ -40937,19 +40952,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="M29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="N29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="O29" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -40958,23 +40973,23 @@
         <v>185</v>
       </c>
       <c r="C30" s="105">
-        <f t="shared" ref="C30:O30" si="4">IF(C7=1,1,C7*0.9)</f>
+        <f t="shared" ref="C30:O30" si="6">IF(C7=1,1,C7*0.9)</f>
         <v>1</v>
       </c>
       <c r="D30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H30" s="105">
@@ -40990,19 +41005,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O30" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -41011,39 +41026,39 @@
         <v>182</v>
       </c>
       <c r="C31" s="105">
-        <f t="shared" ref="C31:K31" si="5">IF(C8=1,1,C8*0.9)</f>
+        <f t="shared" ref="C31:K31" si="7">IF(C8=1,1,C8*0.9)</f>
         <v>1</v>
       </c>
       <c r="D31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K31" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L31" s="105">
@@ -41064,39 +41079,39 @@
         <v>202</v>
       </c>
       <c r="C32" s="105">
-        <f t="shared" ref="C32:K32" si="6">IF(C9=1,1,C9*0.9)</f>
+        <f t="shared" ref="C32:K32" si="8">IF(C9=1,1,C9*0.9)</f>
         <v>1</v>
       </c>
       <c r="D32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="F32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="G32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K32" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L32" s="105">
@@ -41117,39 +41132,39 @@
         <v>57</v>
       </c>
       <c r="C33" s="105">
-        <f t="shared" ref="C33:K33" si="7">IF(C10=1,1,C10*0.9)</f>
+        <f t="shared" ref="C33:K33" si="9">IF(C10=1,1,C10*0.9)</f>
         <v>1</v>
       </c>
       <c r="D33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="E33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="I33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K33" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="L33" s="105">
@@ -41170,11 +41185,11 @@
         <v>131</v>
       </c>
       <c r="C34" s="105">
-        <f t="shared" ref="C34:O34" si="8">IF(C11=1,1,C11*0.9)</f>
+        <f t="shared" ref="C34:O34" si="10">IF(C11=1,1,C11*0.9)</f>
         <v>1</v>
       </c>
       <c r="D34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E34" s="105">
@@ -41187,35 +41202,35 @@
         <v>1</v>
       </c>
       <c r="H34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="I34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="K34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="L34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="M34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="N34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="O34" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -41268,11 +41283,11 @@
         <v>132</v>
       </c>
       <c r="C36" s="105">
-        <f t="shared" ref="C36:O36" si="9">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:O36" si="11">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="E36" s="105">
@@ -41285,35 +41300,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="I36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="J36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="K36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="L36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="M36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="N36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O36" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -41322,39 +41337,39 @@
         <v>59</v>
       </c>
       <c r="C37" s="105">
-        <f t="shared" ref="C37:K37" si="10">IF(C14=1,1,C14*0.9)</f>
+        <f t="shared" ref="C37:K37" si="12">IF(C14=1,1,C14*0.9)</f>
         <v>1</v>
       </c>
       <c r="D37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="E37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="F37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="I37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K37" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="L37" s="105">
@@ -41375,11 +41390,11 @@
         <v>337</v>
       </c>
       <c r="C38" s="105">
-        <f t="shared" ref="C38:O38" si="11">IF(C15=1,1,C15*0.9)</f>
+        <f t="shared" ref="C38:O38" si="13">IF(C15=1,1,C15*0.9)</f>
         <v>1</v>
       </c>
       <c r="D38" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E38" s="105">
@@ -41389,39 +41404,39 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H38" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="I38" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="J38" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="K38" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="L38" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="M38" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="N38" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="O38" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -41436,55 +41451,55 @@
         <v>63</v>
       </c>
       <c r="C41" s="105">
-        <f t="shared" ref="C41:O41" si="12">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:O41" si="14">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="E41" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="F41" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="G41" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="H41" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="I41" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="J41" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="K41" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="L41" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M41" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N41" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O41" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -41493,11 +41508,11 @@
         <v>64</v>
       </c>
       <c r="C42" s="105">
-        <f t="shared" ref="C42:D44" si="13">IF(C19=1,1,C19*0.9)</f>
+        <f t="shared" ref="C42:D44" si="15">IF(C19=1,1,C19*0.9)</f>
         <v>1</v>
       </c>
       <c r="D42" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E42" s="105">
@@ -41539,56 +41554,56 @@
         <v>62</v>
       </c>
       <c r="C43" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="D43" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E43" s="105">
-        <f t="shared" ref="E43:O43" si="14">IF(E20=1,1,E20*0.9)</f>
-        <v>1</v>
+        <f t="shared" ref="E43:O43" si="16">IF(E20=1,1,E20*0.9)</f>
+        <v>0.87839999999999996</v>
       </c>
       <c r="F43" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="G43" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="H43" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="I43" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="J43" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="K43" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="L43" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="M43" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="N43" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="O43" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.87839999999999996</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -41596,11 +41611,11 @@
         <v>47</v>
       </c>
       <c r="C44" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="D44" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="E44" s="105">
@@ -41701,47 +41716,47 @@
         <v>0.7</v>
       </c>
       <c r="E49" s="105">
-        <f t="shared" ref="E49:O49" si="15">IF(E3=1,1,E3*1.05)</f>
+        <f t="shared" ref="E49:O49" si="17">IF(E3=1,1,E3*1.05)</f>
         <v>1</v>
       </c>
       <c r="F49" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G49" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H49" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="I49" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="J49" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="K49" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L49" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M49" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N49" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O49" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -41750,23 +41765,23 @@
         <v>183</v>
       </c>
       <c r="C50" s="105">
-        <f t="shared" ref="C50:O50" si="16">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:O50" si="18">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E50" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="F50" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G50" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H50" s="105">
@@ -41782,19 +41797,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="M50" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="N50" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="O50" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
@@ -41803,23 +41818,23 @@
         <v>201</v>
       </c>
       <c r="C51" s="105">
-        <f t="shared" ref="C51:O51" si="17">IF(C5=1,1,C5*1.05)</f>
+        <f t="shared" ref="C51:O51" si="19">IF(C5=1,1,C5*1.05)</f>
         <v>1</v>
       </c>
       <c r="D51" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="E51" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F51" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G51" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H51" s="105">
@@ -41835,19 +41850,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M51" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="N51" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="O51" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
@@ -41856,23 +41871,23 @@
         <v>184</v>
       </c>
       <c r="C52" s="105">
-        <f t="shared" ref="C52:O52" si="18">IF(C6=1,1,C6*1.05)</f>
+        <f t="shared" ref="C52:O52" si="20">IF(C6=1,1,C6*1.05)</f>
         <v>1</v>
       </c>
       <c r="D52" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E52" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F52" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G52" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H52" s="105">
@@ -41888,19 +41903,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="M52" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="N52" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="O52" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -41909,23 +41924,23 @@
         <v>185</v>
       </c>
       <c r="C53" s="105">
-        <f t="shared" ref="C53:O53" si="19">IF(C7=1,1,C7*1.05)</f>
+        <f t="shared" ref="C53:O53" si="21">IF(C7=1,1,C7*1.05)</f>
         <v>1</v>
       </c>
       <c r="D53" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E53" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="F53" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="G53" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="H53" s="105">
@@ -41941,19 +41956,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="M53" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="N53" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="O53" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
     </row>
@@ -41962,39 +41977,39 @@
         <v>182</v>
       </c>
       <c r="C54" s="105">
-        <f t="shared" ref="C54:K54" si="20">IF(C8=1,1,C8*1.05)</f>
+        <f t="shared" ref="C54:K54" si="22">IF(C8=1,1,C8*1.05)</f>
         <v>1</v>
       </c>
       <c r="D54" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="E54" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="F54" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="G54" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="H54" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="I54" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="J54" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="K54" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="L54" s="105">
@@ -42015,39 +42030,39 @@
         <v>202</v>
       </c>
       <c r="C55" s="105">
-        <f t="shared" ref="C55:K55" si="21">IF(C9=1,1,C9*1.05)</f>
+        <f t="shared" ref="C55:K55" si="23">IF(C9=1,1,C9*1.05)</f>
         <v>1</v>
       </c>
       <c r="D55" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="E55" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="F55" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="G55" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="H55" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="I55" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="J55" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="K55" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="L55" s="105">
@@ -42068,39 +42083,39 @@
         <v>57</v>
       </c>
       <c r="C56" s="105">
-        <f t="shared" ref="C56:K56" si="22">IF(C10=1,1,C10*1.05)</f>
+        <f t="shared" ref="C56:K56" si="24">IF(C10=1,1,C10*1.05)</f>
         <v>1</v>
       </c>
       <c r="D56" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="E56" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="F56" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="G56" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="H56" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="I56" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="J56" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="K56" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="L56" s="105">
@@ -42121,11 +42136,11 @@
         <v>131</v>
       </c>
       <c r="C57" s="105">
-        <f t="shared" ref="C57:O57" si="23">IF(C11=1,1,C11*1.05)</f>
+        <f t="shared" ref="C57:O57" si="25">IF(C11=1,1,C11*1.05)</f>
         <v>1</v>
       </c>
       <c r="D57" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="E57" s="105">
@@ -42135,39 +42150,39 @@
         <v>0.77</v>
       </c>
       <c r="G57" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="H57" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="I57" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="J57" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="K57" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="L57" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="M57" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="N57" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="O57" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
     </row>
@@ -42220,11 +42235,11 @@
         <v>132</v>
       </c>
       <c r="C59" s="105">
-        <f t="shared" ref="C59:O59" si="24">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:O59" si="26">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="E59" s="105">
@@ -42237,35 +42252,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="I59" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="J59" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="K59" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="L59" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="M59" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="N59" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="O59" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
     </row>
@@ -42274,39 +42289,39 @@
         <v>59</v>
       </c>
       <c r="C60" s="105">
-        <f t="shared" ref="C60:K60" si="25">IF(C14=1,1,C14*1.05)</f>
+        <f t="shared" ref="C60:K60" si="27">IF(C14=1,1,C14*1.05)</f>
         <v>1</v>
       </c>
       <c r="D60" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="E60" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="F60" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G60" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="H60" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="I60" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="J60" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="K60" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="L60" s="105">
@@ -42327,11 +42342,11 @@
         <v>337</v>
       </c>
       <c r="C61" s="105">
-        <f t="shared" ref="C61:O61" si="26">IF(C15=1,1,C15*1.05)</f>
+        <f t="shared" ref="C61:O61" si="28">IF(C15=1,1,C15*1.05)</f>
         <v>1</v>
       </c>
       <c r="D61" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="E61" s="105">
@@ -42341,39 +42356,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="H61" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="I61" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="J61" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="K61" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="L61" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="M61" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="N61" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="O61" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
     </row>
@@ -42388,55 +42403,55 @@
         <v>63</v>
       </c>
       <c r="C64" s="105">
-        <f t="shared" ref="C64:O64" si="27">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:O64" si="29">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="E64" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F64" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G64" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H64" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="I64" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="J64" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="K64" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="L64" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="M64" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="N64" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="O64" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
     </row>
@@ -42445,11 +42460,11 @@
         <v>64</v>
       </c>
       <c r="C65" s="105">
-        <f t="shared" ref="C65:D67" si="28">IF(C19=1,1,C19*1.05)</f>
+        <f t="shared" ref="C65:D67" si="30">IF(C19=1,1,C19*1.05)</f>
         <v>1</v>
       </c>
       <c r="D65" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="E65" s="105">
@@ -42491,56 +42506,56 @@
         <v>62</v>
       </c>
       <c r="C66" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="D66" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="E66" s="105">
-        <f t="shared" ref="E66:O66" si="29">IF(E20=1,1,E20*1.05)</f>
-        <v>1</v>
+        <f t="shared" ref="E66:O66" si="31">IF(E20=1,1,E20*1.05)</f>
+        <v>1.0247999999999999</v>
       </c>
       <c r="F66" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <f t="shared" si="31"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="G66" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <f t="shared" si="31"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="H66" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <f t="shared" si="31"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="I66" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <f t="shared" si="31"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="J66" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <f t="shared" si="31"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="K66" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <f t="shared" si="31"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="L66" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <f t="shared" si="31"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="M66" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <f t="shared" si="31"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="N66" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <f t="shared" si="31"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="O66" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <f t="shared" si="31"/>
+        <v>1.0247999999999999</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.25">
@@ -42548,11 +42563,11 @@
         <v>47</v>
       </c>
       <c r="C67" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="D67" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="E67" s="105">
@@ -48506,23 +48521,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MediaLengthInSeconds xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="107b52809c0cc4b5077f1ac81d3c69cc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="82b7e1b740270cfb0676be859a78f3d0" ns2:_="">
     <xsd:import namespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
@@ -48678,25 +48676,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F25ACC24-A23B-4F66-B2C3-F39116C08A35}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87E89A13-0449-4026-BB40-CE009D889E15}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MediaLengthInSeconds xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07F27224-E052-49D0-B72B-C9073A8D27C1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -48712,4 +48709,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87E89A13-0449-4026-BB40-CE009D889E15}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F25ACC24-A23B-4F66-B2C3-F39116C08A35}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/inputs/en/template_input.xlsx
+++ b/inputs/en/template_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\Nutrition\inputs\en\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D905AA7-4AC3-4BA4-8908-65267A345F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE937B0-5846-4A73-B47E-3FCA624CE6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="9" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline year population inputs" sheetId="1" r:id="rId1"/>
@@ -34,13 +34,13 @@
     <sheet name="Population risk areas" sheetId="64" state="hidden" r:id="rId19"/>
     <sheet name="IYCF odds ratios" sheetId="65" state="hidden" r:id="rId20"/>
     <sheet name="Birth outcome risks" sheetId="66" state="hidden" r:id="rId21"/>
-    <sheet name="Relative risks" sheetId="67" state="hidden" r:id="rId22"/>
-    <sheet name="Odds ratios" sheetId="68" state="hidden" r:id="rId23"/>
+    <sheet name="Relative risks" sheetId="67" r:id="rId22"/>
+    <sheet name="Odds ratios" sheetId="68" r:id="rId23"/>
     <sheet name="Programs birth outcomes" sheetId="69" state="hidden" r:id="rId24"/>
-    <sheet name="Programs anaemia" sheetId="70" state="hidden" r:id="rId25"/>
+    <sheet name="Programs anaemia" sheetId="70" r:id="rId25"/>
     <sheet name="Programs wasting" sheetId="71" state="hidden" r:id="rId26"/>
-    <sheet name="Programs for children" sheetId="72" state="hidden" r:id="rId27"/>
-    <sheet name="Programs for PW" sheetId="73" state="hidden" r:id="rId28"/>
+    <sheet name="Programs for children" sheetId="72" r:id="rId27"/>
+    <sheet name="Programs for PW" sheetId="73" r:id="rId28"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Birth outcome risks'!$A$1:$F$7</definedName>
@@ -92,7 +92,7 @@
     <definedName name="term_SGA">'Baseline year population inputs'!$C$47</definedName>
     <definedName name="U5_mortality">'Baseline year population inputs'!$C$39</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -973,85 +973,299 @@
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>Nick Scott</author>
     <author>Tharindu Wickramaarachchi</author>
   </authors>
   <commentList>
-    <comment ref="B56" authorId="0" shapeId="0" xr:uid="{FC66AFB0-BAF9-4DBB-AF6D-B8B87CA43EAC}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-LiST 6.29
-Katz J, Lee AC, Kozuki N, et al. Mortality risk in preterm and small-for-gestational-age infants in low-income and middle-income countries: A pooled country analysis. Lancet 2013; 382(9890): 417–25</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B65" authorId="0" shapeId="0" xr:uid="{C839D234-346C-480F-A0B8-0A83B9B7B14B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-LiST 6.29
-Black RE, Victora CG, Walker SP, et al. Maternal and child undernutrition and overweight in low-income and middle-income countries. Lancet 2013; 382(9890): 427-51. http://www.ncbi.nlm.nih.gov/pubmed/23746772. (Supplementary material - Web Table 17.)
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C104" authorId="0" shapeId="0" xr:uid="{CA18766C-7ED2-4431-93C7-93BF2011C527}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Spectrum LiST 6.29</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A220" authorId="0" shapeId="0" xr:uid="{547E0BFB-8818-4349-8845-A1120C93D6D0}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{34B96FEA-B964-4EC2-B53C-D2953DF6BC58}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Olofin I, McDonald CM, Ezzati M, et al. Associations of Suboptimal Growth with All-Cause and Cause-Specific Mortality in Children under Five Years: A Pooled Analysis of Ten Prospective Studies. PLOS One 2013; 8(5): e64636. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D30" authorId="0" shapeId="0" xr:uid="{43367D38-92C3-4E0E-A4DC-CDB1A72DEE2F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Olofin I, McDonald CM, Ezzati M, et al. Associations of Suboptimal Growth with All-Cause and Cause-Specific Mortality in Children under Five Years: A Pooled Analysis of Ten Prospective Studies. PLOS One 2013; 8(5): e64636</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D57" authorId="0" shapeId="0" xr:uid="{6A8DF9E7-4D66-4EC7-9706-E5186D82B96A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Heidkamp R, Guida R, Phillips E, Clermont A. The Lives Saved Tool (LiST) as a Model for Prevention of Anemia in Women of Reproductive Age. J Nutr. 2017;147(11):2156S-2162S</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D66" authorId="0" shapeId="0" xr:uid="{889A3473-AB31-40E6-B9D0-633D6B72F3FC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D70" authorId="0" shapeId="0" xr:uid="{53AC47BB-8A66-4B39-B002-09D03EB8B997}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D74" authorId="0" shapeId="0" xr:uid="{814EC85F-D2EC-46FD-8BA2-C49BA3C34245}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+NEOVITA Study Group. Timing of initiation, patterns of breastfeeding, and infant survival: prospective analysis of pooled data from three randomised trials. Lancet Global Health 2016; 4(4): e266-75. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D82" authorId="0" shapeId="0" xr:uid="{EAE9BBD8-A606-4467-AE3F-B7B4E6C55FB3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D86" authorId="0" shapeId="0" xr:uid="{4D8D5033-A8BA-4DD6-ADC9-02ECAFAE5C2B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D90" authorId="0" shapeId="0" xr:uid="{C5201C06-1C5C-4C76-A3A5-D2BD69256AF7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D94" authorId="0" shapeId="0" xr:uid="{585AA742-BC60-4C28-A6B2-DB640388547E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D98" authorId="0" shapeId="0" xr:uid="{00A01ACB-0F5A-457B-8EDE-D7BDA4A6F01C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011. </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D105" authorId="0" shapeId="0" xr:uid="{E56D0B66-2989-49AD-904D-C505C2A6640F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Lamberti LM, Fischer Walker CL, Noiman A, et al. Breastfeeding and the risk for diarrhea morbidity and mortality. BMC Public Health 2011</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A220" authorId="1" shapeId="0" xr:uid="{547E0BFB-8818-4349-8845-A1120C93D6D0}">
       <text>
         <r>
           <rPr>
@@ -1086,6 +1300,31 @@
     <author>Tharindu Wickramaarachchi</author>
   </authors>
   <commentList>
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{14B14DA1-34EA-47AB-8E43-07604E896F80}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Checkley et al. Int J Epidemiol 2008.
+The adjusted odds of stunting increased by 1.13 for every five episodes (95% CI 1.07-1.19)</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000001000000}">
       <text>
         <r>
@@ -1357,6 +1596,83 @@
         </r>
       </text>
     </comment>
+    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{2ED71DA4-16C9-4E3C-BA26-DD6273DAAE4D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Troeger et al Lancet Glob Health 2018
+weight-for-height Z-score per day of diarrhoea –0·0096 (–0·0067 to −0·0125).
+OR calculated assuming weight-for-heaght distribution with mean=0 and S.D.=1, cumulative probability -2 (wasting) vs cumulative probability -2+0.0096</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{A7010501-4261-4C9B-90BB-6443ACFD3649}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Troeger et al Lancet Glob Health 2018
+weight-for-height Z-score per day of diarrhoea –0·0096 (–0·0067 to −0·0125).
+OR calculated assuming weight-for-heaght distribution with mean=0 and S.D.=1, cumulative probability -2 (wasting) vs cumulative probability -2+0.0096</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C27" authorId="0" shapeId="0" xr:uid="{A3E68AAD-3178-41B6-9912-DE240CC0354A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Checkley et al. Int J Epidemiol 2008.
+The adjusted odds of stunting increased by 1.13 for every five episodes (95% CI 1.07-1.19)</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="A28" authorId="1" shapeId="0" xr:uid="{ABB260EC-B8A5-4BFA-A0E7-ADE01D05CBD8}">
       <text>
         <r>
@@ -1528,6 +1844,58 @@
         </r>
       </text>
     </comment>
+    <comment ref="C38" authorId="0" shapeId="0" xr:uid="{D2D71672-0937-4CE2-B37E-4A5F8ACA207B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Troeger et al Lancet Glob Health 2018
+weight-for-height Z-score per day of diarrhoea –0·0096 (–0·0067 to −0·0125).
+OR calculated assuming weight-for-heaght distribution with mean=0 and S.D.=1, cumulative probability -2 (wasting) vs cumulative probability -2+0.0096</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C39" authorId="0" shapeId="0" xr:uid="{988C97C2-2596-4071-90C3-3B6EC84C56BC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Troeger et al Lancet Glob Health 2018
+weight-for-height Z-score per day of diarrhoea –0·0096 (–0·0067 to −0·0125).
+OR calculated assuming weight-for-heaght distribution with mean=0 and S.D.=1, cumulative probability -2 (wasting) vs cumulative probability -2+0.0096</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B44" authorId="1" shapeId="0" xr:uid="{B098814A-8C4C-43C0-9A4A-035A49677972}">
       <text>
         <r>
@@ -1549,6 +1917,31 @@
           </rPr>
           <t xml:space="preserve">
 &gt;1 but &lt; point estimate</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{D09CF5A5-8767-485E-B990-089CC054A8DA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Checkley et al. Int J Epidemiol 2008.
+The adjusted odds of stunting increased by 1.13 for every five episodes (95% CI 1.07-1.19)</t>
         </r>
       </text>
     </comment>
@@ -1672,6 +2065,58 @@
           <t xml:space="preserve">
 Dewey et al 2021, stunting, PR 0.88 (0.85-0.91)  
 Converted to OR is prev. data inputs are available else RR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C61" authorId="0" shapeId="0" xr:uid="{E3284572-14C7-4B88-AD6A-C589CAA24F4A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Troeger et al Lancet Glob Health 2018
+weight-for-height Z-score per day of diarrhoea –0·0096 (–0·0067 to −0·0125).
+OR calculated assuming weight-for-heaght distribution with mean=0 and S.D.=1, cumulative probability -2 (wasting) vs cumulative probability -2+0.0096</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C62" authorId="0" shapeId="0" xr:uid="{5262E1D2-D729-4DC6-AF18-93BB11321A99}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Troeger et al Lancet Glob Health 2018
+weight-for-height Z-score per day of diarrhoea –0·0096 (–0·0067 to −0·0125).
+OR calculated assuming weight-for-heaght distribution with mean=0 and S.D.=1, cumulative probability -2 (wasting) vs cumulative probability -2+0.0096</t>
         </r>
       </text>
     </comment>
@@ -2584,7 +3029,7 @@
     <author>Nick Scott</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{9046FF1F-8540-4D35-B867-C2C36C5D1F33}">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{E5FA8BAD-93BF-409D-A7D5-AB8BEFDB8E24}">
       <text>
         <r>
           <rPr>
@@ -2608,7 +3053,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{D67CBEA5-65B4-4FE9-82C7-DC2AFB4A875F}">
+    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{19D2142B-A8DC-45EF-A75E-42D0B53AA49F}">
       <text>
         <r>
           <rPr>
@@ -2633,7 +3078,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{3BDE8296-7C75-4D75-89DD-AB7DB3608948}">
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{2338D7F3-E9E5-4E5D-8043-C677065DC133}">
       <text>
         <r>
           <rPr>
@@ -2657,7 +3102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0" xr:uid="{F3E89390-03F9-4868-AA11-F5840E71531E}">
+    <comment ref="H6" authorId="0" shapeId="0" xr:uid="{41F6EA7C-88F2-417F-B020-50B4F5B3B2D9}">
       <text>
         <r>
           <rPr>
@@ -2681,7 +3126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H7" authorId="0" shapeId="0" xr:uid="{D6341004-DACF-4489-BD18-B9D4ADBB48A7}">
+    <comment ref="H7" authorId="0" shapeId="0" xr:uid="{0459F4A6-55D6-4F9D-973F-13451DE8F8CB}">
       <text>
         <r>
           <rPr>
@@ -2705,7 +3150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{38233D40-CF64-4BA1-A67E-D1A5F013CCE7}">
+    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{282A36CA-CBF0-4BFC-B054-E835C2383C4B}">
       <text>
         <r>
           <rPr>
@@ -2729,7 +3174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{269025AE-B01A-4939-B3A6-C9A8A90B5DBE}">
+    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{0153DB92-F989-40D6-B393-0529B54E74CE}">
       <text>
         <r>
           <rPr>
@@ -2753,7 +3198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{8C9BCD7E-B703-4A83-8F19-21A01D8E5A3E}">
+    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{FEC4637E-57DA-467E-B19C-E1BB5860B0F9}">
       <text>
         <r>
           <rPr>
@@ -2777,7 +3222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O8" authorId="0" shapeId="0" xr:uid="{1CCE61E6-CCD9-4D40-832B-38F858F363CF}">
+    <comment ref="O8" authorId="0" shapeId="0" xr:uid="{D33E7E37-FEC4-4A7F-8D6B-742EF3900718}">
       <text>
         <r>
           <rPr>
@@ -2801,7 +3246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{7A589E3F-DC46-4670-AAD1-FB091303D5EA}">
+    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{6E170B96-50CF-43CE-89A1-0A99D95CA858}">
       <text>
         <r>
           <rPr>
@@ -2825,7 +3270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M9" authorId="0" shapeId="0" xr:uid="{88A4C4E8-9044-4590-A24A-819DBD3B74B6}">
+    <comment ref="M9" authorId="0" shapeId="0" xr:uid="{9F65C420-B856-46C7-9C18-6E08DD715BAC}">
       <text>
         <r>
           <rPr>
@@ -2849,7 +3294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N9" authorId="0" shapeId="0" xr:uid="{58F5961E-BE27-42DC-BA47-8052CD598E83}">
+    <comment ref="N9" authorId="0" shapeId="0" xr:uid="{E51DEFC4-68A2-421B-A28A-9E152F9E95F5}">
       <text>
         <r>
           <rPr>
@@ -2873,7 +3318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O9" authorId="0" shapeId="0" xr:uid="{A44DF036-F705-4C9E-869B-35FA20D22C7E}">
+    <comment ref="O9" authorId="0" shapeId="0" xr:uid="{93884D12-F580-4E1D-BB10-84E5D687601A}">
       <text>
         <r>
           <rPr>
@@ -2897,7 +3342,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L10" authorId="0" shapeId="0" xr:uid="{4853B685-0C9D-4310-89B4-FC55EFF15D08}">
+    <comment ref="L10" authorId="0" shapeId="0" xr:uid="{965E08A1-26DC-4F21-92A8-4046BF82F03E}">
       <text>
         <r>
           <rPr>
@@ -2921,7 +3366,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{610733DC-C5A0-477F-8779-3D5E978ECE77}">
+    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{1D2694FE-075A-46BA-878B-631B3C98B805}">
       <text>
         <r>
           <rPr>
@@ -2945,7 +3390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N10" authorId="0" shapeId="0" xr:uid="{EE403504-DD2F-44B3-9A8E-DF158FE53E17}">
+    <comment ref="N10" authorId="0" shapeId="0" xr:uid="{3BD2F475-860D-4076-A33C-C3BBF462D828}">
       <text>
         <r>
           <rPr>
@@ -2969,7 +3414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O10" authorId="0" shapeId="0" xr:uid="{CE2D5E10-5A45-4DC2-A353-819F7441B3A1}">
+    <comment ref="O10" authorId="0" shapeId="0" xr:uid="{6C6350E6-B429-4ACB-BB83-EFD489CB8F3F}">
       <text>
         <r>
           <rPr>
@@ -2993,7 +3438,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="1" shapeId="0" xr:uid="{F2C39704-4C3A-4A8D-B44A-4D6BA1C4A29E}">
+    <comment ref="E11" authorId="1" shapeId="0" xr:uid="{1B542159-0FF4-41A6-B2FD-8AADA895E61A}">
       <text>
         <r>
           <rPr>
@@ -3017,7 +3462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F11" authorId="1" shapeId="0" xr:uid="{041AC73E-CAC4-4B9B-ACEA-673946341161}">
+    <comment ref="F11" authorId="1" shapeId="0" xr:uid="{3C50A6A9-0D90-4379-A195-680EA20E9B44}">
       <text>
         <r>
           <rPr>
@@ -3041,7 +3486,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{0C5A92FA-D3CC-48D7-98B6-B07F92400627}">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{4930BCCD-4A8B-4494-95EC-46501BD2F5CE}">
       <text>
         <r>
           <rPr>
@@ -3066,7 +3511,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{45B10EAE-5294-4D5C-A683-55F408C0B701}">
+    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{50A6554B-81C6-4ECA-A58A-3893B5884806}">
       <text>
         <r>
           <rPr>
@@ -3091,7 +3536,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{75744FDF-8C2B-47E9-AEB0-1C94AAACCAC2}">
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{7511E2FF-D780-4F72-B05B-DD82D102703F}">
       <text>
         <r>
           <rPr>
@@ -3116,7 +3561,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{D4FC7E72-C437-4FB5-9C44-584CA25710E4}">
+    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{AC3F1E65-252C-4D84-89B5-99BFA0EC8D41}">
       <text>
         <r>
           <rPr>
@@ -3141,7 +3586,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{CF10A52A-4ED3-4679-AFB4-90DA85BE03FD}">
+    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{03B9CF86-2812-4917-BCCB-02E3B86B5FA5}">
       <text>
         <r>
           <rPr>
@@ -3166,7 +3611,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{B970E795-852B-4AFE-B2F5-4657D760B1CD}">
+    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{5CC84E68-F3A4-4939-85E0-159EE927CD80}">
       <text>
         <r>
           <rPr>
@@ -3191,7 +3636,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{B49D247E-8A43-4781-A096-6E6A2FDED63D}">
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{7C950990-554A-4703-93E9-7168EB8940B1}">
       <text>
         <r>
           <rPr>
@@ -3216,7 +3661,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{31077B81-8906-4022-BC22-AE7E434C4614}">
+    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{395E7529-ADBB-419F-9D5C-6C3D717C3A77}">
       <text>
         <r>
           <rPr>
@@ -3241,7 +3686,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K12" authorId="0" shapeId="0" xr:uid="{AA5BBD63-A836-4F73-B67F-4BC99C44C3CE}">
+    <comment ref="K12" authorId="0" shapeId="0" xr:uid="{4D009898-38F9-4FB5-8886-82DB3F331B29}">
       <text>
         <r>
           <rPr>
@@ -3266,7 +3711,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L12" authorId="0" shapeId="0" xr:uid="{501E7324-9119-44AF-98D9-3E0B0E0C2BF9}">
+    <comment ref="L12" authorId="0" shapeId="0" xr:uid="{BCADDE0F-D7D1-41E4-999B-9329A1133C77}">
       <text>
         <r>
           <rPr>
@@ -3291,7 +3736,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{BCAB7316-A6FB-41C7-94CB-AF6B4B3DCD6B}">
+    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{88835307-D05D-42FB-9B0A-0BBC6A19B441}">
       <text>
         <r>
           <rPr>
@@ -3316,7 +3761,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N12" authorId="0" shapeId="0" xr:uid="{B783C35A-C5C2-453A-BF67-9BC060F631E5}">
+    <comment ref="N12" authorId="0" shapeId="0" xr:uid="{777F9507-4FE8-447F-A11B-2ED30AE86852}">
       <text>
         <r>
           <rPr>
@@ -3341,7 +3786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O12" authorId="0" shapeId="0" xr:uid="{6F4FF2C8-7E0A-452D-9458-64173E3775DD}">
+    <comment ref="O12" authorId="0" shapeId="0" xr:uid="{C305BC5B-9D0D-4A4B-8A5F-E25346BC42F8}">
       <text>
         <r>
           <rPr>
@@ -3366,7 +3811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{754B5520-8785-4461-975F-14AD84462369}">
+    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{F5AD49F9-4E89-4303-B1DD-7C6C1EE34017}">
       <text>
         <r>
           <rPr>
@@ -3390,7 +3835,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{63C7E154-C355-4E37-B74E-A3F877BF9D65}">
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{F676AA82-4CC2-47BE-BB83-AC3CACB210D9}">
       <text>
         <r>
           <rPr>
@@ -3414,7 +3859,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{0AD9136A-B010-472E-B476-412E5F3485AC}">
+    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{21376480-CB3C-4F03-B39F-E5C06467F3E7}">
       <text>
         <r>
           <rPr>
@@ -3438,7 +3883,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L14" authorId="1" shapeId="0" xr:uid="{062FE8A3-3283-42BF-A0B4-B7965DC3FA49}">
+    <comment ref="L14" authorId="1" shapeId="0" xr:uid="{4C6321D4-BCE4-4AFE-98BE-ABC964A5464C}">
       <text>
         <r>
           <rPr>
@@ -3465,7 +3910,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M14" authorId="1" shapeId="0" xr:uid="{8BEABB9E-7617-4425-9F34-DDCFB6159EDE}">
+    <comment ref="M14" authorId="1" shapeId="0" xr:uid="{8F4E5DE3-6143-4F3E-A9C5-79C2F897E7F4}">
       <text>
         <r>
           <rPr>
@@ -3492,7 +3937,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N14" authorId="1" shapeId="0" xr:uid="{1EE23FE8-D97D-4DEE-B454-BB0CCEA6D996}">
+    <comment ref="N14" authorId="1" shapeId="0" xr:uid="{F66DBC46-D127-4B29-9DD4-AEF5E8FB1506}">
       <text>
         <r>
           <rPr>
@@ -3519,7 +3964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O14" authorId="1" shapeId="0" xr:uid="{2A92BEC6-9FDF-41B4-88F1-665C46639186}">
+    <comment ref="O14" authorId="1" shapeId="0" xr:uid="{31FE7754-E232-4A6D-8C5B-07B95C1BC2F8}">
       <text>
         <r>
           <rPr>
@@ -3546,7 +3991,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E15" authorId="0" shapeId="0" xr:uid="{EA967CFD-9817-42D6-892E-FBA384C4301C}">
+    <comment ref="E15" authorId="0" shapeId="0" xr:uid="{FCC33859-1961-4C6C-8BCD-2204DB58E6EE}">
       <text>
         <r>
           <rPr>
@@ -3570,7 +4015,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F15" authorId="0" shapeId="0" xr:uid="{13BE5A6A-0492-4BAA-8205-C4784D5A42C3}">
+    <comment ref="F15" authorId="0" shapeId="0" xr:uid="{5E1923EB-511F-4256-A1A7-E9CBDA5CCF45}">
       <text>
         <r>
           <rPr>
@@ -3594,15 +4039,15 @@
         </r>
       </text>
     </comment>
-    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{3BE68A51-A16C-4D2E-97C7-0702A8A5C5BD}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
+    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{44B6BEF2-7264-44EC-B06E-F361DAB56203}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:</t>
         </r>
@@ -3611,10 +4056,250 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Insufficient published research on the intervention’s effect on the outcome.</t>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{37735778-291F-4C48-8839-E59D32F7BE70}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{F2662C3C-8D6A-4222-A7A4-47AD6B7FA978}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{D150A46D-92DD-4DFC-9DE9-CD874D4AD5DC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{0DB3E05F-1BE4-4008-83A6-4D31928F8E61}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{3E65390B-60D3-4D3A-AA37-9B3D6EC91E2B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{E8897B0B-2707-4B2B-8FDA-52A3F582068E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L18" authorId="0" shapeId="0" xr:uid="{4FE59595-C62B-46D3-89A9-59146ACE5031}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{E2BDDEB1-B8BE-41E5-AAB8-9B8F7493F0EC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N18" authorId="0" shapeId="0" xr:uid="{3A28F73A-73D9-407B-A2DD-CBB904F50AF2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O18" authorId="0" shapeId="0" xr:uid="{258334C9-E76A-4FA7-A10F-7CCC0B0563D1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -3642,15 +4327,15 @@
         </r>
       </text>
     </comment>
-    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{2678EEA8-4E8E-4BDA-93AA-8CDC1BD15666}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
+    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{3BC9A9D5-CC60-4731-8923-E10030869F4F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:</t>
         </r>
@@ -3659,10 +4344,250 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Insufficient published research on the intervention’s effect on the outcome.</t>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{7760C48C-4F93-48B5-9FFC-DE563A233354}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{5B3766FE-CA92-4F62-9E72-19F21FF5D56E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{CE76ABCD-147B-4784-849A-9998ABE98BBA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{EBA450B2-1CF2-4288-BDA2-78745CAD7431}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{24448E14-B7A1-43CB-984E-19C2A7416D14}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{595E7BB3-39E3-42DE-A065-546E90831A5B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L20" authorId="0" shapeId="0" xr:uid="{CD3045CB-86C7-4BF8-9279-07B5A622D32F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M20" authorId="0" shapeId="0" xr:uid="{000ADE9C-7F23-4944-92BE-0C516E4123CC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N20" authorId="0" shapeId="0" xr:uid="{89E488E8-E6DA-4D0F-A685-36FB1F3044F1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O20" authorId="0" shapeId="0" xr:uid="{C086FE8B-A83A-4BD2-8BA8-B7EAD0672690}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -3714,7 +4639,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{0B3EBDB6-6355-42A0-886E-0D1673220EC2}">
+    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{8278CAA9-6D3F-47D1-BDAE-A9947B15A28F}">
       <text>
         <r>
           <rPr>
@@ -3738,7 +4663,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H27" authorId="0" shapeId="0" xr:uid="{0CCDC919-E274-4983-8D71-A8E899C3967D}">
+    <comment ref="H27" authorId="0" shapeId="0" xr:uid="{2EECE645-A9A1-495A-BCF7-2DD081BA9A97}">
       <text>
         <r>
           <rPr>
@@ -3763,7 +4688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="0" shapeId="0" xr:uid="{51B6C54F-17AF-4947-AB65-A920A491A627}">
+    <comment ref="H28" authorId="0" shapeId="0" xr:uid="{5CF8896A-3906-4A61-B963-91AF6895990C}">
       <text>
         <r>
           <rPr>
@@ -3788,7 +4713,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H29" authorId="0" shapeId="0" xr:uid="{49F25E15-38FC-4B0B-872F-06342668DA34}">
+    <comment ref="H29" authorId="0" shapeId="0" xr:uid="{8CF218BE-16AD-4E44-AFAA-F8503A37EEC9}">
       <text>
         <r>
           <rPr>
@@ -3813,7 +4738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H30" authorId="0" shapeId="0" xr:uid="{B4621789-60C7-4A32-8E7A-5169D4D05E10}">
+    <comment ref="H30" authorId="0" shapeId="0" xr:uid="{31EE5334-3B32-4627-8AA8-43C5DCABFE57}">
       <text>
         <r>
           <rPr>
@@ -3838,7 +4763,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L31" authorId="0" shapeId="0" xr:uid="{7BB77FEE-C001-44D6-82E7-58224035CC6C}">
+    <comment ref="L31" authorId="0" shapeId="0" xr:uid="{ED226BFF-22AC-4047-93D1-962A9FEF3CD2}">
       <text>
         <r>
           <rPr>
@@ -3862,7 +4787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M31" authorId="0" shapeId="0" xr:uid="{3BF5BF1A-652C-42DC-AC35-91515B6AC350}">
+    <comment ref="M31" authorId="0" shapeId="0" xr:uid="{FFF2E41D-D700-4A82-8987-9FDAD4E67C9E}">
       <text>
         <r>
           <rPr>
@@ -3886,7 +4811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N31" authorId="0" shapeId="0" xr:uid="{99D0C8B5-E236-4FC6-B684-E70FA4E7AA38}">
+    <comment ref="N31" authorId="0" shapeId="0" xr:uid="{50D34FA5-3380-4C57-A332-46CE9E8219B8}">
       <text>
         <r>
           <rPr>
@@ -3910,7 +4835,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O31" authorId="0" shapeId="0" xr:uid="{4EC2F4FE-02D6-4961-8634-B4576AC781DE}">
+    <comment ref="O31" authorId="0" shapeId="0" xr:uid="{CF22250A-9F96-414C-BF3B-09B794CAA5FB}">
       <text>
         <r>
           <rPr>
@@ -3934,7 +4859,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L32" authorId="0" shapeId="0" xr:uid="{A840B2B0-4167-4D7A-9530-A506727B7DFF}">
+    <comment ref="L32" authorId="0" shapeId="0" xr:uid="{C704A05C-ABF8-46CF-8830-60096BC91E98}">
       <text>
         <r>
           <rPr>
@@ -3958,7 +4883,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M32" authorId="0" shapeId="0" xr:uid="{769730BA-E261-4A37-A623-A8672BFAEC53}">
+    <comment ref="M32" authorId="0" shapeId="0" xr:uid="{1B730C56-AD19-4F33-8439-BA27E227C179}">
       <text>
         <r>
           <rPr>
@@ -3982,7 +4907,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N32" authorId="0" shapeId="0" xr:uid="{B33C0480-82DC-47C1-A2B0-309E1A041440}">
+    <comment ref="N32" authorId="0" shapeId="0" xr:uid="{E071AC68-E7A6-42B5-98FE-A5D4898327BF}">
       <text>
         <r>
           <rPr>
@@ -4006,7 +4931,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O32" authorId="0" shapeId="0" xr:uid="{AD06F308-7008-4506-9FE1-A95ED9B85B36}">
+    <comment ref="O32" authorId="0" shapeId="0" xr:uid="{56119EC3-31D8-4D15-A004-FDB2E57F18F6}">
       <text>
         <r>
           <rPr>
@@ -4030,7 +4955,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{6F2BF4C1-4CC5-4E05-B9F0-97D1912529C9}">
+    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{37263B80-E038-4697-91D1-B0CF6BA1E9E5}">
       <text>
         <r>
           <rPr>
@@ -4054,7 +4979,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M33" authorId="0" shapeId="0" xr:uid="{FE4781E3-C7FD-43DE-85B2-A3DEE792462B}">
+    <comment ref="M33" authorId="0" shapeId="0" xr:uid="{C0DD9308-7FDF-45F2-91F0-9630B2C85152}">
       <text>
         <r>
           <rPr>
@@ -4078,7 +5003,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N33" authorId="0" shapeId="0" xr:uid="{C18686B2-EEAE-4B6B-86D9-E5A53F241AD3}">
+    <comment ref="N33" authorId="0" shapeId="0" xr:uid="{684C6939-D57C-476F-AAA3-1C24A9999F66}">
       <text>
         <r>
           <rPr>
@@ -4102,7 +5027,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O33" authorId="0" shapeId="0" xr:uid="{99B9577F-5A08-419B-9D4B-DBCE0A829734}">
+    <comment ref="O33" authorId="0" shapeId="0" xr:uid="{DB802992-0C36-4251-96F3-BB879D05216B}">
       <text>
         <r>
           <rPr>
@@ -4126,7 +5051,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C35" authorId="0" shapeId="0" xr:uid="{E2226ABC-B663-441F-A667-3F60C248AAF2}">
+    <comment ref="C35" authorId="0" shapeId="0" xr:uid="{2D277618-7513-4F17-938E-65CFBA3262D5}">
       <text>
         <r>
           <rPr>
@@ -4151,7 +5076,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D35" authorId="0" shapeId="0" xr:uid="{04CD71BD-C936-4211-8F17-8914E187F43F}">
+    <comment ref="D35" authorId="0" shapeId="0" xr:uid="{508277B8-700A-4F25-B6D2-785887B20506}">
       <text>
         <r>
           <rPr>
@@ -4176,7 +5101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{2F2BD23D-031D-46AF-8CF4-3733CB7647D1}">
+    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{3140FF00-E5C4-4EB7-92CA-DD2E79AA7C44}">
       <text>
         <r>
           <rPr>
@@ -4201,7 +5126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F35" authorId="0" shapeId="0" xr:uid="{021E4BB3-D607-4A9F-8F03-38756D38D55D}">
+    <comment ref="F35" authorId="0" shapeId="0" xr:uid="{65FA314B-75F8-476B-AD0B-CAC2A2A05057}">
       <text>
         <r>
           <rPr>
@@ -4226,7 +5151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G35" authorId="0" shapeId="0" xr:uid="{C7E4159B-48FA-49FA-A21E-D0E8058DD5C8}">
+    <comment ref="G35" authorId="0" shapeId="0" xr:uid="{A5E315C2-B1F7-4C0B-AFDE-031EC481296B}">
       <text>
         <r>
           <rPr>
@@ -4251,7 +5176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H35" authorId="0" shapeId="0" xr:uid="{C55018F6-BB8B-4E47-BDDB-FF2FA3113319}">
+    <comment ref="H35" authorId="0" shapeId="0" xr:uid="{E0794B47-8F2E-4F96-A88B-9F5F2150C516}">
       <text>
         <r>
           <rPr>
@@ -4276,7 +5201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I35" authorId="0" shapeId="0" xr:uid="{38B8F017-E9E3-48BE-9E3E-1F2E62357701}">
+    <comment ref="I35" authorId="0" shapeId="0" xr:uid="{5637E9AC-577E-4CD4-B7F6-F896D0CA7E6A}">
       <text>
         <r>
           <rPr>
@@ -4301,7 +5226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J35" authorId="0" shapeId="0" xr:uid="{A06F7E0F-6BCB-4171-BD35-92A1937E55CB}">
+    <comment ref="J35" authorId="0" shapeId="0" xr:uid="{C4A1DE1D-6EE0-4163-9C0B-44AB9F5FE270}">
       <text>
         <r>
           <rPr>
@@ -4326,7 +5251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K35" authorId="0" shapeId="0" xr:uid="{0BD504C1-DD1F-491C-8586-E9F514092FB5}">
+    <comment ref="K35" authorId="0" shapeId="0" xr:uid="{7A11B1E1-C245-46B6-BD73-3812B00EC553}">
       <text>
         <r>
           <rPr>
@@ -4351,7 +5276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L35" authorId="0" shapeId="0" xr:uid="{A7E1D82F-A105-4285-9320-564ABA15FA0A}">
+    <comment ref="L35" authorId="0" shapeId="0" xr:uid="{657794F4-F779-47EB-89F9-95A42B332050}">
       <text>
         <r>
           <rPr>
@@ -4376,7 +5301,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M35" authorId="0" shapeId="0" xr:uid="{76A0EBD9-EE74-49D2-BFAF-9E4570F3A42E}">
+    <comment ref="M35" authorId="0" shapeId="0" xr:uid="{205C026D-F608-453C-8497-15BA1FA6910D}">
       <text>
         <r>
           <rPr>
@@ -4401,7 +5326,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N35" authorId="0" shapeId="0" xr:uid="{5B469B1A-2312-4851-92CB-831841315810}">
+    <comment ref="N35" authorId="0" shapeId="0" xr:uid="{85994BEB-F7F3-407F-A201-28B4187CF856}">
       <text>
         <r>
           <rPr>
@@ -4426,7 +5351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O35" authorId="0" shapeId="0" xr:uid="{5DE19DA1-9B2C-40A8-980E-1FC1E21FD5E5}">
+    <comment ref="O35" authorId="0" shapeId="0" xr:uid="{293CF64E-D534-4060-842C-0BE286513FE7}">
       <text>
         <r>
           <rPr>
@@ -4451,7 +5376,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E36" authorId="0" shapeId="0" xr:uid="{5FC2E3EF-E369-40D1-B470-6268D53F14D1}">
+    <comment ref="E36" authorId="0" shapeId="0" xr:uid="{AC375BB9-56D8-456E-A5AD-7A369B8D0358}">
       <text>
         <r>
           <rPr>
@@ -4475,7 +5400,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F36" authorId="0" shapeId="0" xr:uid="{C5BD6115-C708-4DEC-995E-522DA89D35BE}">
+    <comment ref="F36" authorId="0" shapeId="0" xr:uid="{AC1B6E2C-8AB1-4B6A-9CEC-75C0325D952B}">
       <text>
         <r>
           <rPr>
@@ -4499,7 +5424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G36" authorId="0" shapeId="0" xr:uid="{1E2B46E6-88EA-43EF-9F1E-23C9C78960C6}">
+    <comment ref="G36" authorId="0" shapeId="0" xr:uid="{E5847517-BA54-4497-898C-2EBAA48B5122}">
       <text>
         <r>
           <rPr>
@@ -4523,7 +5448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E38" authorId="0" shapeId="0" xr:uid="{F7697C34-EFEB-4834-AB19-D49B2964AA25}">
+    <comment ref="E38" authorId="0" shapeId="0" xr:uid="{F91DFF6E-E132-40E3-B99C-BE644BAFFE8A}">
       <text>
         <r>
           <rPr>
@@ -4547,7 +5472,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F38" authorId="0" shapeId="0" xr:uid="{88722465-6E97-4B0D-BB97-6A5E32582AE5}">
+    <comment ref="F38" authorId="0" shapeId="0" xr:uid="{82C2EC19-9EA1-4B89-BAEC-820493A0211B}">
       <text>
         <r>
           <rPr>
@@ -4571,6 +5496,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="E41" authorId="0" shapeId="0" xr:uid="{47D26035-BD89-470E-B909-0F120207FEB4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E42" authorId="0" shapeId="0" xr:uid="{2D128182-DACE-428A-9973-2C830923549B}">
       <text>
         <r>
@@ -4595,6 +5544,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="E43" authorId="0" shapeId="0" xr:uid="{703E1076-E4D4-414E-AE8E-3B551ABFDA7D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E44" authorId="0" shapeId="0" xr:uid="{0C3E6647-06D5-44EF-8FE5-59B1329FE276}">
       <text>
         <r>
@@ -4619,7 +5592,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{0F186CC8-6BE9-43A0-8E16-F53C8B65D3DA}">
+    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{3C7C01D7-6D29-42FA-8893-336D7F9A27EA}">
       <text>
         <r>
           <rPr>
@@ -4643,7 +5616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{86BB7B11-2D62-461C-B5FF-13F9D106F9F0}">
+    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{A18414E9-EAB5-4272-A620-3B11A62429A3}">
       <text>
         <r>
           <rPr>
@@ -4668,7 +5641,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{3AD85D21-4A9E-4BA8-9583-AB1AEDAAA017}">
+    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{36F68044-2A01-4C00-B659-D3B347F98ECC}">
       <text>
         <r>
           <rPr>
@@ -4693,7 +5666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{BBFE44D4-A76B-416F-8B24-3824EBCC8892}">
+    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{A91B0525-7A2B-4703-B98A-94D3F10A149F}">
       <text>
         <r>
           <rPr>
@@ -4718,7 +5691,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{A4F204A0-9139-47F9-B75E-C981662F0F6B}">
+    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{42F796A1-11D9-4B30-B0B7-6BC3C8093FD7}">
       <text>
         <r>
           <rPr>
@@ -4743,7 +5716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{89A7FF6D-A36B-486A-A9C6-797D8BED6AA2}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{3D616178-B84C-4532-89BF-C77E6D793FCF}">
       <text>
         <r>
           <rPr>
@@ -4768,7 +5741,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{20798702-230C-4F00-AC38-1B4BAD0CDF84}">
+    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{FAAC60D6-044B-478A-9B0B-0C0FFB302D79}">
       <text>
         <r>
           <rPr>
@@ -4793,7 +5766,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{3BA879E9-D676-40BD-86CA-F58D4B85CEA3}">
+    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{F1BE21FE-CB2D-4A0A-9245-4A6341540639}">
       <text>
         <r>
           <rPr>
@@ -4818,7 +5791,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{87F81283-9267-48E0-A463-385D11BE6F99}">
+    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{4A265A01-3E89-4702-80D3-57603965C4C8}">
       <text>
         <r>
           <rPr>
@@ -4843,7 +5816,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{A6D31735-995B-46FB-BC78-739AD411616F}">
+    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{985C719D-E2C6-4933-BF71-E38D897FE12B}">
       <text>
         <r>
           <rPr>
@@ -4868,7 +5841,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{784DCF15-72B9-477B-9D34-3553E7651657}">
+    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{8479D2CB-03CE-473D-983E-28F11CD5AA01}">
       <text>
         <r>
           <rPr>
@@ -4893,7 +5866,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{EEBE9062-AEC4-4BDC-A97E-30FEC3DC4226}">
+    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{1EE4B4B5-07D8-43E9-90E4-6167AB4A5804}">
       <text>
         <r>
           <rPr>
@@ -4918,7 +5891,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{F4AC0CCA-9161-4E26-8404-BB9BE932DE66}">
+    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{2C5F5C95-FE40-44BE-AB6B-24B84CC79E82}">
       <text>
         <r>
           <rPr>
@@ -4943,7 +5916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{972F82C0-6D52-4A29-B849-E7476FF3FD80}">
+    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{9DBF1062-4EB0-4501-B88E-624A35471B86}">
       <text>
         <r>
           <rPr>
@@ -4968,7 +5941,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{2C0CC425-D9FB-4B5A-91D9-D41080A5EE18}">
+    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{C1F17F73-EC9A-4810-8A7A-F37F3FD46C56}">
       <text>
         <r>
           <rPr>
@@ -4993,7 +5966,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{6F834B84-A5A0-4617-ACC2-BD9D44C9FDEF}">
+    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{61E1631A-04B9-41CB-87A5-10C1D7D69153}">
       <text>
         <r>
           <rPr>
@@ -5018,7 +5991,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{CABFA532-7C41-4FD1-9A14-950757EA6F35}">
+    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{8C61CF6A-A609-470A-A7A3-BBACAA6AD3DE}">
       <text>
         <r>
           <rPr>
@@ -5043,7 +6016,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{514E6ACE-57F4-4A0C-AE58-91B69BF03B29}">
+    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{CE3C9D8C-4F68-4541-89EE-ECB5F1C01ABC}">
       <text>
         <r>
           <rPr>
@@ -5067,7 +6040,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{20C90787-495B-43F3-B459-97D6525BC244}">
+    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{0222CD48-1A54-45B6-8DDD-BD2B4D9FB190}">
       <text>
         <r>
           <rPr>
@@ -5091,7 +6064,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{21DCA492-D9E7-4DC0-9B43-D7228E093375}">
+    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{14540435-C53E-48A5-96E5-10D11AF2955E}">
       <text>
         <r>
           <rPr>
@@ -5115,7 +6088,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{C1CD31AD-0DAC-46C5-AF6A-15F92DDCB1F1}">
+    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{BBE77DE0-7A1E-42DF-ABE9-D82F8C26127D}">
       <text>
         <r>
           <rPr>
@@ -5139,7 +6112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{2D849AFF-3B69-4EE0-B4F5-99C3367EBBD7}">
+    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{A3259BE7-694C-4766-8BD3-A0A97D1DE1ED}">
       <text>
         <r>
           <rPr>
@@ -5163,7 +6136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{2A9FF904-557C-42E3-A7CC-24E5C6F2A892}">
+    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{F7755F1F-A813-4835-A282-698D00A09844}">
       <text>
         <r>
           <rPr>
@@ -5187,7 +6160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{C11DE72B-F6BB-4A40-AF3E-D7E2208BB4BA}">
+    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{D0D590D2-669B-4C41-99E3-E63B98949724}">
       <text>
         <r>
           <rPr>
@@ -5211,7 +6184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{0E6D1AFE-8A69-4BC8-B975-B23C532BD7A5}">
+    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{314B446B-9F7D-41D5-A1B8-D97E681FF177}">
       <text>
         <r>
           <rPr>
@@ -5235,7 +6208,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{64CA34B0-A41A-4BDA-B979-BCB88E9EE8DC}">
+    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{CC8922FE-CC83-4A52-942B-00AA8EDEE5F9}">
       <text>
         <r>
           <rPr>
@@ -5259,7 +6232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{11F73239-626A-4DF9-9812-819843340AA8}">
+    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{55DC4339-F215-4D17-9848-20452CF5C3FB}">
       <text>
         <r>
           <rPr>
@@ -5283,7 +6256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{10B00C10-8E38-486A-8681-EAB2DB52644B}">
+    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{50736DF7-ED00-4D51-928B-D3E4EDEFB050}">
       <text>
         <r>
           <rPr>
@@ -5307,7 +6280,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{9166A6F0-10A1-4B50-8BAA-C182F31FA14A}">
+    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{EECBB7E7-C411-49E0-8D2A-DD2380F7EAC5}">
       <text>
         <r>
           <rPr>
@@ -5331,7 +6304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{21359D7B-485C-42CE-B0DC-D76CE9D6B49C}">
+    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{9F6EC162-AE63-43AC-8675-C73F6D71FBE1}">
       <text>
         <r>
           <rPr>
@@ -5356,7 +6329,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{55315153-9BC1-4951-B118-6FE67FC07072}">
+    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{528D7DC3-28A1-42C0-B5A7-0B1AE522D2E9}">
       <text>
         <r>
           <rPr>
@@ -5381,7 +6354,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{7528943F-AA91-48F3-8950-3DF851CFCE7A}">
+    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{0E52F3DA-85C8-4EDF-BBA5-23EB8DA6A233}">
       <text>
         <r>
           <rPr>
@@ -5406,7 +6379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{DEE4EC48-FA9D-48CE-A5A3-74CDC3DC9EBC}">
+    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{2DD481FB-8AE3-46B2-9930-22ED657EB3FE}">
       <text>
         <r>
           <rPr>
@@ -5431,7 +6404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{2C044F4D-68D1-424B-A7F0-E7D08785AB4C}">
+    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{0512303C-3E5A-4EEF-9EE8-EA9D414BC1A4}">
       <text>
         <r>
           <rPr>
@@ -5456,7 +6429,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{72DA9D23-70D8-4FAC-A7FD-A5A0E96A685E}">
+    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{77053D45-3784-4849-9B25-BD4C7AD510C5}">
       <text>
         <r>
           <rPr>
@@ -5481,7 +6454,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{A76F8BCF-C7D9-4559-A882-2D795EECA249}">
+    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{CA0262BD-63E6-4FD0-B7EE-313318E1F162}">
       <text>
         <r>
           <rPr>
@@ -5506,7 +6479,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{7DE1034D-A7E0-4362-9134-74EB9F38F8EC}">
+    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{05027182-F7FF-4732-B11F-D74DE48E498E}">
       <text>
         <r>
           <rPr>
@@ -5531,7 +6504,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00A2CC2B-93A6-473D-9783-7010D10C9457}">
+    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{88D5A977-B039-40FE-B322-05334DB48445}">
       <text>
         <r>
           <rPr>
@@ -5556,7 +6529,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{6A375C4B-6000-4C47-B755-C120CD0FDDBF}">
+    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{FD8A8321-3E19-46B3-90B7-E4985D3B368D}">
       <text>
         <r>
           <rPr>
@@ -5581,7 +6554,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{D636E105-D8C3-42D0-9194-4D5088786912}">
+    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{5B839781-622F-4556-A941-11CABC94AA3F}">
       <text>
         <r>
           <rPr>
@@ -5606,7 +6579,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{18B923B3-AD41-46EE-8233-DA746F361DDA}">
+    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{F72A35BD-7808-4E2A-97DB-1547D7DE38CB}">
       <text>
         <r>
           <rPr>
@@ -5631,7 +6604,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{DD907AE0-B29F-46A7-A880-4C47805C02CC}">
+    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{C442AB46-7D51-44EE-B1D2-8495078CEB2E}">
       <text>
         <r>
           <rPr>
@@ -5656,7 +6629,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{DB4BE836-7FA2-41C2-9CD9-F1C0ED004FBB}">
+    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{49AC4147-F9B9-494C-9058-DA92433E4106}">
       <text>
         <r>
           <rPr>
@@ -5680,7 +6653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{3260BDE2-DFE0-4E41-B354-4028D234C478}">
+    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{78574AE1-34B9-42A4-8BEE-E7D4FD56F6F0}">
       <text>
         <r>
           <rPr>
@@ -5704,7 +6677,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{EFF8A991-084C-4008-8A98-1943E25D4593}">
+    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{F3FBE881-CBB5-4B12-A5C2-47275C41E6F6}">
       <text>
         <r>
           <rPr>
@@ -5728,7 +6701,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{4780F23D-3420-46C0-BD73-C4050B77B45A}">
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{448E421B-66BD-4CA7-B88B-9F2FB353DE97}">
       <text>
         <r>
           <rPr>
@@ -5752,7 +6725,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{252B1441-0F40-4A84-B964-B8C15CE9C2DE}">
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{5AF20AF2-9237-43D2-A95B-C798F84C0A97}">
       <text>
         <r>
           <rPr>
@@ -5776,7 +6749,55 @@
         </r>
       </text>
     </comment>
+    <comment ref="E64" authorId="0" shapeId="0" xr:uid="{99763706-AB36-423D-B603-89A180EBF315}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E65" authorId="0" shapeId="0" xr:uid="{4B855F12-6C36-4B60-815A-EB7307931232}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E66" authorId="0" shapeId="0" xr:uid="{25A25BB3-9D28-4E6F-BCBE-6E99FF6C1210}">
       <text>
         <r>
           <rPr>
@@ -6877,150 +7898,53 @@
         </r>
       </text>
     </comment>
-    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{2B111FF6-32AF-490F-BF45-36D6B2F617ED}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{76D98853-BB8C-4B0C-BAE1-222B40A58BCE}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-RRR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{8028E63A-8F6D-4DD5-9FD7-7B268382BCB5}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-RRR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{37DC67B4-781D-46AE-85D0-650BF89D9901}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{BEE86973-7582-48DF-9D80-A64B6CDE2F47}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-RRR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{1FD6EAE0-2A34-4907-922D-670FC38A8C50}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-RRR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
+    <comment ref="F18" authorId="1" shapeId="0" xr:uid="{CD5241BA-7E8D-4462-ABA4-B2922B52C11D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+AIR 2024, prevalence of wasting OR 0.89 (0.80, 0.99). Cash transfers (cash only), unconditional or conditional.
+Converted to 1-RR using setting-specific prevalence. Assumes baseline intervention coverage is low</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="1" shapeId="0" xr:uid="{5CAB40CA-B365-420C-86B5-CA0D2244D888}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+AIR 2024, prevalence of wasting OR 0.89 (0.80, 0.99). Cash transfers (cash only), unconditional or conditional.
+Converted to 1-RR using setting-specific prevalence. Assumes baseline intervention coverage is low</t>
         </r>
       </text>
     </comment>
@@ -8175,7 +9099,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{2EF31D2B-EE72-4E50-B73F-6BB854BF1596}">
+    <comment ref="F73" authorId="1" shapeId="0" xr:uid="{12D3E130-78C1-4018-877C-57E4727FDB78}">
       <text>
         <r>
           <rPr>
@@ -8185,7 +9109,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
+          <t>Nick Scott:</t>
         </r>
         <r>
           <rPr>
@@ -8195,12 +9119,12 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-RR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{AA7B5B79-0EF5-4B80-ADA3-6BB092050B1F}">
+AIR 2024, prevalence of wasting OR 0.89 (0.80, 0.99). Cash transfers (cash only), unconditional or conditional.
+Converted to 1-RR using setting-specific prevalence. Assumes baseline intervention coverage is low</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F75" authorId="1" shapeId="0" xr:uid="{4BA56D8C-26E2-475E-A5E1-3FAFF6E9026B}">
       <text>
         <r>
           <rPr>
@@ -8210,7 +9134,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
+          <t>Nick Scott:</t>
         </r>
         <r>
           <rPr>
@@ -8220,105 +9144,8 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-RR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H73" authorId="0" shapeId="0" xr:uid="{A23A97FE-F160-4FAF-A5C6-044B27899A4E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F75" authorId="0" shapeId="0" xr:uid="{D5765185-45BB-48A7-8BFA-49E29B1C9F07}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G75" authorId="0" shapeId="0" xr:uid="{AA6A188C-A883-4D96-A686-6C77878183D8}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H75" authorId="0" shapeId="0" xr:uid="{971DF49E-F060-486E-9A67-11CA7117B586}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
+AIR 2024, prevalence of wasting OR 0.89 (0.80, 0.99). Cash transfers (cash only), unconditional or conditional.
+Converted to 1-RR using setting-specific prevalence. Assumes baseline intervention coverage is low</t>
         </r>
       </text>
     </comment>
@@ -9353,7 +10180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F128" authorId="0" shapeId="0" xr:uid="{C41D4345-94EC-4C3D-BAC5-55251871261A}">
+    <comment ref="F128" authorId="1" shapeId="0" xr:uid="{0505E57F-55CF-4368-8509-A3CBC586A661}">
       <text>
         <r>
           <rPr>
@@ -9363,7 +10190,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
+          <t>Nick Scott:</t>
         </r>
         <r>
           <rPr>
@@ -9373,12 +10200,12 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-RR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G128" authorId="0" shapeId="0" xr:uid="{E5EACFBE-BDC4-44B9-A7FA-E1488BEEEAB7}">
+AIR 2024, prevalence of wasting OR 0.89 (0.80, 0.99). Cash transfers (cash only), unconditional or conditional.
+Converted to 1-RR using setting-specific prevalence. Assumes baseline intervention coverage is low</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F130" authorId="1" shapeId="0" xr:uid="{775EE633-76A8-41FB-B903-2E128613C2F4}">
       <text>
         <r>
           <rPr>
@@ -9388,7 +10215,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
+          <t>Nick Scott:</t>
         </r>
         <r>
           <rPr>
@@ -9398,105 +10225,8 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-RR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H128" authorId="0" shapeId="0" xr:uid="{3E9D0706-9699-486E-AFE7-CA48FAE26B20}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.32 (0.16-0.61) for SAM incidence 
-Langendorf et al. 2014</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F130" authorId="0" shapeId="0" xr:uid="{66F6E996-8793-4164-B934-3FE8FCAFEAE3}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G130" authorId="0" shapeId="0" xr:uid="{03906487-B396-4B62-B8FA-17ECA6B3B9D1}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H130" authorId="0" shapeId="0" xr:uid="{6E556D4E-A49C-4B50-A08F-779BAFC92048}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.40 (0.23-0.68) for MAM incidence Langendorf et al. 2014, PLoS Med </t>
+AIR 2024, prevalence of wasting OR 0.89 (0.80, 0.99). Cash transfers (cash only), unconditional or conditional.
+Converted to 1-RR using setting-specific prevalence. Assumes baseline intervention coverage is low</t>
         </r>
       </text>
     </comment>
@@ -10129,12 +10859,312 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
+Not statistically significant from Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
+RRR=1-1*0.17=0.83</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{06D1C44F-322F-4250-B3A0-5CA1DD139792}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Not statistically significant from Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
+RRR=1-1*0.17=0.83</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{2316F266-D52E-4626-AADC-A82258451B11}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Not statistically significant from Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
+RRR=1-1*0.17=0.83</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{C9FD3895-C876-4843-9135-73283F7BAC05}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Not statistically significant from Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
+RRR=1-1*0.17=0.83</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{DBC8EAB4-C899-4BBC-A4E3-6534A9F2F203}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
+1-RR was used</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{0820F85D-9E73-4A1A-B6F6-C5F5DD2CE081}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
+1-RR was used</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{BCDE0D77-A36F-4E35-8550-F83F97EE1626}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
+1-RR was used</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{CE31B658-B0F4-4C26-A7D3-BDCC437F45BD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
+1-RR was used</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{1A51A655-115C-46D3-8BEC-D1321F203EF7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
+1-RR was used</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{20CEB4DE-F378-42D4-AFE1-DE0F6124BCC4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
+1-RR was used</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{F289026A-BAA6-40BC-8CB3-4B50E93AE045}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
+1-RR was used</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{B891291C-D76B-4BA8-A489-F5A6DD80C9AE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
+1-RR was used</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{EC946BD0-74CB-4126-AD0A-06ECB3478EB9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
 Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
 RRR=1-1*0.17=0.83</t>
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{9A71D084-A2DD-4EDA-9211-F5D5AE1346E9}">
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{541E11DF-9974-4387-8BC9-BDDAECDA040F}">
       <text>
         <r>
           <rPr>
@@ -10159,7 +11189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{7B22FC18-B278-4AB2-BDF9-F8817A4174C5}">
+    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{1AABDF78-4D8B-4FC7-97DD-58CBEADBE7BA}">
       <text>
         <r>
           <rPr>
@@ -10184,7 +11214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{AEFD8D38-12E3-4BC8-81DB-1DB99406E5E8}">
+    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{5CBA35A5-780D-433D-BC55-B72A13DBD931}">
       <text>
         <r>
           <rPr>
@@ -10209,207 +11239,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{DBC8EAB4-C899-4BBC-A4E3-6534A9F2F203}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
-1-RR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{0820F85D-9E73-4A1A-B6F6-C5F5DD2CE081}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
-1-RR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{BCDE0D77-A36F-4E35-8550-F83F97EE1626}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
-1-RR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{CE31B658-B0F4-4C26-A7D3-BDCC437F45BD}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
-1-RR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{1A51A655-115C-46D3-8BEC-D1321F203EF7}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
-1-RR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{20CEB4DE-F378-42D4-AFE1-DE0F6124BCC4}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
-1-RR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{F289026A-BAA6-40BC-8CB3-4B50E93AE045}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
-1-RR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{B891291C-D76B-4BA8-A489-F5A6DD80C9AE}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-RR = 0.41 for mortlaity from hypertensive disorders [Ronsmans et al. 2011, BMC Public Health] 
-1-RR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{EC946BD0-74CB-4126-AD0A-06ECB3478EB9}">
+    <comment ref="D21" authorId="0" shapeId="0" xr:uid="{27471D75-5386-4823-96A1-95168EDC6FA3}">
       <text>
         <r>
           <rPr>
@@ -10434,7 +11264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{541E11DF-9974-4387-8BC9-BDDAECDA040F}">
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{43FD30AE-661F-4270-8872-B297C7CFCB5A}">
       <text>
         <r>
           <rPr>
@@ -10459,7 +11289,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{1AABDF78-4D8B-4FC7-97DD-58CBEADBE7BA}">
+    <comment ref="F21" authorId="0" shapeId="0" xr:uid="{0B66076E-4643-42C8-9D0B-3074C6005DD8}">
       <text>
         <r>
           <rPr>
@@ -10484,107 +11314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{5CBA35A5-780D-433D-BC55-B72A13DBD931}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
-RRR=1-1*0.17=0.83</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D21" authorId="0" shapeId="0" xr:uid="{27471D75-5386-4823-96A1-95168EDC6FA3}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
-RRR=1-1*0.17=0.83</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{79696A72-1F7B-4916-A4C3-09F82414EB4C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
-RRR=1-1*0.17=0.83</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F21" authorId="0" shapeId="0" xr:uid="{B92DFDBB-68C7-41E1-931A-A5F42F0631FF}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Hofmeyr et al 2018, RR 0.17 (0.02-1.39)
-RRR=1-1*0.17=0.83</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G21" authorId="0" shapeId="0" xr:uid="{75DCCE96-0ADD-4B65-B69A-0B01405DC1AB}">
+    <comment ref="G21" authorId="0" shapeId="0" xr:uid="{2B2C0A0D-B7EC-451A-B28B-718901FC632A}">
       <text>
         <r>
           <rPr>
@@ -13019,7 +13749,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="341">
   <si>
     <t>year</t>
   </si>
@@ -18834,23 +19564,39 @@
       <c r="C5" s="64"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="67"/>
-      <c r="B6" s="68"/>
+      <c r="A6" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>337</v>
+      </c>
       <c r="C6" s="68"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="67"/>
-      <c r="B7" s="68"/>
+      <c r="A7" s="67" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="68" t="s">
+        <v>337</v>
+      </c>
       <c r="C7" s="68"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="67"/>
-      <c r="B8" s="68"/>
+      <c r="A8" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="68" t="s">
+        <v>337</v>
+      </c>
       <c r="C8" s="68"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="67"/>
-      <c r="B9" s="68"/>
+      <c r="A9" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="68" t="s">
+        <v>337</v>
+      </c>
       <c r="C9" s="68"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -18974,7 +19720,9 @@
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36"/>
+      <c r="A10" s="36" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="36"/>
@@ -31547,7 +32295,7 @@
         <v>161</v>
       </c>
       <c r="D66" s="105">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="E66" s="104">
         <v>1</v>
@@ -31662,7 +32410,7 @@
         <v>161</v>
       </c>
       <c r="D70" s="105">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="E70" s="104">
         <v>1</v>
@@ -31777,7 +32525,7 @@
         <v>161</v>
       </c>
       <c r="D74" s="105">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="E74" s="104">
         <v>1</v>
@@ -34280,7 +35028,7 @@
       </c>
       <c r="D176" s="106">
         <f>IF(D66=1,1,D66*0.9)</f>
-        <v>1.2150000000000001</v>
+        <v>1</v>
       </c>
       <c r="E176" s="106">
         <f t="shared" ref="E176:G176" si="54">IF(E66=1,1,E66*0.9)</f>
@@ -34379,7 +35127,7 @@
       </c>
       <c r="D180" s="106">
         <f t="shared" ref="D180:G180" si="58">IF(D70=1,1,D70*0.9)</f>
-        <v>1.2150000000000001</v>
+        <v>1</v>
       </c>
       <c r="E180" s="106">
         <f t="shared" si="58"/>
@@ -34478,7 +35226,7 @@
       </c>
       <c r="D184" s="106">
         <f t="shared" ref="D184:G184" si="62">IF(D74=1,1,D74*0.9)</f>
-        <v>1.2150000000000001</v>
+        <v>1</v>
       </c>
       <c r="E184" s="106">
         <f t="shared" si="62"/>
@@ -36906,7 +37654,7 @@
       </c>
       <c r="D286" s="106">
         <f>IF(D66=1,1,D66*1.1)</f>
-        <v>1.4850000000000003</v>
+        <v>1</v>
       </c>
       <c r="E286" s="106">
         <f t="shared" ref="E286:G286" si="148">IF(E66=1,1,E66*1.1)</f>
@@ -37009,7 +37757,7 @@
       </c>
       <c r="D290" s="106">
         <f t="shared" ref="D290:G290" si="152">IF(D70=1,1,D70*1.1)</f>
-        <v>1.4850000000000003</v>
+        <v>1</v>
       </c>
       <c r="E290" s="106">
         <f t="shared" si="152"/>
@@ -37112,7 +37860,7 @@
       </c>
       <c r="D294" s="106">
         <f t="shared" ref="D294:G294" si="156">IF(D74=1,1,D74*1.1)</f>
-        <v>1.4850000000000003</v>
+        <v>1</v>
       </c>
       <c r="E294" s="106">
         <f t="shared" si="156"/>
@@ -37966,7 +38714,7 @@
       <c r="I328" s="93"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1gEiboypgN1VYdmLYuHEsviiXDH91vsC32xKqzOEbclcsh2pOXs0vX071vry3NRJsC+T2/BNfpXbXWW7dldjVQ==" saltValue="XZihSWmo245BlR0GYalydw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1tfvvRE4M+vgwC7GiVJh8UWd9rYaMO2ID4FVARJWfxoJZRuabSnv5aYZjF5gU5Dq8AfGZ9OiwIwkdIqKnd3j8Q==" saltValue="gOCxMG9BScL982qe3BaWhw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
@@ -38197,19 +38945,19 @@
         <v>249</v>
       </c>
       <c r="C15" s="105">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="D15" s="105">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="E15" s="105">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="F15" s="105">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="G15" s="105">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -38218,19 +38966,19 @@
         <v>250</v>
       </c>
       <c r="C16" s="105">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="D16" s="105">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="E16" s="105">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="F16" s="105">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
       <c r="G16" s="105">
-        <v>1.0249999999999999</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -38360,24 +39108,19 @@
         <v>278</v>
       </c>
       <c r="C27" s="105">
-        <f>IF(C4=1,1,C4*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="D27" s="105">
-        <f t="shared" ref="D27:G27" si="1">IF(D4=1,1,D4*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="E27" s="105">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="F27" s="105">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
       <c r="G27" s="105">
-        <f t="shared" si="1"/>
-        <v>0.92249999999999999</v>
+        <v>1.014</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -38394,7 +39137,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="105">
-        <f t="shared" ref="D29:G29" si="2">IF(D6=1,1,D6*0.9)</f>
+        <f t="shared" ref="D29:G29" si="1">IF(D6=1,1,D6*0.9)</f>
         <v>1</v>
       </c>
       <c r="E29" s="105">
@@ -38406,7 +39149,7 @@
         <v>0.80100000000000005</v>
       </c>
       <c r="G29" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -38415,11 +39158,11 @@
         <v>280</v>
       </c>
       <c r="C30" s="105">
-        <f t="shared" ref="C30:G30" si="3">IF(C7=1,1,C7*0.9)</f>
+        <f t="shared" ref="C30:G30" si="2">IF(C7=1,1,C7*0.9)</f>
         <v>1</v>
       </c>
       <c r="D30" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E30" s="105">
@@ -38429,7 +39172,7 @@
         <v>0.85</v>
       </c>
       <c r="G30" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -38438,11 +39181,11 @@
         <v>338</v>
       </c>
       <c r="C31" s="105">
-        <f t="shared" ref="C31:G31" si="4">IF(C8=1,1,C8*0.9)</f>
+        <f t="shared" ref="C31:G31" si="3">IF(C8=1,1,C8*0.9)</f>
         <v>1</v>
       </c>
       <c r="D31" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E31" s="105">
@@ -38452,7 +39195,7 @@
         <v>0.85</v>
       </c>
       <c r="G31" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -38461,23 +39204,23 @@
         <v>281</v>
       </c>
       <c r="C32" s="105">
-        <f t="shared" ref="C32:G32" si="5">IF(C9=1,1,C9*0.9)</f>
+        <f t="shared" ref="C32:G32" si="4">IF(C9=1,1,C9*0.9)</f>
         <v>1</v>
       </c>
       <c r="D32" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E32" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="F32" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G32" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -38544,24 +39287,19 @@
         <v>283</v>
       </c>
       <c r="C38" s="105">
-        <f>IF(C15=1,1,C15*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="D38" s="105">
-        <f t="shared" ref="D38:G38" si="6">IF(D15=1,1,D15*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="E38" s="105">
-        <f t="shared" si="6"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="F38" s="105">
-        <f t="shared" si="6"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="G38" s="105">
-        <f t="shared" si="6"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -38570,24 +39308,19 @@
         <v>284</v>
       </c>
       <c r="C39" s="105">
-        <f t="shared" ref="C39:G39" si="7">IF(C16=1,1,C16*0.9)</f>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="D39" s="105">
-        <f t="shared" si="7"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="E39" s="105">
-        <f t="shared" si="7"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="F39" s="105">
-        <f t="shared" si="7"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
       <c r="G39" s="105">
-        <f t="shared" si="7"/>
-        <v>0.92249999999999999</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -38598,23 +39331,23 @@
         <v>285</v>
       </c>
       <c r="C40" s="105">
-        <f t="shared" ref="C40:G40" si="8">IF(C17=1,1,C17*0.9)</f>
+        <f t="shared" ref="C40:G40" si="5">IF(C17=1,1,C17*0.9)</f>
         <v>1</v>
       </c>
       <c r="D40" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E40" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F40" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G40" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -38709,19 +39442,19 @@
         <v>244</v>
       </c>
       <c r="D49" s="105">
-        <f t="shared" ref="D49:G50" si="9">D3*1.05</f>
+        <f t="shared" ref="D49:G49" si="6">D3*1.05</f>
         <v>47.25</v>
       </c>
       <c r="E49" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>379.68000000000006</v>
       </c>
       <c r="F49" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>183.435</v>
       </c>
       <c r="G49" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>183.435</v>
       </c>
     </row>
@@ -38731,24 +39464,19 @@
         <v>288</v>
       </c>
       <c r="C50" s="105">
-        <f>C4*1.05</f>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="D50" s="105">
-        <f t="shared" si="9"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="E50" s="105">
-        <f t="shared" si="9"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="F50" s="105">
-        <f t="shared" si="9"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
       <c r="G50" s="105">
-        <f t="shared" si="9"/>
-        <v>1.0762499999999999</v>
+        <v>1.0349999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -38765,7 +39493,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="105">
-        <f t="shared" ref="D52:G52" si="10">IF(D6=1,1,D6*1.1)</f>
+        <f t="shared" ref="D52:G52" si="7">IF(D6=1,1,D6*1.1)</f>
         <v>1</v>
       </c>
       <c r="E52" s="105">
@@ -38777,7 +39505,7 @@
         <v>0.93450000000000011</v>
       </c>
       <c r="G52" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -38786,11 +39514,11 @@
         <v>290</v>
       </c>
       <c r="C53" s="105">
-        <f t="shared" ref="C53:G53" si="11">IF(C7=1,1,C7*1.1)</f>
+        <f t="shared" ref="C53:G53" si="8">IF(C7=1,1,C7*1.1)</f>
         <v>1</v>
       </c>
       <c r="D53" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E53" s="105">
@@ -38800,7 +39528,7 @@
         <v>0.91</v>
       </c>
       <c r="G53" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -38809,11 +39537,11 @@
         <v>339</v>
       </c>
       <c r="C54" s="105">
-        <f t="shared" ref="C54:G54" si="12">IF(C8=1,1,C8*1.1)</f>
+        <f t="shared" ref="C54:G54" si="9">IF(C8=1,1,C8*1.1)</f>
         <v>1</v>
       </c>
       <c r="D54" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="E54" s="105">
@@ -38823,7 +39551,7 @@
         <v>0.91</v>
       </c>
       <c r="G54" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -38832,23 +39560,23 @@
         <v>291</v>
       </c>
       <c r="C55" s="105">
-        <f t="shared" ref="C55:G55" si="13">IF(C9=1,1,C9*1.1)</f>
+        <f t="shared" ref="C55:G55" si="10">IF(C9=1,1,C9*1.1)</f>
         <v>1</v>
       </c>
       <c r="D55" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E55" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="F55" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="G55" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -38915,24 +39643,19 @@
         <v>293</v>
       </c>
       <c r="C61" s="105">
-        <f>IF(C15=1,1,C15*1.1)</f>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="D61" s="105">
-        <f t="shared" ref="D61:G61" si="14">IF(D15=1,1,D15*1.1)</f>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="E61" s="105">
-        <f t="shared" si="14"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="F61" s="105">
-        <f t="shared" si="14"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="G61" s="105">
-        <f t="shared" si="14"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -38941,24 +39664,19 @@
         <v>294</v>
       </c>
       <c r="C62" s="105">
-        <f t="shared" ref="C62:G62" si="15">IF(C16=1,1,C16*1.1)</f>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="D62" s="105">
-        <f t="shared" si="15"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="E62" s="105">
-        <f t="shared" si="15"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="F62" s="105">
-        <f t="shared" si="15"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="G62" s="105">
-        <f t="shared" si="15"/>
-        <v>1.1274999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="13" x14ac:dyDescent="0.3">
@@ -38969,23 +39687,23 @@
         <v>295</v>
       </c>
       <c r="C63" s="105">
-        <f t="shared" ref="C63:G63" si="16">IF(C17=1,1,C17*1.1)</f>
+        <f t="shared" ref="C63:G63" si="11">IF(C17=1,1,C17*1.1)</f>
         <v>1</v>
       </c>
       <c r="D63" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="E63" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="F63" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="G63" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -39036,11 +39754,11 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Z5W0iLQonUXgebQ0oBIAJiknKvZHIMnPuF1vh21+BfR+VnJC7YVzBoFQiTm+hEbHNMOFIRa563Ft7+Jm2vvcKg==" saltValue="MgosxU+mdCbdebb7wBaTKg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="3r0ndAu+RUH96hYdp6WO+AwhqNH3NdCl1iIQ1gOJediM4KZ6ZFChNm7EJWrxH9+qR/lxiuugH22Ay8HV8gJ1Ng==" saltValue="2Kh7azF7eJZU/t5Zk7zWnw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
-    <ignoredError sqref="D26:G26 C44 C50:G50 D49:G49 C61:G63 C27:G28 C38:G40 C52:D52 C32:G32 C30:D30 G30 C31:D31 G31 C55:G55 C53:D53 G53 C54:D54 G54 C29:D29 G29 G52" unlockedFormula="1"/>
+    <ignoredError sqref="D26:G26 C44 D49:G49 C63:G63 C28:G28 C40:G40 C52:D52 C32:G32 C30:D30 G30 C31:D31 G31 C55:G55 C53:D53 G53 C54:D54 G54 C29:D29 G29 G52" unlockedFormula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -40525,37 +41243,37 @@
         <v>1</v>
       </c>
       <c r="E18" s="105">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F18" s="105">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G18" s="105">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H18" s="105">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I18" s="105">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J18" s="105">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K18" s="105">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L18" s="105">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M18" s="105">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N18" s="105">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O18" s="105">
-        <v>1</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -40613,47 +41331,36 @@
         <v>1</v>
       </c>
       <c r="E20" s="105">
-        <f>E19</f>
         <v>0.97599999999999998</v>
       </c>
       <c r="F20" s="105">
-        <f t="shared" ref="F20:O20" si="1">F19</f>
         <v>0.97599999999999998</v>
       </c>
       <c r="G20" s="105">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="H20" s="105">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="I20" s="105">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="J20" s="105">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="K20" s="105">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="L20" s="105">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="M20" s="105">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="N20" s="105">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
       <c r="O20" s="105">
-        <f t="shared" si="1"/>
         <v>0.97599999999999998</v>
       </c>
     </row>
@@ -40765,47 +41472,47 @@
         <v>0.4</v>
       </c>
       <c r="E26" s="105">
-        <f t="shared" ref="E26:O26" si="2">IF(E3=1,1,E3*0.9)</f>
+        <f t="shared" ref="E26:O26" si="1">IF(E3=1,1,E3*0.9)</f>
         <v>1</v>
       </c>
       <c r="F26" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G26" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H26" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I26" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J26" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K26" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L26" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M26" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N26" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="O26" s="105">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -40814,23 +41521,23 @@
         <v>183</v>
       </c>
       <c r="C27" s="105">
-        <f t="shared" ref="C27:O27" si="3">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:O34" si="2">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E27" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F27" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G27" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H27" s="105">
@@ -40846,19 +41553,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M27" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N27" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O27" s="105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -40867,23 +41574,23 @@
         <v>201</v>
       </c>
       <c r="C28" s="105">
-        <f t="shared" ref="C28:O28" si="4">IF(C5=1,1,C5*0.9)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D28" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E28" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F28" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G28" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H28" s="105">
@@ -40899,19 +41606,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M28" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N28" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O28" s="105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -40920,23 +41627,23 @@
         <v>184</v>
       </c>
       <c r="C29" s="105">
-        <f t="shared" ref="C29:O29" si="5">IF(C6=1,1,C6*0.9)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D29" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E29" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F29" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G29" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H29" s="105">
@@ -40952,19 +41659,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M29" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N29" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O29" s="105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -40973,23 +41680,23 @@
         <v>185</v>
       </c>
       <c r="C30" s="105">
-        <f t="shared" ref="C30:O30" si="6">IF(C7=1,1,C7*0.9)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D30" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E30" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F30" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G30" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H30" s="105">
@@ -41005,19 +41712,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M30" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N30" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O30" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -41026,39 +41733,39 @@
         <v>182</v>
       </c>
       <c r="C31" s="105">
-        <f t="shared" ref="C31:K31" si="7">IF(C8=1,1,C8*0.9)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D31" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E31" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F31" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G31" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H31" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I31" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J31" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K31" s="105">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L31" s="105">
@@ -41079,39 +41786,39 @@
         <v>202</v>
       </c>
       <c r="C32" s="105">
-        <f t="shared" ref="C32:K32" si="8">IF(C9=1,1,C9*0.9)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D32" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E32" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F32" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G32" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H32" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I32" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J32" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K32" s="105">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L32" s="105">
@@ -41132,39 +41839,39 @@
         <v>57</v>
       </c>
       <c r="C33" s="105">
-        <f t="shared" ref="C33:K33" si="9">IF(C10=1,1,C10*0.9)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D33" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E33" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F33" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G33" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H33" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I33" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J33" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K33" s="105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L33" s="105">
@@ -41185,11 +41892,11 @@
         <v>131</v>
       </c>
       <c r="C34" s="105">
-        <f t="shared" ref="C34:O34" si="10">IF(C11=1,1,C11*0.9)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D34" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E34" s="105">
@@ -41202,35 +41909,35 @@
         <v>1</v>
       </c>
       <c r="H34" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I34" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J34" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="K34" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L34" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M34" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N34" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O34" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -41283,11 +41990,11 @@
         <v>132</v>
       </c>
       <c r="C36" s="105">
-        <f t="shared" ref="C36:O36" si="11">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:O38" si="3">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E36" s="105">
@@ -41300,35 +42007,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I36" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J36" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K36" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L36" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M36" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N36" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O36" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -41337,39 +42044,39 @@
         <v>59</v>
       </c>
       <c r="C37" s="105">
-        <f t="shared" ref="C37:K37" si="12">IF(C14=1,1,C14*0.9)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D37" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E37" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F37" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G37" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H37" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I37" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J37" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K37" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L37" s="105">
@@ -41390,11 +42097,11 @@
         <v>337</v>
       </c>
       <c r="C38" s="105">
-        <f t="shared" ref="C38:O38" si="13">IF(C15=1,1,C15*0.9)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E38" s="105">
@@ -41404,39 +42111,39 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O38" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -41451,56 +42158,45 @@
         <v>63</v>
       </c>
       <c r="C41" s="105">
-        <f t="shared" ref="C41:O41" si="14">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:D41" si="4">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E41" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F41" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G41" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H41" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I41" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J41" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K41" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L41" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M41" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N41" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O41" s="105">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -41508,11 +42204,11 @@
         <v>64</v>
       </c>
       <c r="C42" s="105">
-        <f t="shared" ref="C42:D44" si="15">IF(C19=1,1,C19*0.9)</f>
+        <f t="shared" ref="C42:D44" si="5">IF(C19=1,1,C19*0.9)</f>
         <v>1</v>
       </c>
       <c r="D42" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E42" s="105">
@@ -41554,56 +42250,45 @@
         <v>62</v>
       </c>
       <c r="C43" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D43" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E43" s="105">
-        <f t="shared" ref="E43:O43" si="16">IF(E20=1,1,E20*0.9)</f>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F43" s="105">
-        <f t="shared" si="16"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G43" s="105">
-        <f t="shared" si="16"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H43" s="105">
-        <f t="shared" si="16"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I43" s="105">
-        <f t="shared" si="16"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J43" s="105">
-        <f t="shared" si="16"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K43" s="105">
-        <f t="shared" si="16"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L43" s="105">
-        <f t="shared" si="16"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M43" s="105">
-        <f t="shared" si="16"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N43" s="105">
-        <f t="shared" si="16"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O43" s="105">
-        <f t="shared" si="16"/>
-        <v>0.87839999999999996</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -41611,11 +42296,11 @@
         <v>47</v>
       </c>
       <c r="C44" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D44" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E44" s="105">
@@ -41716,47 +42401,47 @@
         <v>0.7</v>
       </c>
       <c r="E49" s="105">
-        <f t="shared" ref="E49:O49" si="17">IF(E3=1,1,E3*1.05)</f>
+        <f t="shared" ref="E49:O49" si="6">IF(E3=1,1,E3*1.05)</f>
         <v>1</v>
       </c>
       <c r="F49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O49" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -41765,23 +42450,23 @@
         <v>183</v>
       </c>
       <c r="C50" s="105">
-        <f t="shared" ref="C50:O50" si="18">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:O57" si="7">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H50" s="105">
@@ -41797,19 +42482,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O50" s="105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -41818,23 +42503,23 @@
         <v>201</v>
       </c>
       <c r="C51" s="105">
-        <f t="shared" ref="C51:O51" si="19">IF(C5=1,1,C5*1.05)</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H51" s="105">
@@ -41850,19 +42535,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O51" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -41871,23 +42556,23 @@
         <v>184</v>
       </c>
       <c r="C52" s="105">
-        <f t="shared" ref="C52:O52" si="20">IF(C6=1,1,C6*1.05)</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H52" s="105">
@@ -41903,19 +42588,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O52" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -41924,23 +42609,23 @@
         <v>185</v>
       </c>
       <c r="C53" s="105">
-        <f t="shared" ref="C53:O53" si="21">IF(C7=1,1,C7*1.05)</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H53" s="105">
@@ -41956,19 +42641,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O53" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -41977,39 +42662,39 @@
         <v>182</v>
       </c>
       <c r="C54" s="105">
-        <f t="shared" ref="C54:K54" si="22">IF(C8=1,1,C8*1.05)</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K54" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L54" s="105">
@@ -42030,39 +42715,39 @@
         <v>202</v>
       </c>
       <c r="C55" s="105">
-        <f t="shared" ref="C55:K55" si="23">IF(C9=1,1,C9*1.05)</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K55" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L55" s="105">
@@ -42083,39 +42768,39 @@
         <v>57</v>
       </c>
       <c r="C56" s="105">
-        <f t="shared" ref="C56:K56" si="24">IF(C10=1,1,C10*1.05)</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="F56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K56" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L56" s="105">
@@ -42136,11 +42821,11 @@
         <v>131</v>
       </c>
       <c r="C57" s="105">
-        <f t="shared" ref="C57:O57" si="25">IF(C11=1,1,C11*1.05)</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="D57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E57" s="105">
@@ -42150,39 +42835,39 @@
         <v>0.77</v>
       </c>
       <c r="G57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="M57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="N57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="O57" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -42235,11 +42920,11 @@
         <v>132</v>
       </c>
       <c r="C59" s="105">
-        <f t="shared" ref="C59:O59" si="26">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:O61" si="8">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E59" s="105">
@@ -42252,35 +42937,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="M59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O59" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -42289,39 +42974,39 @@
         <v>59</v>
       </c>
       <c r="C60" s="105">
-        <f t="shared" ref="C60:K60" si="27">IF(C14=1,1,C14*1.05)</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="F60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="G60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K60" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L60" s="105">
@@ -42342,11 +43027,11 @@
         <v>337</v>
       </c>
       <c r="C61" s="105">
-        <f t="shared" ref="C61:O61" si="28">IF(C15=1,1,C15*1.05)</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="D61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E61" s="105">
@@ -42356,39 +43041,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="M61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O61" s="105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -42403,56 +43088,45 @@
         <v>63</v>
       </c>
       <c r="C64" s="105">
-        <f t="shared" ref="C64:O64" si="29">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:D64" si="9">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="E64" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F64" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G64" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H64" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I64" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J64" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K64" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L64" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M64" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N64" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O64" s="105">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="65" spans="2:15" x14ac:dyDescent="0.25">
@@ -42460,11 +43134,11 @@
         <v>64</v>
       </c>
       <c r="C65" s="105">
-        <f t="shared" ref="C65:D67" si="30">IF(C19=1,1,C19*1.05)</f>
+        <f t="shared" ref="C65:D67" si="10">IF(C19=1,1,C19*1.05)</f>
         <v>1</v>
       </c>
       <c r="D65" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E65" s="105">
@@ -42506,56 +43180,45 @@
         <v>62</v>
       </c>
       <c r="C66" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D66" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E66" s="105">
-        <f t="shared" ref="E66:O66" si="31">IF(E20=1,1,E20*1.05)</f>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F66" s="105">
-        <f t="shared" si="31"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G66" s="105">
-        <f t="shared" si="31"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H66" s="105">
-        <f t="shared" si="31"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I66" s="105">
-        <f t="shared" si="31"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J66" s="105">
-        <f t="shared" si="31"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K66" s="105">
-        <f t="shared" si="31"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L66" s="105">
-        <f t="shared" si="31"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M66" s="105">
-        <f t="shared" si="31"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N66" s="105">
-        <f t="shared" si="31"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O66" s="105">
-        <f t="shared" si="31"/>
-        <v>1.0247999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.25">
@@ -42563,11 +43226,11 @@
         <v>47</v>
       </c>
       <c r="C67" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D67" s="105">
-        <f t="shared" si="30"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E67" s="105">
@@ -42605,7 +43268,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Z+I5w7Zv8b/t9kdTHtfTBlYoSm79UCEUpz3ShmnqEGsFIWvoyqli8qZ/O3UtxFRtNUOisgC6wk7M7CD5q+6g2w==" saltValue="qncMJDCOHin5ZX0oUaABDg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="YpA6JbbIyNNCAAhRjaoEttkYgV7fGrwEhDjKYZ2OCSpwzWlm782Eof8cRr+Z8CHrTCidfma6dSt/f77dCElh7Q==" saltValue="MkDqdd5l6/bsAXXLurhBUw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
@@ -43311,13 +43974,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="105">
-        <v>0.68</v>
+        <f>MIN(MAX(1-0.89/(1-frac_sam_6_11months+(frac_sam_6_11months*0.89)),0),1)</f>
+        <v>0.10999999999999999</v>
       </c>
       <c r="G18" s="105">
-        <v>0.68</v>
+        <f>MIN(MAX(1-0.89/(1-frac_sam_12_23months+(frac_sam_12_23months*0.89)),0),1)</f>
+        <v>0.10999999999999999</v>
       </c>
       <c r="H18" s="105">
-        <v>0.68</v>
+        <f>MIN(MAX(1-0.89/(1-frac_sam_24_59months+(frac_sam_24_59months*0.89)),0),1)</f>
+        <v>0.10999999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -43354,13 +44020,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="105">
-        <v>0.6</v>
+        <f>MIN(MAX(1-0.89/(1-frac_mam_6_11months+(frac_mam_6_11months*0.89)),0),1)</f>
+        <v>0.10999999999999999</v>
       </c>
       <c r="G20" s="105">
-        <v>0.6</v>
+        <f>MIN(MAX(1-0.89/(1-frac_mam_12_23months+(frac_mam_12_23months*0.89)),0),1)</f>
+        <v>0.10999999999999999</v>
       </c>
       <c r="H20" s="105">
-        <v>0.6</v>
+        <f>MIN(MAX(1-0.89/(1-frac_mam_24_59months+(frac_mam_24_59months*0.89)),0),1)</f>
+        <v>0.10999999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -44528,13 +45197,16 @@
         <v>0</v>
       </c>
       <c r="F73" s="105">
-        <v>0.39</v>
+        <f>MIN(MAX(1-0.99/(1-frac_sam_6_11months+(frac_sam_6_11months*0.99)),0),1)</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="G73" s="105">
-        <v>0.39</v>
+        <f>MIN(MAX(1-0.99/(1-frac_sam_12_23months+(frac_sam_12_23months*0.99)),0),1)</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="H73" s="105">
-        <v>0.39</v>
+        <f>MIN(MAX(1-0.99/(1-frac_sam_24_59months+(frac_sam_24_59months*0.99)),0),1)</f>
+        <v>1.0000000000000009E-2</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -44545,7 +45217,7 @@
         <v>261</v>
       </c>
       <c r="D74" s="105">
-        <f t="shared" ref="D74:G74" si="8">IF($C19="Affected fraction",D19,IF(D19=1,1,D19*0.9))</f>
+        <f t="shared" ref="D74:E74" si="8">IF($C19="Affected fraction",D19,IF(D19=1,1,D19*0.9))</f>
         <v>0</v>
       </c>
       <c r="E74" s="105">
@@ -44553,15 +45225,12 @@
         <v>0</v>
       </c>
       <c r="F74" s="105">
-        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="G74" s="105">
-        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="H74" s="105">
-        <f t="shared" ref="H74" si="9">IF($C19="Affected fraction",H19,IF(H19=1,1,H19*0.9))</f>
         <v>1</v>
       </c>
     </row>
@@ -44570,21 +45239,24 @@
         <v>263</v>
       </c>
       <c r="D75" s="105">
-        <f t="shared" ref="D75:E75" si="10">IF($C20="Affected fraction",D20,IF(D20=1,1,D20*0.9))</f>
+        <f t="shared" ref="D75:E75" si="9">IF($C20="Affected fraction",D20,IF(D20=1,1,D20*0.9))</f>
         <v>0</v>
       </c>
       <c r="E75" s="105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F75" s="105">
-        <v>0.32</v>
+        <f>MIN(MAX(1-0.99/(1-frac_mam_6_11months+(frac_mam_6_11months*0.99)),0),1)</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="G75" s="105">
-        <v>0.32</v>
+        <f>MIN(MAX(1-0.99/(1-frac_mam_12_23months+(frac_mam_12_23months*0.99)),0),1)</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="H75" s="105">
-        <v>0.32</v>
+        <f>MIN(MAX(1-0.99/(1-frac_mam_24_59months+(frac_mam_24_59months*0.99)),0),1)</f>
+        <v>1.0000000000000009E-2</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -44598,23 +45270,23 @@
         <v>261</v>
       </c>
       <c r="D76" s="105">
-        <f t="shared" ref="D76:H76" si="11">IF($C21="Affected fraction",D21,IF(D21=1,1,D21*0.9))</f>
+        <f t="shared" ref="D76:H76" si="10">IF($C21="Affected fraction",D21,IF(D21=1,1,D21*0.9))</f>
         <v>1</v>
       </c>
       <c r="E76" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F76" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G76" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H76" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -44626,19 +45298,19 @@
         <v>0.11</v>
       </c>
       <c r="E77" s="105">
-        <f t="shared" ref="E77:H77" si="12">IF($C22="Affected fraction",E22,IF(E22=1,1,E22*0.9))</f>
+        <f t="shared" ref="E77:H77" si="11">IF($C22="Affected fraction",E22,IF(E22=1,1,E22*0.9))</f>
         <v>0</v>
       </c>
       <c r="F77" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="G77" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H77" s="105">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -44653,23 +45325,23 @@
         <v>261</v>
       </c>
       <c r="D78" s="105">
-        <f t="shared" ref="D78:H78" si="13">IF($C23="Affected fraction",D23,IF(D23=1,1,D23*0.9))</f>
+        <f t="shared" ref="D78:H78" si="12">IF($C23="Affected fraction",D23,IF(D23=1,1,D23*0.9))</f>
         <v>1</v>
       </c>
       <c r="E78" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F78" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G78" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H78" s="105">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -44681,19 +45353,19 @@
         <v>0.11</v>
       </c>
       <c r="E79" s="105">
-        <f t="shared" ref="E79:H79" si="14">IF($C24="Affected fraction",E24,IF(E24=1,1,E24*0.9))</f>
+        <f t="shared" ref="E79:H79" si="13">IF($C24="Affected fraction",E24,IF(E24=1,1,E24*0.9))</f>
         <v>0</v>
       </c>
       <c r="F79" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G79" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H79" s="105">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -44708,23 +45380,23 @@
         <v>261</v>
       </c>
       <c r="D80" s="105">
-        <f t="shared" ref="D80:H80" si="15">IF($C25="Affected fraction",D25,IF(D25=1,1,D25*0.9))</f>
+        <f t="shared" ref="D80:H80" si="14">IF($C25="Affected fraction",D25,IF(D25=1,1,D25*0.9))</f>
         <v>1</v>
       </c>
       <c r="E80" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F80" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="G80" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H80" s="105">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -44736,19 +45408,19 @@
         <v>0.11</v>
       </c>
       <c r="E81" s="105">
-        <f t="shared" ref="E81:H81" si="16">IF($C26="Affected fraction",E26,IF(E26=1,1,E26*0.9))</f>
+        <f t="shared" ref="E81:H81" si="15">IF($C26="Affected fraction",E26,IF(E26=1,1,E26*0.9))</f>
         <v>0</v>
       </c>
       <c r="F81" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G81" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H81" s="105">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -45093,23 +45765,23 @@
         <v>261</v>
       </c>
       <c r="D97" s="105">
-        <f t="shared" ref="D97:H97" si="17">IF($C42="Affected fraction",D42,IF(D42=1,1,D42*0.9))</f>
+        <f t="shared" ref="D97:H97" si="16">IF($C42="Affected fraction",D42,IF(D42=1,1,D42*0.9))</f>
         <v>0</v>
       </c>
       <c r="E97" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="F97" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="G97" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="H97" s="105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
     </row>
@@ -45402,19 +46074,19 @@
         <v>0</v>
       </c>
       <c r="E112" s="105">
-        <f t="shared" ref="E112" si="18">IF($C2="Affected fraction",E2,IF(E2=1,1,E2*1.05))</f>
+        <f t="shared" ref="E112" si="17">IF($C2="Affected fraction",E2,IF(E2=1,1,E2*1.05))</f>
         <v>0</v>
       </c>
       <c r="F112" s="105">
-        <f t="shared" ref="F112:H112" si="19">IF($C57="Affected fraction",F57,IF(F57=1,1,F57*0.9))</f>
+        <f t="shared" ref="F112:H112" si="18">IF($C57="Affected fraction",F57,IF(F57=1,1,F57*0.9))</f>
         <v>1</v>
       </c>
       <c r="G112" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H112" s="105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
@@ -45423,11 +46095,11 @@
         <v>262</v>
       </c>
       <c r="D113" s="105">
-        <f t="shared" ref="D113:E113" si="20">IF($C3="Affected fraction",D3,IF(D3=1,1,D3*1.05))</f>
+        <f t="shared" ref="D113:E113" si="19">IF($C3="Affected fraction",D3,IF(D3=1,1,D3*1.05))</f>
         <v>0</v>
       </c>
       <c r="E113" s="105">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F113" s="105">
@@ -45445,11 +46117,11 @@
         <v>263</v>
       </c>
       <c r="D114" s="105">
-        <f t="shared" ref="D114:E114" si="21">IF($C4="Affected fraction",D4,IF(D4=1,1,D4*1.05))</f>
+        <f t="shared" ref="D114:E114" si="20">IF($C4="Affected fraction",D4,IF(D4=1,1,D4*1.05))</f>
         <v>0</v>
       </c>
       <c r="E114" s="105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F114" s="105">
@@ -45671,11 +46343,11 @@
         <v>263</v>
       </c>
       <c r="D124" s="105">
-        <f t="shared" ref="D124:H124" si="22">IF($C14="Affected fraction",D14,IF(D14=1,1,D14*1.05))</f>
+        <f t="shared" ref="D124:H124" si="21">IF($C14="Affected fraction",D14,IF(D14=1,1,D14*1.05))</f>
         <v>0</v>
       </c>
       <c r="E124" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="F124" s="105">
@@ -45685,7 +46357,7 @@
         <v>0.45</v>
       </c>
       <c r="H124" s="105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -45697,23 +46369,23 @@
         <v>261</v>
       </c>
       <c r="D125" s="105">
-        <f t="shared" ref="D125:H125" si="23">IF($C15="Affected fraction",D15,IF(D15=1,1,D15*1.05))</f>
+        <f t="shared" ref="D125:H125" si="22">IF($C15="Affected fraction",D15,IF(D15=1,1,D15*1.05))</f>
         <v>0</v>
       </c>
       <c r="E125" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F125" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="G125" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="H125" s="105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -45722,11 +46394,11 @@
         <v>263</v>
       </c>
       <c r="D126" s="105">
-        <f t="shared" ref="D126:H126" si="24">IF($C16="Affected fraction",D16,IF(D16=1,1,D16*1.05))</f>
+        <f t="shared" ref="D126:H126" si="23">IF($C16="Affected fraction",D16,IF(D16=1,1,D16*1.05))</f>
         <v>0</v>
       </c>
       <c r="E126" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="F126" s="105">
@@ -45736,7 +46408,7 @@
         <v>0.2</v>
       </c>
       <c r="H126" s="105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -45751,23 +46423,23 @@
         <v>261</v>
       </c>
       <c r="D127" s="105">
-        <f t="shared" ref="D127:H127" si="25">IF($C17="Affected fraction",D17,IF(D17=1,1,D17*1.05))</f>
+        <f t="shared" ref="D127:H127" si="24">IF($C17="Affected fraction",D17,IF(D17=1,1,D17*1.05))</f>
         <v>0</v>
       </c>
       <c r="E127" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F127" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="G127" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="H127" s="105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
     </row>
@@ -45776,21 +46448,24 @@
         <v>263</v>
       </c>
       <c r="D128" s="105">
-        <f t="shared" ref="D128:E128" si="26">IF($C18="Affected fraction",D18,IF(D18=1,1,D18*1.05))</f>
+        <f t="shared" ref="D128:E128" si="25">IF($C18="Affected fraction",D18,IF(D18=1,1,D18*1.05))</f>
         <v>0</v>
       </c>
       <c r="E128" s="105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="F128" s="105">
-        <v>0.84</v>
+        <f>MIN(MAX(1-0.8/(1-frac_sam_6_11months+(frac_sam_6_11months*0.8)),0),1)</f>
+        <v>0.19999999999999996</v>
       </c>
       <c r="G128" s="105">
-        <v>0.84</v>
+        <f>MIN(MAX(1-0.8/(1-frac_sam_12_23months+(frac_sam_12_23months*0.8)),0),1)</f>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H128" s="105">
-        <v>0.84</v>
+        <f>MIN(MAX(1-0.8/(1-frac_sam_24_59months+(frac_sam_24_59months*0.8)),0),1)</f>
+        <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -45801,23 +46476,20 @@
         <v>261</v>
       </c>
       <c r="D129" s="105">
-        <f t="shared" ref="D129:E129" si="27">IF($C19="Affected fraction",D19,IF(D19=1,1,D19*1.05))</f>
+        <f t="shared" ref="D129:E129" si="26">IF($C19="Affected fraction",D19,IF(D19=1,1,D19*1.05))</f>
         <v>0</v>
       </c>
       <c r="E129" s="105">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="F129" s="105">
-        <f t="shared" ref="F129:H129" si="28">IF($C74="Affected fraction",F74,IF(F74=1,1,F74*0.9))</f>
         <v>1</v>
       </c>
       <c r="G129" s="105">
-        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="H129" s="105">
-        <f t="shared" si="28"/>
         <v>1</v>
       </c>
     </row>
@@ -45826,21 +46498,24 @@
         <v>263</v>
       </c>
       <c r="D130" s="105">
-        <f t="shared" ref="D130:E130" si="29">IF($C20="Affected fraction",D20,IF(D20=1,1,D20*1.05))</f>
+        <f t="shared" ref="D130:E130" si="27">IF($C20="Affected fraction",D20,IF(D20=1,1,D20*1.05))</f>
         <v>0</v>
       </c>
       <c r="E130" s="105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F130" s="105">
-        <v>0.77</v>
+        <f>MIN(MAX(1-0.8/(1-frac_mam_6_11months+(frac_mam_6_11months*0.8)),0),1)</f>
+        <v>0.19999999999999996</v>
       </c>
       <c r="G130" s="105">
-        <v>0.77</v>
+        <f>MIN(MAX(1-0.8/(1-frac_mam_12_23months+(frac_mam_12_23months*0.8)),0),1)</f>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H130" s="105">
-        <v>0.77</v>
+        <f>MIN(MAX(1-0.8/(1-frac_mam_24_59months+(frac_mam_24_59months*0.8)),0),1)</f>
+        <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -45854,23 +46529,23 @@
         <v>261</v>
       </c>
       <c r="D131" s="105">
-        <f t="shared" ref="D131" si="30">IF($C76="Affected fraction",D76,IF(D76=1,1,D76*0.9))</f>
+        <f t="shared" ref="D131" si="28">IF($C76="Affected fraction",D76,IF(D76=1,1,D76*0.9))</f>
         <v>1</v>
       </c>
       <c r="E131" s="105">
-        <f t="shared" ref="E131:H131" si="31">IF($C21="Affected fraction",E21,IF(E21=1,1,E21*1.05))</f>
+        <f t="shared" ref="E131:H131" si="29">IF($C21="Affected fraction",E21,IF(E21=1,1,E21*1.05))</f>
         <v>0</v>
       </c>
       <c r="F131" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="G131" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H131" s="105">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -45882,19 +46557,19 @@
         <v>0.16</v>
       </c>
       <c r="E132" s="105">
-        <f t="shared" ref="E132:H132" si="32">IF($C22="Affected fraction",E22,IF(E22=1,1,E22*1.05))</f>
+        <f t="shared" ref="E132:H132" si="30">IF($C22="Affected fraction",E22,IF(E22=1,1,E22*1.05))</f>
         <v>0</v>
       </c>
       <c r="F132" s="105">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G132" s="105">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H132" s="105">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -45909,23 +46584,23 @@
         <v>261</v>
       </c>
       <c r="D133" s="105">
-        <f t="shared" ref="D133" si="33">IF($C78="Affected fraction",D78,IF(D78=1,1,D78*0.9))</f>
+        <f t="shared" ref="D133" si="31">IF($C78="Affected fraction",D78,IF(D78=1,1,D78*0.9))</f>
         <v>1</v>
       </c>
       <c r="E133" s="105">
-        <f t="shared" ref="E133:H133" si="34">IF($C23="Affected fraction",E23,IF(E23=1,1,E23*1.05))</f>
+        <f t="shared" ref="E133:H133" si="32">IF($C23="Affected fraction",E23,IF(E23=1,1,E23*1.05))</f>
         <v>0</v>
       </c>
       <c r="F133" s="105">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="G133" s="105">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H133" s="105">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -45937,19 +46612,19 @@
         <v>0.16</v>
       </c>
       <c r="E134" s="105">
-        <f t="shared" ref="E134:H134" si="35">IF($C24="Affected fraction",E24,IF(E24=1,1,E24*1.05))</f>
+        <f t="shared" ref="E134:H134" si="33">IF($C24="Affected fraction",E24,IF(E24=1,1,E24*1.05))</f>
         <v>0</v>
       </c>
       <c r="F134" s="105">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="G134" s="105">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="H134" s="105">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -45964,23 +46639,23 @@
         <v>261</v>
       </c>
       <c r="D135" s="105">
-        <f t="shared" ref="D135" si="36">IF($C80="Affected fraction",D80,IF(D80=1,1,D80*0.9))</f>
+        <f t="shared" ref="D135" si="34">IF($C80="Affected fraction",D80,IF(D80=1,1,D80*0.9))</f>
         <v>1</v>
       </c>
       <c r="E135" s="105">
-        <f t="shared" ref="E135:H135" si="37">IF($C25="Affected fraction",E25,IF(E25=1,1,E25*1.05))</f>
+        <f t="shared" ref="E135:H135" si="35">IF($C25="Affected fraction",E25,IF(E25=1,1,E25*1.05))</f>
         <v>0</v>
       </c>
       <c r="F135" s="105">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="G135" s="105">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="H135" s="105">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -45992,19 +46667,19 @@
         <v>0.16</v>
       </c>
       <c r="E136" s="105">
-        <f t="shared" ref="E136:H136" si="38">IF($C26="Affected fraction",E26,IF(E26=1,1,E26*1.05))</f>
+        <f t="shared" ref="E136:H136" si="36">IF($C26="Affected fraction",E26,IF(E26=1,1,E26*1.05))</f>
         <v>0</v>
       </c>
       <c r="F136" s="105">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="G136" s="105">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H136" s="105">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
@@ -46349,23 +47024,23 @@
         <v>261</v>
       </c>
       <c r="D152" s="105">
-        <f t="shared" ref="D152:H152" si="39">IF($C97="Affected fraction",D97,IF(D97=1,1,D97*0.9))</f>
+        <f t="shared" ref="D152:H152" si="37">IF($C97="Affected fraction",D97,IF(D97=1,1,D97*0.9))</f>
         <v>0</v>
       </c>
       <c r="E152" s="105">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="F152" s="105">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="G152" s="105">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H152" s="105">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
     </row>
@@ -46374,23 +47049,23 @@
         <v>262</v>
       </c>
       <c r="D153" s="105">
-        <f t="shared" ref="D153:H153" si="40">IF($C98="Affected fraction",D98,IF(D98=1,1,D98*0.9))</f>
+        <f t="shared" ref="D153:H153" si="38">IF($C98="Affected fraction",D98,IF(D98=1,1,D98*0.9))</f>
         <v>0</v>
       </c>
       <c r="E153" s="105">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="F153" s="105">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="G153" s="105">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="H153" s="105">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
@@ -46616,11 +47291,11 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ogxQtq/9g6OeNkiNBs6ghJq8+LdVqsoK1CbSDtbSeFSK0ebg4cqAnXfIn86tuaNowgHjhLbE7woQSAqVYa5K1w==" saltValue="QFHNUEWTAfsZg09RvHfUXA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="W7trpA30YWk5Jr/jScHRObXHTbskGlEnvWYvD30IOj42vYmMSULI7hj5MMMzKmnRnjAoTPBVv8QyGss+btXRNg==" saltValue="rKtIaAjK8h4IDBxFHcbbkQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
-    <ignoredError sqref="D112:E112 E57:H57 D58:E58 D59:E59 D113:E113 D114:E114 D70:H70 D69:E69 H69 D72:H72 D71:E71 H71 D125:H125 D124:E124 H124 D127:H127 D126:E126 H126 D78:H78 E77:H77 D80:H80 E79:H79 D97:H97 E81:H81 E131:H136 D74:G74 D73:E73 D76:H76 D75:E75 D128:E130" unlockedFormula="1"/>
+    <ignoredError sqref="D112:E112 E57:H57 D58:E58 D59:E59 D113:E113 D114:E114 D70:H70 D69:E69 H69 D72:H72 D71:E71 H71 D125:H125 D124:E124 H124 D127:H127 D126:E126 H126 D78:H78 E77:H77 D80:H80 E79:H79 D97:H97 E81:H81 E131:H136 D74:E74 D73:E73 D76:H76 D75:E75 D128:E130" unlockedFormula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -46692,16 +47367,16 @@
         <v>262</v>
       </c>
       <c r="D3" s="105">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="E3" s="105">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="F3" s="105">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="G3" s="105">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="H3" s="32"/>
     </row>
@@ -47013,16 +47688,16 @@
         <v>262</v>
       </c>
       <c r="D21" s="105">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="E21" s="105">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="F21" s="105">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="G21" s="105">
-        <v>0.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -47122,7 +47797,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bFi4UO/MYSy1ocOot5y7JdpTLSj3VYrhdtuVEmlekdzp7NtFBQZX4yNIi9A9S9nFic+mLseFiB4QMgSz7PmPmQ==" saltValue="0Yi1KsKDfpD+pl5y1FWoHw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="K8oQd97EGTyELizd/OBv25NdUi0dfr+nHstdw1jgvK9KIw7xQQu4jOvKJk5azskLTZ5a8KxgKzCQTWejOXFNZg==" saltValue="W1MAFbsrhVC+a/zI9dICGA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="D20:G20 D11:G11 D13:G16 D22:G22 D24:G24" unlockedFormula="1"/>
@@ -48521,6 +49196,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MediaLengthInSeconds xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="107b52809c0cc4b5077f1ac81d3c69cc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="82b7e1b740270cfb0676be859a78f3d0" ns2:_="">
     <xsd:import namespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
@@ -48676,24 +49368,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87E89A13-0449-4026-BB40-CE009D889E15}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MediaLengthInSeconds xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F25ACC24-A23B-4F66-B2C3-F39116C08A35}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07F27224-E052-49D0-B72B-C9073A8D27C1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -48709,22 +49402,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87E89A13-0449-4026-BB40-CE009D889E15}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F25ACC24-A23B-4F66-B2C3-F39116C08A35}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/inputs/en/template_input.xlsx
+++ b/inputs/en/template_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\Nutrition\inputs\en\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE937B0-5846-4A73-B47E-3FCA624CE6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686DF5B5-CCE4-4F3E-84EB-47399811522A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="9" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="9" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline year population inputs" sheetId="1" r:id="rId1"/>
@@ -32,14 +32,14 @@
     <sheet name="Programs impacted population" sheetId="62" state="hidden" r:id="rId17"/>
     <sheet name="Program risk areas" sheetId="63" state="hidden" r:id="rId18"/>
     <sheet name="Population risk areas" sheetId="64" state="hidden" r:id="rId19"/>
-    <sheet name="IYCF odds ratios" sheetId="65" state="hidden" r:id="rId20"/>
+    <sheet name="IYCF odds ratios" sheetId="65" r:id="rId20"/>
     <sheet name="Birth outcome risks" sheetId="66" state="hidden" r:id="rId21"/>
     <sheet name="Relative risks" sheetId="67" r:id="rId22"/>
     <sheet name="Odds ratios" sheetId="68" r:id="rId23"/>
     <sheet name="Programs birth outcomes" sheetId="69" state="hidden" r:id="rId24"/>
-    <sheet name="Programs anaemia" sheetId="70" r:id="rId25"/>
+    <sheet name="Programs anaemia" sheetId="70" state="hidden" r:id="rId25"/>
     <sheet name="Programs wasting" sheetId="71" state="hidden" r:id="rId26"/>
-    <sheet name="Programs for children" sheetId="72" r:id="rId27"/>
+    <sheet name="Programs for children" sheetId="72" state="hidden" r:id="rId27"/>
     <sheet name="Programs for PW" sheetId="73" r:id="rId28"/>
   </sheets>
   <definedNames>
@@ -92,7 +92,7 @@
     <definedName name="term_SGA">'Baseline year population inputs'!$C$47</definedName>
     <definedName name="U5_mortality">'Baseline year population inputs'!$C$39</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1548,31 +1548,31 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="1" shapeId="0" xr:uid="{80ACFD6E-6E15-4465-8450-02C12E80A408}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-OR = 1.50 (1.26-1.78) for exclusive breastfeeding in children &lt; 1 month.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D12" authorId="1" shapeId="0" xr:uid="{3F25901D-4847-47DB-9D36-FCDEB14B8222}">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{E6FDF84E-3D11-4E70-83C8-F3597619C247}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Impact on &lt;1 month not considered to avoid double counting with the mortality benefits for this age group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="1" shapeId="0" xr:uid="{8D635818-F406-4CAE-A115-80A4E006529C}">
       <text>
         <r>
           <rPr>
@@ -1820,6 +1820,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="C35" authorId="0" shapeId="0" xr:uid="{0081E56F-AA05-44A7-AD3E-16DCCF8419BA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Impact on &lt;1 month not considered to avoid double counting with the mortality benefits for this age group</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="A37" authorId="1" shapeId="0" xr:uid="{9C9C28EB-E12B-4C9B-9084-AB7550B28024}">
       <text>
         <r>
@@ -2065,6 +2089,30 @@
           <t xml:space="preserve">
 Dewey et al 2021, stunting, PR 0.88 (0.85-0.91)  
 Converted to OR is prev. data inputs are available else RR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{4BEF5729-E89C-4BC0-851B-74D57A9BA550}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Impact on &lt;1 month not considered to avoid double counting with the mortality benefits for this age group</t>
         </r>
       </text>
     </comment>
@@ -3029,7 +3077,7 @@
     <author>Nick Scott</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{E5FA8BAD-93BF-409D-A7D5-AB8BEFDB8E24}">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{45A337A4-FF7C-4570-99C9-ADFCC16A29D0}">
       <text>
         <r>
           <rPr>
@@ -3049,7 +3097,57 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 );
+Assuming at least the same effect on younger group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{CF7396EE-A585-4103-A40A-B7211A54AD96}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 );
+Assuming at least the same effect on younger group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{EAB8438F-16BB-45F4-ACED-7B0E4241452C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -4639,7 +4737,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{8278CAA9-6D3F-47D1-BDAE-A9947B15A28F}">
+    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{41224EBC-F1AA-418B-B532-EF5C73BDB65F}">
       <text>
         <r>
           <rPr>
@@ -4659,7 +4757,57 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 );
+Assuming at least the same effect on younger group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{E62F37D1-31A0-47B4-BEB4-7E2FA599AD80}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 );
+Assuming at least the same effect on younger group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E26" authorId="0" shapeId="0" xr:uid="{838740CD-3310-41C9-B5DC-3D7BE5A74488}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -5592,7 +5740,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{3C7C01D7-6D29-42FA-8893-336D7F9A27EA}">
+    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{A96EF5BA-761A-4524-840D-9A3F70C10FB0}">
       <text>
         <r>
           <rPr>
@@ -5612,7 +5760,57 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 );
+Assuming at least the same effect on younger group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{E19FDBFD-3130-4EFE-95D7-8D93A2429DF8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 );
+Assuming at least the same effect on younger group</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{F3913CCC-CECF-40A2-9FEF-3CD1FE8698A7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Zhao et al 2019, 6-12 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -8023,6 +8221,131 @@
         </r>
       </text>
     </comment>
+    <comment ref="D28" authorId="1" shapeId="0" xr:uid="{982AA0D3-742C-40A6-A7FD-BC3CA735B008}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E28" authorId="1" shapeId="0" xr:uid="{688C221F-E3FD-4352-92B8-297CA8ACCC2C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F28" authorId="1" shapeId="0" xr:uid="{A15C74FD-0745-49C1-81D1-DE63A59E6E56}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G28" authorId="1" shapeId="0" xr:uid="{816DA7E9-3A71-4307-A495-59268FE7B2E5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H28" authorId="1" shapeId="0" xr:uid="{2146E23C-EA28-4CC0-A596-B42C3CE66A14}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D43" authorId="0" shapeId="0" xr:uid="{99A71181-D279-4717-8E4F-638D060FEA8C}">
       <text>
         <r>
@@ -9224,6 +9547,131 @@
         </r>
       </text>
     </comment>
+    <comment ref="D83" authorId="1" shapeId="0" xr:uid="{3FFA5C55-6349-4E86-B693-665E93994E51}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E83" authorId="1" shapeId="0" xr:uid="{20E4CCC9-88BF-465B-938D-6E3B27CCB20E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F83" authorId="1" shapeId="0" xr:uid="{AE734E7C-85D3-4322-8524-0CBCF321FA76}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G83" authorId="1" shapeId="0" xr:uid="{F4C339EF-36AA-4A18-B221-BC2F118695CE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H83" authorId="1" shapeId="0" xr:uid="{6A645D69-764D-42E9-AC2D-CD3B6FB5E85A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D99" authorId="0" shapeId="0" xr:uid="{0280DC98-C77C-49C3-8E69-CB8B06EC6EF3}">
       <text>
         <r>
@@ -10302,6 +10750,131 @@
           <t xml:space="preserve">
 RRR = 0.87 (0.84-0.89) of neonatal mortality [prevention of neural tube defects Blencowe et al. 2010, I J Epidemiology [81]]
 1-RRR was used</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D138" authorId="1" shapeId="0" xr:uid="{6F6E1181-10DD-42FF-9C70-FE274116F736}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E138" authorId="1" shapeId="0" xr:uid="{C04BAF7D-7FCE-4681-B207-62908C416F79}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F138" authorId="1" shapeId="0" xr:uid="{7F13252F-3409-4E6C-8F01-C002D14A8CD9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G138" authorId="1" shapeId="0" xr:uid="{62DB8744-7841-4BF3-AA0D-1947E0ABFF72}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H138" authorId="1" shapeId="0" xr:uid="{8FEAA011-6675-4E79-85B9-905C2A099816}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+OR on all-cause mortlality 0.70 (0.49-0.93)
+Kremer, M., Luby, S. P., Maertens, R., Tan, B., &amp; Więcek, W. (2023). Water treatment and child mortality: A meta-analysis and cost-effectiveness analysis (No. w30835). National Bureau of Economic Research.</t>
         </r>
       </text>
     </comment>
@@ -10836,10 +11409,35 @@
 <file path=xl/comments17.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>Nick Scott</author>
     <author>Tharindu Wickramaarachchi</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{DF98C925-BAB3-4853-B5FB-028B49229B3A}">
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{4AF61CA1-88F8-4A2D-AF4D-FE702C266CD4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Note: Ca supplementation impacts preterm birth, not curretly captured in the model Hofmeyr et al 2023, RR 0.76 (0.60-0.97), all women</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="1" shapeId="0" xr:uid="{DF98C925-BAB3-4853-B5FB-028B49229B3A}">
       <text>
         <r>
           <rPr>
@@ -10864,7 +11462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{06D1C44F-322F-4250-B3A0-5CA1DD139792}">
+    <comment ref="E3" authorId="1" shapeId="0" xr:uid="{06D1C44F-322F-4250-B3A0-5CA1DD139792}">
       <text>
         <r>
           <rPr>
@@ -10889,7 +11487,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{2316F266-D52E-4626-AADC-A82258451B11}">
+    <comment ref="F3" authorId="1" shapeId="0" xr:uid="{2316F266-D52E-4626-AADC-A82258451B11}">
       <text>
         <r>
           <rPr>
@@ -10914,7 +11512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{C9FD3895-C876-4843-9135-73283F7BAC05}">
+    <comment ref="G3" authorId="1" shapeId="0" xr:uid="{C9FD3895-C876-4843-9135-73283F7BAC05}">
       <text>
         <r>
           <rPr>
@@ -10939,7 +11537,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{DBC8EAB4-C899-4BBC-A4E3-6534A9F2F203}">
+    <comment ref="D5" authorId="1" shapeId="0" xr:uid="{DBC8EAB4-C899-4BBC-A4E3-6534A9F2F203}">
       <text>
         <r>
           <rPr>
@@ -10964,7 +11562,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{0820F85D-9E73-4A1A-B6F6-C5F5DD2CE081}">
+    <comment ref="E5" authorId="1" shapeId="0" xr:uid="{0820F85D-9E73-4A1A-B6F6-C5F5DD2CE081}">
       <text>
         <r>
           <rPr>
@@ -10989,7 +11587,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{BCDE0D77-A36F-4E35-8550-F83F97EE1626}">
+    <comment ref="F5" authorId="1" shapeId="0" xr:uid="{BCDE0D77-A36F-4E35-8550-F83F97EE1626}">
       <text>
         <r>
           <rPr>
@@ -11014,7 +11612,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{CE31B658-B0F4-4C26-A7D3-BDCC437F45BD}">
+    <comment ref="G5" authorId="1" shapeId="0" xr:uid="{CE31B658-B0F4-4C26-A7D3-BDCC437F45BD}">
       <text>
         <r>
           <rPr>
@@ -11039,7 +11637,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{1A51A655-115C-46D3-8BEC-D1321F203EF7}">
+    <comment ref="D7" authorId="1" shapeId="0" xr:uid="{1A51A655-115C-46D3-8BEC-D1321F203EF7}">
       <text>
         <r>
           <rPr>
@@ -11064,7 +11662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{20CEB4DE-F378-42D4-AFE1-DE0F6124BCC4}">
+    <comment ref="E7" authorId="1" shapeId="0" xr:uid="{20CEB4DE-F378-42D4-AFE1-DE0F6124BCC4}">
       <text>
         <r>
           <rPr>
@@ -11089,7 +11687,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{F289026A-BAA6-40BC-8CB3-4B50E93AE045}">
+    <comment ref="F7" authorId="1" shapeId="0" xr:uid="{F289026A-BAA6-40BC-8CB3-4B50E93AE045}">
       <text>
         <r>
           <rPr>
@@ -11114,7 +11712,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{B891291C-D76B-4BA8-A489-F5A6DD80C9AE}">
+    <comment ref="G7" authorId="1" shapeId="0" xr:uid="{B891291C-D76B-4BA8-A489-F5A6DD80C9AE}">
       <text>
         <r>
           <rPr>
@@ -11139,7 +11737,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{EC946BD0-74CB-4126-AD0A-06ECB3478EB9}">
+    <comment ref="D12" authorId="1" shapeId="0" xr:uid="{EC946BD0-74CB-4126-AD0A-06ECB3478EB9}">
       <text>
         <r>
           <rPr>
@@ -11164,7 +11762,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{541E11DF-9974-4387-8BC9-BDDAECDA040F}">
+    <comment ref="E12" authorId="1" shapeId="0" xr:uid="{541E11DF-9974-4387-8BC9-BDDAECDA040F}">
       <text>
         <r>
           <rPr>
@@ -11189,7 +11787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{1AABDF78-4D8B-4FC7-97DD-58CBEADBE7BA}">
+    <comment ref="F12" authorId="1" shapeId="0" xr:uid="{1AABDF78-4D8B-4FC7-97DD-58CBEADBE7BA}">
       <text>
         <r>
           <rPr>
@@ -11214,7 +11812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{5CBA35A5-780D-433D-BC55-B72A13DBD931}">
+    <comment ref="G12" authorId="1" shapeId="0" xr:uid="{5CBA35A5-780D-433D-BC55-B72A13DBD931}">
       <text>
         <r>
           <rPr>
@@ -11239,7 +11837,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D21" authorId="0" shapeId="0" xr:uid="{27471D75-5386-4823-96A1-95168EDC6FA3}">
+    <comment ref="D21" authorId="1" shapeId="0" xr:uid="{27471D75-5386-4823-96A1-95168EDC6FA3}">
       <text>
         <r>
           <rPr>
@@ -11264,7 +11862,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{43FD30AE-661F-4270-8872-B297C7CFCB5A}">
+    <comment ref="E21" authorId="1" shapeId="0" xr:uid="{43FD30AE-661F-4270-8872-B297C7CFCB5A}">
       <text>
         <r>
           <rPr>
@@ -11289,7 +11887,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F21" authorId="0" shapeId="0" xr:uid="{0B66076E-4643-42C8-9D0B-3074C6005DD8}">
+    <comment ref="F21" authorId="1" shapeId="0" xr:uid="{0B66076E-4643-42C8-9D0B-3074C6005DD8}">
       <text>
         <r>
           <rPr>
@@ -11314,7 +11912,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G21" authorId="0" shapeId="0" xr:uid="{2B2C0A0D-B7EC-451A-B28B-718901FC632A}">
+    <comment ref="G21" authorId="1" shapeId="0" xr:uid="{2B2C0A0D-B7EC-451A-B28B-718901FC632A}">
       <text>
         <r>
           <rPr>
@@ -12968,203 +13566,203 @@
 <file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>Nick Scott</author>
     <author>Tharindu Wickramaarachchi</author>
-    <author>Nick Scott</author>
   </authors>
   <commentList>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{8A55B1A6-998D-42DE-B0E4-F240F12DC066}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{4763D3C6-2461-434E-A9CE-8176C3AEEEC0}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{D2793965-226C-4498-9C0C-8763958E0A0E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{70344548-3959-4495-A5BD-FC2105C0CA4C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{934311F3-3119-4762-A57B-B5D8D98FBE77}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{CB0B6DF7-1160-43EE-9BA1-46B5A8F8A379}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{F90F950A-4BED-41DD-B48B-9332BFFD40CE}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G15" authorId="0" shapeId="0" xr:uid="{611286D5-4A2C-4A35-A282-958F6464EEDF}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F28" authorId="0" shapeId="0" xr:uid="{B25FC505-4665-46A5-9225-26659F16396B}">
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{CEC2BEAB-8106-4F99-B7F9-AEBA888C1D32}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 home or community settings, OR 2.17 (1.84-2.56)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{B4E34681-6C8E-46E8-A7CE-75F882328DAD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 home or community settings, OR 2.17 (1.84-2.56)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{3FF52173-B5FC-43E4-A67D-20701A8BC965}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 home and community settings, OR 2.48 (1.99-3.09) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{F0176B0F-5C2B-4F2F-9499-45DCF7600739}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 home and community settings, OR 2.48 (1.99-3.09) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{5F6FC69E-E315-495C-B61C-54987031E97C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{D1B45D24-EA42-4396-A64B-F606BC50060A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{DA396848-65DD-4B57-85EB-992E288BCAD5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G15" authorId="0" shapeId="0" xr:uid="{189B850A-ACBA-4BE1-873E-283E961004C2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F28" authorId="1" shapeId="0" xr:uid="{B25FC505-4665-46A5-9225-26659F16396B}">
       <text>
         <r>
           <rPr>
@@ -13189,7 +13787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F29" authorId="0" shapeId="0" xr:uid="{DA1E1D5C-DFEF-4A4B-A104-119FF2140CA6}">
+    <comment ref="F29" authorId="1" shapeId="0" xr:uid="{DA1E1D5C-DFEF-4A4B-A104-119FF2140CA6}">
       <text>
         <r>
           <rPr>
@@ -13214,7 +13812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G31" authorId="0" shapeId="0" xr:uid="{4DAD8BF0-3624-489E-B2A6-E7727833D9DB}">
+    <comment ref="G31" authorId="1" shapeId="0" xr:uid="{4DAD8BF0-3624-489E-B2A6-E7727833D9DB}">
       <text>
         <r>
           <rPr>
@@ -13239,7 +13837,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G32" authorId="0" shapeId="0" xr:uid="{B1000665-B1E0-4756-B8D6-1B1420AC591C}">
+    <comment ref="G32" authorId="1" shapeId="0" xr:uid="{B1000665-B1E0-4756-B8D6-1B1420AC591C}">
       <text>
         <r>
           <rPr>
@@ -13264,7 +13862,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A36" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1200-000001000000}">
+    <comment ref="A36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -13288,7 +13886,415 @@
         </r>
       </text>
     </comment>
-    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{3F0FEEEB-825A-4110-B4FF-9A53AA391466}">
+    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{D01AC6EE-E4BD-455A-B47D-D367ABF5D331}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 home or community settings, OR 2.17 (1.84-2.56)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{8D4ECCD0-1449-4907-9EE4-3F4F33A91629}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 home or community settings, OR 2.17 (1.84-2.56)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{87550490-2E92-430D-8CCB-5242A1A9D507}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 home and community settings, OR 2.48 (1.99-3.09) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{929C211E-AFB8-4942-92A3-F08DCCA38431}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 home and community settings, OR 2.48 (1.99-3.09) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F64" authorId="0" shapeId="0" xr:uid="{DAE73675-BF94-4B92-965F-CED0E4F2E752}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{9AC383ED-752D-479A-8A46-29B84B76CDB6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{2A536D68-8AED-4664-A323-C8125E57E6E1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{9AE796FE-126D-49A7-BBC6-220FCF06A274}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A89" authorId="0" shapeId="0" xr:uid="{5908CA99-F1E4-42FF-8470-54CE0B811DA6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+These are not used in the current model version</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D111" authorId="0" shapeId="0" xr:uid="{13400FB3-01A1-4882-AD45-5A8B25ED1C61}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 home or community settings, OR 2.17 (1.84-2.56)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D112" authorId="0" shapeId="0" xr:uid="{ACB9181C-4E58-4785-A928-2B341BA5DE89}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 home or community settings, OR 2.17 (1.84-2.56)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E114" authorId="0" shapeId="0" xr:uid="{8A187BD4-0E28-4A12-A931-1E243292F407}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 home and community settings, OR 2.48 (1.99-3.09) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E115" authorId="0" shapeId="0" xr:uid="{FF62E2B3-990A-42FC-8814-F571D1D5DF80}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 home and community settings, OR 2.48 (1.99-3.09) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F117" authorId="0" shapeId="0" xr:uid="{AD76BC8D-C149-4D23-9603-FD42F8F8BEA8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{5B838039-11A3-4B31-8003-020BE09FD80C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G120" authorId="0" shapeId="0" xr:uid="{F715BF6B-4779-4228-819D-568A7EE0BBB9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G121" authorId="0" shapeId="0" xr:uid="{0AD14782-5C07-4167-BF2E-A0C3A8D841A1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nick Scott:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sinah et al 2017 combined delivery: home and community settings and health systems and and services, OR 1.82 (1.36-2.45)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A125" authorId="1" shapeId="0" xr:uid="{A46685C5-1E1A-49D6-A03B-FAD21AA4A9D5}">
       <text>
         <r>
           <rPr>
@@ -13308,419 +14314,11 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{C9172DAA-EA75-4BC3-8012-7E92325DB83B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{D43067D2-2309-4597-85D8-BAFDF8E5791E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{F39039B9-7D81-47CF-B3A8-351139B676C9}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F64" authorId="0" shapeId="0" xr:uid="{4F6AC7D6-DAC7-40F6-8960-A3CF48CE75F7}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{F2191B0D-8AF1-4732-9B04-12866F3B96D4}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{62DC9D77-0A4F-4189-8AC6-B11C119B50E1}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{8829626C-DD33-463A-9EEA-F0B6B10881A7}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A89" authorId="1" shapeId="0" xr:uid="{5908CA99-F1E4-42FF-8470-54CE0B811DA6}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Nick Scott:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-These are not used in the current model version</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D111" authorId="0" shapeId="0" xr:uid="{8646C2BC-114A-44B6-910E-A63844A6CAA3}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D112" authorId="0" shapeId="0" xr:uid="{F27C32B5-B3C2-41D1-973D-A09E1B24FC8F}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E114" authorId="0" shapeId="0" xr:uid="{C40AF175-9B94-403A-96D8-12E3FCC112CA}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E115" authorId="0" shapeId="0" xr:uid="{4799B878-EEA1-4273-B476-A4A0B739A2A7}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F117" authorId="0" shapeId="0" xr:uid="{1208C5D4-F0B8-4078-8F44-E3AEBC531CD7}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{AA909F86-3EF2-4E7B-87FF-06C3D4FE6C89}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G120" authorId="0" shapeId="0" xr:uid="{19ED0103-E2E6-4CFE-B598-FC0BED4B5ED4}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G121" authorId="0" shapeId="0" xr:uid="{1DB7DC00-4486-4245-A40E-282B3E14788E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A125" authorId="0" shapeId="0" xr:uid="{A46685C5-1E1A-49D6-A03B-FAD21AA4A9D5}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
 Upper boundary for the impact means that the point estimate of the OR should be lower</t>
         </r>
       </text>
     </comment>
-    <comment ref="A142" authorId="1" shapeId="0" xr:uid="{4B182B4D-FF1A-4874-81DB-D2F500281F94}">
+    <comment ref="A142" authorId="0" shapeId="0" xr:uid="{4B182B4D-FF1A-4874-81DB-D2F500281F94}">
       <text>
         <r>
           <rPr>
@@ -13749,7 +14347,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="341">
   <si>
     <t>year</t>
   </si>
@@ -19591,12 +20189,8 @@
       <c r="C8" s="68"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="67" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="68" t="s">
-        <v>337</v>
-      </c>
+      <c r="A9" s="67"/>
+      <c r="B9" s="68"/>
       <c r="C9" s="68"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -25647,7 +26241,7 @@
         <v>171</v>
       </c>
       <c r="D5" s="103">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="E5" s="103">
         <v>1</v>
@@ -25668,7 +26262,7 @@
         <v>170</v>
       </c>
       <c r="D6" s="103">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="E6" s="103">
         <v>1</v>
@@ -25715,7 +26309,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="103">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="F8" s="103">
         <v>1</v>
@@ -25736,7 +26330,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="103">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="F9" s="103">
         <v>1</v>
@@ -25783,7 +26377,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="103">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="G11" s="103">
         <v>1</v>
@@ -25804,7 +26398,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="103">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="G12" s="103">
         <v>1</v>
@@ -25851,7 +26445,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="103">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="H14" s="103">
         <v>1</v>
@@ -25872,7 +26466,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="103">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="H15" s="103">
         <v>1</v>
@@ -26739,7 +27333,7 @@
         <v>169</v>
       </c>
       <c r="D57" s="103">
-        <f t="shared" ref="D57:H57" si="2">IF(D4=1,1,D4*0.9)</f>
+        <f t="shared" ref="D57:H59" si="2">IF(D4=1,1,D4*0.9)</f>
         <v>1</v>
       </c>
       <c r="E57" s="103">
@@ -26767,22 +27361,22 @@
         <v>171</v>
       </c>
       <c r="D58" s="103">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="E58" s="103">
-        <f t="shared" ref="E58:H58" si="3">IF(E5=1,1,E5*0.9)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F58" s="103">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G58" s="103">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H58" s="103">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H58" si="3">IF(H5=1,1,H5*0.9)</f>
         <v>1</v>
       </c>
     </row>
@@ -26792,22 +27386,22 @@
         <v>170</v>
       </c>
       <c r="D59" s="103">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="E59" s="103">
-        <f t="shared" ref="E59:H59" si="4">IF(E6=1,1,E6*0.9)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F59" s="103">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G59" s="103">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H59" s="103">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="H59" si="4">IF(H6=1,1,H6*0.9)</f>
         <v>1</v>
       </c>
     </row>
@@ -26817,7 +27411,7 @@
         <v>169</v>
       </c>
       <c r="D60" s="103">
-        <f t="shared" ref="D60:H60" si="5">IF(D7=1,1,D7*0.9)</f>
+        <f t="shared" ref="D60:G68" si="5">IF(D7=1,1,D7*0.9)</f>
         <v>1</v>
       </c>
       <c r="E60" s="103">
@@ -26833,7 +27427,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="103">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="H60" si="6">IF(H7=1,1,H7*0.9)</f>
         <v>1</v>
       </c>
     </row>
@@ -26845,22 +27439,22 @@
         <v>171</v>
       </c>
       <c r="D61" s="103">
-        <f t="shared" ref="D61:H61" si="6">IF(D8=1,1,D8*0.9)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E61" s="103">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="F61" s="103">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G61" s="103">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H61" s="103">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="H61" si="7">IF(H8=1,1,H8*0.9)</f>
         <v>1</v>
       </c>
     </row>
@@ -26870,22 +27464,22 @@
         <v>170</v>
       </c>
       <c r="D62" s="103">
-        <f t="shared" ref="D62:H62" si="7">IF(D9=1,1,D9*0.9)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E62" s="103">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="F62" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G62" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H62" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="H62" si="8">IF(H9=1,1,H9*0.9)</f>
         <v>1</v>
       </c>
     </row>
@@ -26895,23 +27489,23 @@
         <v>169</v>
       </c>
       <c r="D63" s="103">
-        <f t="shared" ref="D63:H63" si="8">IF(D10=1,1,D10*0.9)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E63" s="103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F63" s="103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G63" s="103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H63" s="103">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="H63" si="9">IF(H10=1,1,H10*0.9)</f>
         <v>1</v>
       </c>
     </row>
@@ -26923,22 +27517,22 @@
         <v>171</v>
       </c>
       <c r="D64" s="103">
-        <f t="shared" ref="D64:H64" si="9">IF(D11=1,1,D11*0.9)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E64" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F64" s="103">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G64" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H64" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="H64" si="10">IF(H11=1,1,H11*0.9)</f>
         <v>1</v>
       </c>
     </row>
@@ -26948,22 +27542,22 @@
         <v>170</v>
       </c>
       <c r="D65" s="103">
-        <f t="shared" ref="D65:H65" si="10">IF(D12=1,1,D12*0.9)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E65" s="103">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F65" s="103">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G65" s="103">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H65" s="103">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="H65" si="11">IF(H12=1,1,H12*0.9)</f>
         <v>1</v>
       </c>
     </row>
@@ -26973,23 +27567,23 @@
         <v>169</v>
       </c>
       <c r="D66" s="103">
-        <f t="shared" ref="D66:H66" si="11">IF(D13=1,1,D13*0.9)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E66" s="103">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F66" s="103">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G66" s="103">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="H66" s="103">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="H66" si="12">IF(H13=1,1,H13*0.9)</f>
         <v>1</v>
       </c>
     </row>
@@ -27001,22 +27595,22 @@
         <v>171</v>
       </c>
       <c r="D67" s="103">
-        <f t="shared" ref="D67:H67" si="12">IF(D14=1,1,D14*0.9)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E67" s="103">
-        <f t="shared" si="12"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F67" s="103">
-        <f t="shared" si="12"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G67" s="103">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H67" s="103">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="H67" si="13">IF(H14=1,1,H14*0.9)</f>
         <v>1</v>
       </c>
     </row>
@@ -27026,22 +27620,22 @@
         <v>170</v>
       </c>
       <c r="D68" s="103">
-        <f t="shared" ref="D68:H68" si="13">IF(D15=1,1,D15*0.9)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E68" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="F68" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G68" s="103">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H68" s="103">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="H68" si="14">IF(H15=1,1,H15*0.9)</f>
         <v>1</v>
       </c>
     </row>
@@ -27051,23 +27645,23 @@
         <v>169</v>
       </c>
       <c r="D69" s="103">
-        <f t="shared" ref="D69:H69" si="14">IF(D16=1,1,D16*0.9)</f>
+        <f t="shared" ref="D69:H69" si="15">IF(D16=1,1,D16*0.9)</f>
         <v>1</v>
       </c>
       <c r="E69" s="103">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="F69" s="103">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="G69" s="103">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="H69" s="103">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
@@ -27079,23 +27673,23 @@
         <v>169</v>
       </c>
       <c r="D70" s="103">
-        <f t="shared" ref="D70:H70" si="15">IF(D17=1,1,D17*0.9)</f>
+        <f t="shared" ref="D70:H70" si="16">IF(D17=1,1,D17*0.9)</f>
         <v>0.94500000000000006</v>
       </c>
       <c r="E70" s="103">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.94500000000000006</v>
       </c>
       <c r="F70" s="103">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.94500000000000006</v>
       </c>
       <c r="G70" s="103">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.94500000000000006</v>
       </c>
       <c r="H70" s="103">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
     </row>
@@ -27121,19 +27715,19 @@
         <v>1</v>
       </c>
       <c r="E72" s="103">
-        <f t="shared" ref="E72:H72" si="16">IF(E19=1,1,E19*0.9)</f>
+        <f t="shared" ref="E72:H72" si="17">IF(E19=1,1,E19*0.9)</f>
         <v>1</v>
       </c>
       <c r="F72" s="103">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="G72" s="103">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H72" s="103">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -27143,23 +27737,23 @@
         <v>170</v>
       </c>
       <c r="D73" s="103">
-        <f t="shared" ref="D73:H73" si="17">IF(D20=1,1,D20*0.9)</f>
+        <f t="shared" ref="D73:H73" si="18">IF(D20=1,1,D20*0.9)</f>
         <v>1</v>
       </c>
       <c r="E73" s="103">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="F73" s="103">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G73" s="103">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H73" s="103">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
@@ -27169,23 +27763,23 @@
         <v>169</v>
       </c>
       <c r="D74" s="103">
-        <f t="shared" ref="D74:H74" si="18">IF(D21=1,1,D21*0.9)</f>
+        <f t="shared" ref="D74:H74" si="19">IF(D21=1,1,D21*0.9)</f>
         <v>1</v>
       </c>
       <c r="E74" s="103">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F74" s="103">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G74" s="103">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="H74" s="103">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
@@ -27197,23 +27791,23 @@
         <v>171</v>
       </c>
       <c r="D75" s="103">
-        <f t="shared" ref="D75:H75" si="19">IF(D22=1,1,D22*0.9)</f>
+        <f t="shared" ref="D75:H75" si="20">IF(D22=1,1,D22*0.9)</f>
         <v>1</v>
       </c>
       <c r="E75" s="103">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F75" s="103">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G75" s="103">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H75" s="103">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -27223,23 +27817,23 @@
         <v>170</v>
       </c>
       <c r="D76" s="103">
-        <f t="shared" ref="D76:H76" si="20">IF(D23=1,1,D23*0.9)</f>
+        <f t="shared" ref="D76:H76" si="21">IF(D23=1,1,D23*0.9)</f>
         <v>1</v>
       </c>
       <c r="E76" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="F76" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="G76" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="H76" s="103">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
     </row>
@@ -27249,23 +27843,23 @@
         <v>169</v>
       </c>
       <c r="D77" s="103">
-        <f t="shared" ref="D77:H77" si="21">IF(D24=1,1,D24*0.9)</f>
+        <f t="shared" ref="D77:H77" si="22">IF(D24=1,1,D24*0.9)</f>
         <v>1</v>
       </c>
       <c r="E77" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="F77" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="G77" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="H77" s="103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
     </row>
@@ -27277,23 +27871,23 @@
         <v>171</v>
       </c>
       <c r="D78" s="103">
-        <f t="shared" ref="D78:H78" si="22">IF(D25=1,1,D25*0.9)</f>
+        <f t="shared" ref="D78:H78" si="23">IF(D25=1,1,D25*0.9)</f>
         <v>1</v>
       </c>
       <c r="E78" s="103">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="F78" s="103">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="G78" s="103">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="H78" s="103">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
     </row>
@@ -27303,23 +27897,23 @@
         <v>170</v>
       </c>
       <c r="D79" s="103">
-        <f t="shared" ref="D79:H79" si="23">IF(D26=1,1,D26*0.9)</f>
+        <f t="shared" ref="D79:H79" si="24">IF(D26=1,1,D26*0.9)</f>
         <v>1</v>
       </c>
       <c r="E79" s="103">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="F79" s="103">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="G79" s="103">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="H79" s="103">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
     </row>
@@ -27329,23 +27923,23 @@
         <v>169</v>
       </c>
       <c r="D80" s="103">
-        <f t="shared" ref="D80:H80" si="24">IF(D27=1,1,D27*0.9)</f>
+        <f t="shared" ref="D80:H80" si="25">IF(D27=1,1,D27*0.9)</f>
         <v>1</v>
       </c>
       <c r="E80" s="103">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="F80" s="103">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="G80" s="103">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="H80" s="103">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
     </row>
@@ -27357,23 +27951,23 @@
         <v>171</v>
       </c>
       <c r="D81" s="103">
-        <f t="shared" ref="D81:H81" si="25">IF(D28=1,1,D28*0.9)</f>
+        <f t="shared" ref="D81:H81" si="26">IF(D28=1,1,D28*0.9)</f>
         <v>1</v>
       </c>
       <c r="E81" s="103">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F81" s="103">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="G81" s="103">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="H81" s="103">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
     </row>
@@ -27383,23 +27977,23 @@
         <v>170</v>
       </c>
       <c r="D82" s="103">
-        <f t="shared" ref="D82:H82" si="26">IF(D29=1,1,D29*0.9)</f>
+        <f t="shared" ref="D82:H82" si="27">IF(D29=1,1,D29*0.9)</f>
         <v>1</v>
       </c>
       <c r="E82" s="103">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="F82" s="103">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G82" s="103">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="H82" s="103">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
     </row>
@@ -27409,23 +28003,23 @@
         <v>169</v>
       </c>
       <c r="D83" s="103">
-        <f t="shared" ref="D83:H83" si="27">IF(D30=1,1,D30*0.9)</f>
+        <f t="shared" ref="D83:H83" si="28">IF(D30=1,1,D30*0.9)</f>
         <v>1</v>
       </c>
       <c r="E83" s="103">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F83" s="103">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="G83" s="103">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="H83" s="103">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
     </row>
@@ -27437,23 +28031,23 @@
         <v>171</v>
       </c>
       <c r="D84" s="103">
-        <f t="shared" ref="D84:H84" si="28">IF(D31=1,1,D31*0.9)</f>
+        <f t="shared" ref="D84:H84" si="29">IF(D31=1,1,D31*0.9)</f>
         <v>1</v>
       </c>
       <c r="E84" s="103">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F84" s="103">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G84" s="103">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="H84" s="103">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
     </row>
@@ -27463,23 +28057,23 @@
         <v>170</v>
       </c>
       <c r="D85" s="103">
-        <f t="shared" ref="D85:H85" si="29">IF(D32=1,1,D32*0.9)</f>
+        <f t="shared" ref="D85:H85" si="30">IF(D32=1,1,D32*0.9)</f>
         <v>1</v>
       </c>
       <c r="E85" s="103">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F85" s="103">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G85" s="103">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="H85" s="103">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
     </row>
@@ -27489,23 +28083,23 @@
         <v>169</v>
       </c>
       <c r="D86" s="103">
-        <f t="shared" ref="D86:H86" si="30">IF(D33=1,1,D33*0.9)</f>
+        <f t="shared" ref="D86:H86" si="31">IF(D33=1,1,D33*0.9)</f>
         <v>1</v>
       </c>
       <c r="E86" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F86" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G86" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="H86" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
     </row>
@@ -27517,23 +28111,23 @@
         <v>169</v>
       </c>
       <c r="D87" s="103">
-        <f t="shared" ref="D87:H87" si="31">IF(D34=1,1,D34*0.9)</f>
+        <f t="shared" ref="D87:H87" si="32">IF(D34=1,1,D34*0.9)</f>
         <v>1</v>
       </c>
       <c r="E87" s="103">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F87" s="103">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G87" s="103">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="H87" s="103">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
     </row>
@@ -27559,19 +28153,19 @@
         <v>1</v>
       </c>
       <c r="E89" s="103">
-        <f t="shared" ref="E89:H89" si="32">IF(E36=1,1,E36*0.9)</f>
+        <f t="shared" ref="E89:H89" si="33">IF(E36=1,1,E36*0.9)</f>
         <v>1</v>
       </c>
       <c r="F89" s="103">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G89" s="103">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="H89" s="103">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
     </row>
@@ -27581,23 +28175,23 @@
         <v>170</v>
       </c>
       <c r="D90" s="103">
-        <f t="shared" ref="D90:H90" si="33">IF(D37=1,1,D37*0.9)</f>
+        <f t="shared" ref="D90:H90" si="34">IF(D37=1,1,D37*0.9)</f>
         <v>1</v>
       </c>
       <c r="E90" s="103">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F90" s="103">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G90" s="103">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="H90" s="103">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
     </row>
@@ -27607,23 +28201,23 @@
         <v>169</v>
       </c>
       <c r="D91" s="103">
-        <f t="shared" ref="D91:H91" si="34">IF(D38=1,1,D38*0.9)</f>
+        <f t="shared" ref="D91:H91" si="35">IF(D38=1,1,D38*0.9)</f>
         <v>1</v>
       </c>
       <c r="E91" s="103">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F91" s="103">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G91" s="103">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="H91" s="103">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
     </row>
@@ -27635,23 +28229,23 @@
         <v>171</v>
       </c>
       <c r="D92" s="103">
-        <f t="shared" ref="D92:H92" si="35">IF(D39=1,1,D39*0.9)</f>
+        <f t="shared" ref="D92:H92" si="36">IF(D39=1,1,D39*0.9)</f>
         <v>1</v>
       </c>
       <c r="E92" s="103">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="F92" s="103">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G92" s="103">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="H92" s="103">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
     </row>
@@ -27661,23 +28255,23 @@
         <v>170</v>
       </c>
       <c r="D93" s="103">
-        <f t="shared" ref="D93:H93" si="36">IF(D40=1,1,D40*0.9)</f>
+        <f t="shared" ref="D93:H93" si="37">IF(D40=1,1,D40*0.9)</f>
         <v>1</v>
       </c>
       <c r="E93" s="103">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="F93" s="103">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="G93" s="103">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
       <c r="H93" s="103">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1</v>
       </c>
     </row>
@@ -27687,23 +28281,23 @@
         <v>169</v>
       </c>
       <c r="D94" s="103">
-        <f t="shared" ref="D94:H94" si="37">IF(D41=1,1,D41*0.9)</f>
+        <f t="shared" ref="D94:H94" si="38">IF(D41=1,1,D41*0.9)</f>
         <v>1</v>
       </c>
       <c r="E94" s="103">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="F94" s="103">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="G94" s="103">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
       <c r="H94" s="103">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1</v>
       </c>
     </row>
@@ -27715,23 +28309,23 @@
         <v>171</v>
       </c>
       <c r="D95" s="103">
-        <f t="shared" ref="D95:H95" si="38">IF(D42=1,1,D42*0.9)</f>
+        <f t="shared" ref="D95:H95" si="39">IF(D42=1,1,D42*0.9)</f>
         <v>1</v>
       </c>
       <c r="E95" s="103">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
       <c r="F95" s="103">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
       <c r="G95" s="103">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
       <c r="H95" s="103">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
     </row>
@@ -27741,23 +28335,23 @@
         <v>170</v>
       </c>
       <c r="D96" s="103">
-        <f t="shared" ref="D96:H96" si="39">IF(D43=1,1,D43*0.9)</f>
+        <f t="shared" ref="D96:H96" si="40">IF(D43=1,1,D43*0.9)</f>
         <v>1</v>
       </c>
       <c r="E96" s="103">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
       <c r="F96" s="103">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
       <c r="G96" s="103">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
       <c r="H96" s="103">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1</v>
       </c>
     </row>
@@ -27767,23 +28361,23 @@
         <v>169</v>
       </c>
       <c r="D97" s="103">
-        <f t="shared" ref="D97:H97" si="40">IF(D44=1,1,D44*0.9)</f>
+        <f t="shared" ref="D97:H97" si="41">IF(D44=1,1,D44*0.9)</f>
         <v>1</v>
       </c>
       <c r="E97" s="103">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1</v>
       </c>
       <c r="F97" s="103">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1</v>
       </c>
       <c r="G97" s="103">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1</v>
       </c>
       <c r="H97" s="103">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1</v>
       </c>
     </row>
@@ -27795,11 +28389,11 @@
         <v>171</v>
       </c>
       <c r="D98" s="103">
-        <f t="shared" ref="D98:H98" si="41">IF(D45=1,1,D45*0.9)</f>
+        <f t="shared" ref="D98:H98" si="42">IF(D45=1,1,D45*0.9)</f>
         <v>1</v>
       </c>
       <c r="E98" s="103">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1</v>
       </c>
       <c r="F98" s="103">
@@ -27807,11 +28401,11 @@
         <v>1</v>
       </c>
       <c r="G98" s="103">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1</v>
       </c>
       <c r="H98" s="103">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1</v>
       </c>
     </row>
@@ -27821,11 +28415,11 @@
         <v>170</v>
       </c>
       <c r="D99" s="103">
-        <f t="shared" ref="D99:H99" si="42">IF(D46=1,1,D46*0.9)</f>
+        <f t="shared" ref="D99:H99" si="43">IF(D46=1,1,D46*0.9)</f>
         <v>1</v>
       </c>
       <c r="E99" s="103">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1</v>
       </c>
       <c r="F99" s="103">
@@ -27833,11 +28427,11 @@
         <v>1</v>
       </c>
       <c r="G99" s="103">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1</v>
       </c>
       <c r="H99" s="103">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1</v>
       </c>
     </row>
@@ -27847,23 +28441,23 @@
         <v>169</v>
       </c>
       <c r="D100" s="103">
-        <f t="shared" ref="D100:H100" si="43">IF(D47=1,1,D47*0.9)</f>
+        <f t="shared" ref="D100:H100" si="44">IF(D47=1,1,D47*0.9)</f>
         <v>1</v>
       </c>
       <c r="E100" s="103">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F100" s="103">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="G100" s="103">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="H100" s="103">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
     </row>
@@ -27875,15 +28469,15 @@
         <v>171</v>
       </c>
       <c r="D101" s="103">
-        <f t="shared" ref="D101:H101" si="44">IF(D48=1,1,D48*0.9)</f>
+        <f t="shared" ref="D101:H101" si="45">IF(D48=1,1,D48*0.9)</f>
         <v>1</v>
       </c>
       <c r="E101" s="103">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F101" s="103">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="G101" s="103">
@@ -27891,7 +28485,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="103">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
     </row>
@@ -27901,15 +28495,15 @@
         <v>170</v>
       </c>
       <c r="D102" s="103">
-        <f t="shared" ref="D102:H102" si="45">IF(D49=1,1,D49*0.9)</f>
+        <f t="shared" ref="D102:H102" si="46">IF(D49=1,1,D49*0.9)</f>
         <v>1</v>
       </c>
       <c r="E102" s="103">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1</v>
       </c>
       <c r="F102" s="103">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1</v>
       </c>
       <c r="G102" s="103">
@@ -27917,7 +28511,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="103">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1</v>
       </c>
     </row>
@@ -27927,23 +28521,23 @@
         <v>169</v>
       </c>
       <c r="D103" s="103">
-        <f t="shared" ref="D103:H103" si="46">IF(D50=1,1,D50*0.9)</f>
+        <f t="shared" ref="D103:H103" si="47">IF(D50=1,1,D50*0.9)</f>
         <v>1</v>
       </c>
       <c r="E103" s="103">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>1</v>
       </c>
       <c r="F103" s="103">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>1</v>
       </c>
       <c r="G103" s="103">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>1</v>
       </c>
       <c r="H103" s="103">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>1</v>
       </c>
     </row>
@@ -27955,23 +28549,23 @@
         <v>169</v>
       </c>
       <c r="D104" s="103">
-        <f t="shared" ref="D104:H104" si="47">IF(D51=1,1,D51*0.9)</f>
+        <f t="shared" ref="D104:H104" si="48">IF(D51=1,1,D51*0.9)</f>
         <v>1</v>
       </c>
       <c r="E104" s="103">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1</v>
       </c>
       <c r="F104" s="103">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1</v>
       </c>
       <c r="G104" s="103">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1</v>
       </c>
       <c r="H104" s="103">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1</v>
       </c>
     </row>
@@ -28028,19 +28622,19 @@
         <v>1</v>
       </c>
       <c r="E108" s="103">
-        <f t="shared" ref="E108:H108" si="48">IF(E2=1,1,E2*1.05)</f>
+        <f t="shared" ref="E108:H108" si="49">IF(E2=1,1,E2*1.05)</f>
         <v>1</v>
       </c>
       <c r="F108" s="103">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1</v>
       </c>
       <c r="G108" s="103">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1</v>
       </c>
       <c r="H108" s="103">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1</v>
       </c>
     </row>
@@ -28050,23 +28644,23 @@
         <v>170</v>
       </c>
       <c r="D109" s="103">
-        <f t="shared" ref="D109:H109" si="49">IF(D3=1,1,D3*1.05)</f>
+        <f t="shared" ref="D109:H109" si="50">IF(D3=1,1,D3*1.05)</f>
         <v>1</v>
       </c>
       <c r="E109" s="103">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>1</v>
       </c>
       <c r="F109" s="103">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>1</v>
       </c>
       <c r="G109" s="103">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>1</v>
       </c>
       <c r="H109" s="103">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>1</v>
       </c>
     </row>
@@ -28076,23 +28670,23 @@
         <v>169</v>
       </c>
       <c r="D110" s="103">
-        <f t="shared" ref="D110:H110" si="50">IF(D4=1,1,D4*1.05)</f>
+        <f t="shared" ref="D110:H110" si="51">IF(D4=1,1,D4*1.05)</f>
         <v>1</v>
       </c>
       <c r="E110" s="103">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1</v>
       </c>
       <c r="F110" s="103">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1</v>
       </c>
       <c r="G110" s="103">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1</v>
       </c>
       <c r="H110" s="103">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1</v>
       </c>
     </row>
@@ -28104,22 +28698,22 @@
         <v>171</v>
       </c>
       <c r="D111" s="103">
-        <v>2.11</v>
+        <v>2.56</v>
       </c>
       <c r="E111" s="103">
-        <f t="shared" ref="E111:H111" si="51">IF(E5=1,1,E5*1.05)</f>
+        <f t="shared" ref="E111:G112" si="52">IF(E58=1,1,E58*0.9)</f>
         <v>1</v>
       </c>
       <c r="F111" s="103">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="G111" s="103">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="H111" s="103">
-        <f t="shared" si="51"/>
+        <f t="shared" ref="H111" si="53">IF(H5=1,1,H5*1.05)</f>
         <v>1</v>
       </c>
     </row>
@@ -28129,10 +28723,10 @@
         <v>170</v>
       </c>
       <c r="D112" s="103">
-        <v>2.11</v>
+        <v>2.56</v>
       </c>
       <c r="E112" s="103">
-        <f t="shared" ref="E112:H112" si="52">IF(E6=1,1,E6*1.05)</f>
+        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="F112" s="103">
@@ -28144,7 +28738,7 @@
         <v>1</v>
       </c>
       <c r="H112" s="103">
-        <f t="shared" si="52"/>
+        <f t="shared" ref="H112" si="54">IF(H6=1,1,H6*1.05)</f>
         <v>1</v>
       </c>
     </row>
@@ -28154,23 +28748,23 @@
         <v>169</v>
       </c>
       <c r="D113" s="103">
-        <f t="shared" ref="D113:H113" si="53">IF(D7=1,1,D7*1.05)</f>
+        <f t="shared" ref="D113:G121" si="55">IF(D60=1,1,D60*0.9)</f>
         <v>1</v>
       </c>
       <c r="E113" s="103">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="F113" s="103">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="G113" s="103">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="H113" s="103">
-        <f t="shared" si="53"/>
+        <f t="shared" ref="H113" si="56">IF(H7=1,1,H7*1.05)</f>
         <v>1</v>
       </c>
     </row>
@@ -28182,22 +28776,22 @@
         <v>171</v>
       </c>
       <c r="D114" s="103">
-        <f t="shared" ref="D114:H114" si="54">IF(D8=1,1,D8*1.05)</f>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="E114" s="103">
-        <v>2.11</v>
+        <v>3.09</v>
       </c>
       <c r="F114" s="103">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="G114" s="103">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="H114" s="103">
-        <f t="shared" si="54"/>
+        <f t="shared" ref="H114" si="57">IF(H8=1,1,H8*1.05)</f>
         <v>1</v>
       </c>
     </row>
@@ -28207,11 +28801,11 @@
         <v>170</v>
       </c>
       <c r="D115" s="103">
-        <f t="shared" ref="D115:H115" si="55">IF(D9=1,1,D9*1.05)</f>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="E115" s="103">
-        <v>2.11</v>
+        <v>3.09</v>
       </c>
       <c r="F115" s="103">
         <f t="shared" si="55"/>
@@ -28222,7 +28816,7 @@
         <v>1</v>
       </c>
       <c r="H115" s="103">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="H115" si="58">IF(H9=1,1,H9*1.05)</f>
         <v>1</v>
       </c>
     </row>
@@ -28232,23 +28826,23 @@
         <v>169</v>
       </c>
       <c r="D116" s="103">
-        <f t="shared" ref="D116:H116" si="56">IF(D10=1,1,D10*1.05)</f>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="E116" s="103">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="F116" s="103">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="G116" s="103">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="H116" s="103">
-        <f t="shared" si="56"/>
+        <f t="shared" ref="H116" si="59">IF(H10=1,1,H10*1.05)</f>
         <v>1</v>
       </c>
     </row>
@@ -28260,22 +28854,22 @@
         <v>171</v>
       </c>
       <c r="D117" s="103">
-        <f t="shared" ref="D117:H117" si="57">IF(D11=1,1,D11*1.05)</f>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="E117" s="103">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="F117" s="103">
-        <v>2.11</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G117" s="103">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="H117" s="103">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="H117" si="60">IF(H11=1,1,H11*1.05)</f>
         <v>1</v>
       </c>
     </row>
@@ -28285,22 +28879,22 @@
         <v>170</v>
       </c>
       <c r="D118" s="103">
-        <f t="shared" ref="D118:H118" si="58">IF(D12=1,1,D12*1.05)</f>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="E118" s="103">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="F118" s="103">
-        <v>2.11</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G118" s="103">
-        <f t="shared" si="58"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="H118" s="103">
-        <f t="shared" si="58"/>
+        <f t="shared" ref="H118" si="61">IF(H12=1,1,H12*1.05)</f>
         <v>1</v>
       </c>
     </row>
@@ -28310,23 +28904,23 @@
         <v>169</v>
       </c>
       <c r="D119" s="103">
-        <f t="shared" ref="D119:H119" si="59">IF(D13=1,1,D13*1.05)</f>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="E119" s="103">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="F119" s="103">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="G119" s="103">
-        <f t="shared" si="59"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="H119" s="103">
-        <f t="shared" si="59"/>
+        <f t="shared" ref="H119" si="62">IF(H13=1,1,H13*1.05)</f>
         <v>1</v>
       </c>
     </row>
@@ -28338,22 +28932,22 @@
         <v>171</v>
       </c>
       <c r="D120" s="103">
-        <f t="shared" ref="D120:H120" si="60">IF(D14=1,1,D14*1.05)</f>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="E120" s="103">
-        <f t="shared" si="60"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="F120" s="103">
-        <f t="shared" si="60"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="G120" s="103">
-        <v>2.11</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H120" s="103">
-        <f t="shared" si="60"/>
+        <f t="shared" ref="H120" si="63">IF(H14=1,1,H14*1.05)</f>
         <v>1</v>
       </c>
     </row>
@@ -28363,22 +28957,22 @@
         <v>170</v>
       </c>
       <c r="D121" s="103">
-        <f t="shared" ref="D121:H121" si="61">IF(D15=1,1,D15*1.05)</f>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="E121" s="103">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="F121" s="103">
-        <f t="shared" si="61"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="G121" s="103">
-        <v>2.11</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H121" s="103">
-        <f t="shared" si="61"/>
+        <f t="shared" ref="H121" si="64">IF(H15=1,1,H15*1.05)</f>
         <v>1</v>
       </c>
     </row>
@@ -28388,23 +28982,23 @@
         <v>169</v>
       </c>
       <c r="D122" s="103">
-        <f t="shared" ref="D122:H122" si="62">IF(D16=1,1,D16*1.05)</f>
+        <f t="shared" ref="D122:H122" si="65">IF(D16=1,1,D16*1.05)</f>
         <v>1</v>
       </c>
       <c r="E122" s="103">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>1</v>
       </c>
       <c r="F122" s="103">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>1</v>
       </c>
       <c r="G122" s="103">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>1</v>
       </c>
       <c r="H122" s="103">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>1</v>
       </c>
     </row>
@@ -28416,23 +29010,23 @@
         <v>169</v>
       </c>
       <c r="D123" s="103">
-        <f t="shared" ref="D123:H123" si="63">IF(D17=1,1,D17*1.05)</f>
+        <f t="shared" ref="D123:H123" si="66">IF(D17=1,1,D17*1.05)</f>
         <v>1.1025</v>
       </c>
       <c r="E123" s="103">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>1.1025</v>
       </c>
       <c r="F123" s="103">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>1.1025</v>
       </c>
       <c r="G123" s="103">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>1.1025</v>
       </c>
       <c r="H123" s="103">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>1</v>
       </c>
     </row>
@@ -28458,19 +29052,19 @@
         <v>1</v>
       </c>
       <c r="E125" s="103">
-        <f t="shared" ref="E125:H125" si="64">IF(E19=1,1,E19*1.05)</f>
+        <f t="shared" ref="E125:H125" si="67">IF(E19=1,1,E19*1.05)</f>
         <v>1</v>
       </c>
       <c r="F125" s="103">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="G125" s="103">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="H125" s="103">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
     </row>
@@ -28480,23 +29074,23 @@
         <v>170</v>
       </c>
       <c r="D126" s="103">
-        <f t="shared" ref="D126:H126" si="65">IF(D20=1,1,D20*1.05)</f>
+        <f t="shared" ref="D126:H126" si="68">IF(D20=1,1,D20*1.05)</f>
         <v>1</v>
       </c>
       <c r="E126" s="103">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="F126" s="103">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="G126" s="103">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="H126" s="103">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
     </row>
@@ -28506,23 +29100,23 @@
         <v>169</v>
       </c>
       <c r="D127" s="103">
-        <f t="shared" ref="D127:H127" si="66">IF(D21=1,1,D21*1.05)</f>
+        <f t="shared" ref="D127:H127" si="69">IF(D21=1,1,D21*1.05)</f>
         <v>1</v>
       </c>
       <c r="E127" s="103">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="F127" s="103">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="G127" s="103">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
       <c r="H127" s="103">
-        <f t="shared" si="66"/>
+        <f t="shared" si="69"/>
         <v>1</v>
       </c>
     </row>
@@ -28534,23 +29128,23 @@
         <v>171</v>
       </c>
       <c r="D128" s="103">
-        <f t="shared" ref="D128:H128" si="67">IF(D22=1,1,D22*1.05)</f>
+        <f t="shared" ref="D128:H128" si="70">IF(D22=1,1,D22*1.05)</f>
         <v>1</v>
       </c>
       <c r="E128" s="103">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>1</v>
       </c>
       <c r="F128" s="103">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>1</v>
       </c>
       <c r="G128" s="103">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>1</v>
       </c>
       <c r="H128" s="103">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>1</v>
       </c>
     </row>
@@ -28560,23 +29154,23 @@
         <v>170</v>
       </c>
       <c r="D129" s="103">
-        <f t="shared" ref="D129:H129" si="68">IF(D23=1,1,D23*1.05)</f>
+        <f t="shared" ref="D129:H129" si="71">IF(D23=1,1,D23*1.05)</f>
         <v>1</v>
       </c>
       <c r="E129" s="103">
-        <f t="shared" si="68"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="F129" s="103">
-        <f t="shared" si="68"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="G129" s="103">
-        <f t="shared" si="68"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
       <c r="H129" s="103">
-        <f t="shared" si="68"/>
+        <f t="shared" si="71"/>
         <v>1</v>
       </c>
     </row>
@@ -28586,23 +29180,23 @@
         <v>169</v>
       </c>
       <c r="D130" s="103">
-        <f t="shared" ref="D130:H130" si="69">IF(D24=1,1,D24*1.05)</f>
+        <f t="shared" ref="D130:H130" si="72">IF(D24=1,1,D24*1.05)</f>
         <v>1</v>
       </c>
       <c r="E130" s="103">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>1</v>
       </c>
       <c r="F130" s="103">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>1</v>
       </c>
       <c r="G130" s="103">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>1</v>
       </c>
       <c r="H130" s="103">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>1</v>
       </c>
     </row>
@@ -28614,23 +29208,23 @@
         <v>171</v>
       </c>
       <c r="D131" s="103">
-        <f t="shared" ref="D131:H131" si="70">IF(D25=1,1,D25*1.05)</f>
+        <f t="shared" ref="D131:H131" si="73">IF(D25=1,1,D25*1.05)</f>
         <v>1</v>
       </c>
       <c r="E131" s="103">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>1</v>
       </c>
       <c r="F131" s="103">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>1</v>
       </c>
       <c r="G131" s="103">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>1</v>
       </c>
       <c r="H131" s="103">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>1</v>
       </c>
     </row>
@@ -28640,23 +29234,23 @@
         <v>170</v>
       </c>
       <c r="D132" s="103">
-        <f t="shared" ref="D132:H132" si="71">IF(D26=1,1,D26*1.05)</f>
+        <f t="shared" ref="D132:H132" si="74">IF(D26=1,1,D26*1.05)</f>
         <v>1</v>
       </c>
       <c r="E132" s="103">
-        <f t="shared" si="71"/>
+        <f t="shared" si="74"/>
         <v>1</v>
       </c>
       <c r="F132" s="103">
-        <f t="shared" si="71"/>
+        <f t="shared" si="74"/>
         <v>1</v>
       </c>
       <c r="G132" s="103">
-        <f t="shared" si="71"/>
+        <f t="shared" si="74"/>
         <v>1</v>
       </c>
       <c r="H132" s="103">
-        <f t="shared" si="71"/>
+        <f t="shared" si="74"/>
         <v>1</v>
       </c>
     </row>
@@ -28666,23 +29260,23 @@
         <v>169</v>
       </c>
       <c r="D133" s="103">
-        <f t="shared" ref="D133:H133" si="72">IF(D27=1,1,D27*1.05)</f>
+        <f t="shared" ref="D133:H133" si="75">IF(D27=1,1,D27*1.05)</f>
         <v>1</v>
       </c>
       <c r="E133" s="103">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>1</v>
       </c>
       <c r="F133" s="103">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>1</v>
       </c>
       <c r="G133" s="103">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>1</v>
       </c>
       <c r="H133" s="103">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>1</v>
       </c>
     </row>
@@ -28694,23 +29288,23 @@
         <v>171</v>
       </c>
       <c r="D134" s="103">
-        <f t="shared" ref="D134:H134" si="73">IF(D28=1,1,D28*1.05)</f>
+        <f t="shared" ref="D134:H134" si="76">IF(D28=1,1,D28*1.05)</f>
         <v>1</v>
       </c>
       <c r="E134" s="103">
-        <f t="shared" si="73"/>
+        <f t="shared" si="76"/>
         <v>1</v>
       </c>
       <c r="F134" s="103">
-        <f t="shared" si="73"/>
+        <f t="shared" si="76"/>
         <v>1</v>
       </c>
       <c r="G134" s="103">
-        <f t="shared" si="73"/>
+        <f t="shared" si="76"/>
         <v>1</v>
       </c>
       <c r="H134" s="103">
-        <f t="shared" si="73"/>
+        <f t="shared" si="76"/>
         <v>1</v>
       </c>
     </row>
@@ -28720,23 +29314,23 @@
         <v>170</v>
       </c>
       <c r="D135" s="103">
-        <f t="shared" ref="D135:H135" si="74">IF(D29=1,1,D29*1.05)</f>
+        <f t="shared" ref="D135:H135" si="77">IF(D29=1,1,D29*1.05)</f>
         <v>1</v>
       </c>
       <c r="E135" s="103">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>1</v>
       </c>
       <c r="F135" s="103">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>1</v>
       </c>
       <c r="G135" s="103">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>1</v>
       </c>
       <c r="H135" s="103">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>1</v>
       </c>
     </row>
@@ -28746,23 +29340,23 @@
         <v>169</v>
       </c>
       <c r="D136" s="103">
-        <f t="shared" ref="D136:H136" si="75">IF(D30=1,1,D30*1.05)</f>
+        <f t="shared" ref="D136:H136" si="78">IF(D30=1,1,D30*1.05)</f>
         <v>1</v>
       </c>
       <c r="E136" s="103">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>1</v>
       </c>
       <c r="F136" s="103">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>1</v>
       </c>
       <c r="G136" s="103">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>1</v>
       </c>
       <c r="H136" s="103">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>1</v>
       </c>
     </row>
@@ -28774,23 +29368,23 @@
         <v>171</v>
       </c>
       <c r="D137" s="103">
-        <f t="shared" ref="D137:H137" si="76">IF(D31=1,1,D31*1.05)</f>
+        <f t="shared" ref="D137:H137" si="79">IF(D31=1,1,D31*1.05)</f>
         <v>1</v>
       </c>
       <c r="E137" s="103">
-        <f t="shared" si="76"/>
+        <f t="shared" si="79"/>
         <v>1</v>
       </c>
       <c r="F137" s="103">
-        <f t="shared" si="76"/>
+        <f t="shared" si="79"/>
         <v>1</v>
       </c>
       <c r="G137" s="103">
-        <f t="shared" si="76"/>
+        <f t="shared" si="79"/>
         <v>1</v>
       </c>
       <c r="H137" s="103">
-        <f t="shared" si="76"/>
+        <f t="shared" si="79"/>
         <v>1</v>
       </c>
     </row>
@@ -28800,23 +29394,23 @@
         <v>170</v>
       </c>
       <c r="D138" s="103">
-        <f t="shared" ref="D138:H138" si="77">IF(D32=1,1,D32*1.05)</f>
+        <f t="shared" ref="D138:H138" si="80">IF(D32=1,1,D32*1.05)</f>
         <v>1</v>
       </c>
       <c r="E138" s="103">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>1</v>
       </c>
       <c r="F138" s="103">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>1</v>
       </c>
       <c r="G138" s="103">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>1</v>
       </c>
       <c r="H138" s="103">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>1</v>
       </c>
     </row>
@@ -28826,23 +29420,23 @@
         <v>169</v>
       </c>
       <c r="D139" s="103">
-        <f t="shared" ref="D139:H139" si="78">IF(D33=1,1,D33*1.05)</f>
+        <f t="shared" ref="D139:H139" si="81">IF(D33=1,1,D33*1.05)</f>
         <v>1</v>
       </c>
       <c r="E139" s="103">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>1</v>
       </c>
       <c r="F139" s="103">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>1</v>
       </c>
       <c r="G139" s="103">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>1</v>
       </c>
       <c r="H139" s="103">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>1</v>
       </c>
     </row>
@@ -28854,23 +29448,23 @@
         <v>169</v>
       </c>
       <c r="D140" s="103">
-        <f t="shared" ref="D140:H140" si="79">IF(D34=1,1,D34*1.05)</f>
+        <f t="shared" ref="D140:H140" si="82">IF(D34=1,1,D34*1.05)</f>
         <v>1</v>
       </c>
       <c r="E140" s="103">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>1</v>
       </c>
       <c r="F140" s="103">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>1</v>
       </c>
       <c r="G140" s="103">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>1</v>
       </c>
       <c r="H140" s="103">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>1</v>
       </c>
     </row>
@@ -28896,19 +29490,19 @@
         <v>1</v>
       </c>
       <c r="E142" s="103">
-        <f t="shared" ref="E142:H142" si="80">IF(E36=1,1,E36*1.05)</f>
+        <f t="shared" ref="E142:H142" si="83">IF(E36=1,1,E36*1.05)</f>
         <v>1</v>
       </c>
       <c r="F142" s="103">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>1</v>
       </c>
       <c r="G142" s="103">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>1</v>
       </c>
       <c r="H142" s="103">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>1</v>
       </c>
     </row>
@@ -28918,23 +29512,23 @@
         <v>170</v>
       </c>
       <c r="D143" s="103">
-        <f t="shared" ref="D143:H143" si="81">IF(D37=1,1,D37*1.05)</f>
+        <f t="shared" ref="D143:H143" si="84">IF(D37=1,1,D37*1.05)</f>
         <v>1</v>
       </c>
       <c r="E143" s="103">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>1</v>
       </c>
       <c r="F143" s="103">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>1</v>
       </c>
       <c r="G143" s="103">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>1</v>
       </c>
       <c r="H143" s="103">
-        <f t="shared" si="81"/>
+        <f t="shared" si="84"/>
         <v>1</v>
       </c>
     </row>
@@ -28944,23 +29538,23 @@
         <v>169</v>
       </c>
       <c r="D144" s="103">
-        <f t="shared" ref="D144:H144" si="82">IF(D38=1,1,D38*1.05)</f>
+        <f t="shared" ref="D144:H144" si="85">IF(D38=1,1,D38*1.05)</f>
         <v>1</v>
       </c>
       <c r="E144" s="103">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>1</v>
       </c>
       <c r="F144" s="103">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>1</v>
       </c>
       <c r="G144" s="103">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>1</v>
       </c>
       <c r="H144" s="103">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>1</v>
       </c>
     </row>
@@ -28972,23 +29566,23 @@
         <v>171</v>
       </c>
       <c r="D145" s="103">
-        <f t="shared" ref="D145:H145" si="83">IF(D39=1,1,D39*1.05)</f>
+        <f t="shared" ref="D145:H145" si="86">IF(D39=1,1,D39*1.05)</f>
         <v>1</v>
       </c>
       <c r="E145" s="103">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>1</v>
       </c>
       <c r="F145" s="103">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>1</v>
       </c>
       <c r="G145" s="103">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>1</v>
       </c>
       <c r="H145" s="103">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>1</v>
       </c>
     </row>
@@ -28998,23 +29592,23 @@
         <v>170</v>
       </c>
       <c r="D146" s="103">
-        <f t="shared" ref="D146:H146" si="84">IF(D40=1,1,D40*1.05)</f>
+        <f t="shared" ref="D146:H146" si="87">IF(D40=1,1,D40*1.05)</f>
         <v>1</v>
       </c>
       <c r="E146" s="103">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>1</v>
       </c>
       <c r="F146" s="103">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>1</v>
       </c>
       <c r="G146" s="103">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>1</v>
       </c>
       <c r="H146" s="103">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>1</v>
       </c>
     </row>
@@ -29024,23 +29618,23 @@
         <v>169</v>
       </c>
       <c r="D147" s="103">
-        <f t="shared" ref="D147:H147" si="85">IF(D41=1,1,D41*1.05)</f>
+        <f t="shared" ref="D147:H147" si="88">IF(D41=1,1,D41*1.05)</f>
         <v>1</v>
       </c>
       <c r="E147" s="103">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>1</v>
       </c>
       <c r="F147" s="103">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>1</v>
       </c>
       <c r="G147" s="103">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>1</v>
       </c>
       <c r="H147" s="103">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>1</v>
       </c>
     </row>
@@ -29052,23 +29646,23 @@
         <v>171</v>
       </c>
       <c r="D148" s="103">
-        <f t="shared" ref="D148:H148" si="86">IF(D42=1,1,D42*1.05)</f>
+        <f t="shared" ref="D148:H148" si="89">IF(D42=1,1,D42*1.05)</f>
         <v>1</v>
       </c>
       <c r="E148" s="103">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>1</v>
       </c>
       <c r="F148" s="103">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>1</v>
       </c>
       <c r="G148" s="103">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>1</v>
       </c>
       <c r="H148" s="103">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>1</v>
       </c>
     </row>
@@ -29078,23 +29672,23 @@
         <v>170</v>
       </c>
       <c r="D149" s="103">
-        <f t="shared" ref="D149:H149" si="87">IF(D43=1,1,D43*1.05)</f>
+        <f t="shared" ref="D149:H149" si="90">IF(D43=1,1,D43*1.05)</f>
         <v>1</v>
       </c>
       <c r="E149" s="103">
-        <f t="shared" si="87"/>
+        <f t="shared" si="90"/>
         <v>1</v>
       </c>
       <c r="F149" s="103">
-        <f t="shared" si="87"/>
+        <f t="shared" si="90"/>
         <v>1</v>
       </c>
       <c r="G149" s="103">
-        <f t="shared" si="87"/>
+        <f t="shared" si="90"/>
         <v>1</v>
       </c>
       <c r="H149" s="103">
-        <f t="shared" si="87"/>
+        <f t="shared" si="90"/>
         <v>1</v>
       </c>
     </row>
@@ -29104,23 +29698,23 @@
         <v>169</v>
       </c>
       <c r="D150" s="103">
-        <f t="shared" ref="D150:H150" si="88">IF(D44=1,1,D44*1.05)</f>
+        <f t="shared" ref="D150:H150" si="91">IF(D44=1,1,D44*1.05)</f>
         <v>1</v>
       </c>
       <c r="E150" s="103">
-        <f t="shared" si="88"/>
+        <f t="shared" si="91"/>
         <v>1</v>
       </c>
       <c r="F150" s="103">
-        <f t="shared" si="88"/>
+        <f t="shared" si="91"/>
         <v>1</v>
       </c>
       <c r="G150" s="103">
-        <f t="shared" si="88"/>
+        <f t="shared" si="91"/>
         <v>1</v>
       </c>
       <c r="H150" s="103">
-        <f t="shared" si="88"/>
+        <f t="shared" si="91"/>
         <v>1</v>
       </c>
     </row>
@@ -29132,23 +29726,23 @@
         <v>171</v>
       </c>
       <c r="D151" s="103">
-        <f t="shared" ref="D151:H151" si="89">IF(D45=1,1,D45*1.05)</f>
+        <f t="shared" ref="D151:H151" si="92">IF(D45=1,1,D45*1.05)</f>
         <v>1</v>
       </c>
       <c r="E151" s="103">
-        <f t="shared" si="89"/>
+        <f t="shared" si="92"/>
         <v>1</v>
       </c>
       <c r="F151" s="103">
-        <f t="shared" si="89"/>
+        <f t="shared" si="92"/>
         <v>1</v>
       </c>
       <c r="G151" s="103">
-        <f t="shared" si="89"/>
+        <f t="shared" si="92"/>
         <v>1</v>
       </c>
       <c r="H151" s="103">
-        <f t="shared" si="89"/>
+        <f t="shared" si="92"/>
         <v>1</v>
       </c>
     </row>
@@ -29158,23 +29752,23 @@
         <v>170</v>
       </c>
       <c r="D152" s="103">
-        <f t="shared" ref="D152:H152" si="90">IF(D46=1,1,D46*1.05)</f>
+        <f t="shared" ref="D152:H152" si="93">IF(D46=1,1,D46*1.05)</f>
         <v>1</v>
       </c>
       <c r="E152" s="103">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>1</v>
       </c>
       <c r="F152" s="103">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>1</v>
       </c>
       <c r="G152" s="103">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>1</v>
       </c>
       <c r="H152" s="103">
-        <f t="shared" si="90"/>
+        <f t="shared" si="93"/>
         <v>1</v>
       </c>
     </row>
@@ -29184,23 +29778,23 @@
         <v>169</v>
       </c>
       <c r="D153" s="103">
-        <f t="shared" ref="D153:H153" si="91">IF(D47=1,1,D47*1.05)</f>
+        <f t="shared" ref="D153:H153" si="94">IF(D47=1,1,D47*1.05)</f>
         <v>1</v>
       </c>
       <c r="E153" s="103">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>1</v>
       </c>
       <c r="F153" s="103">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>1</v>
       </c>
       <c r="G153" s="103">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>1</v>
       </c>
       <c r="H153" s="103">
-        <f t="shared" si="91"/>
+        <f t="shared" si="94"/>
         <v>1</v>
       </c>
     </row>
@@ -29212,23 +29806,23 @@
         <v>171</v>
       </c>
       <c r="D154" s="103">
-        <f t="shared" ref="D154:H154" si="92">IF(D48=1,1,D48*1.05)</f>
+        <f t="shared" ref="D154:H154" si="95">IF(D48=1,1,D48*1.05)</f>
         <v>1</v>
       </c>
       <c r="E154" s="103">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>1</v>
       </c>
       <c r="F154" s="103">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>1</v>
       </c>
       <c r="G154" s="103">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>1</v>
       </c>
       <c r="H154" s="103">
-        <f t="shared" si="92"/>
+        <f t="shared" si="95"/>
         <v>1</v>
       </c>
     </row>
@@ -29238,23 +29832,23 @@
         <v>170</v>
       </c>
       <c r="D155" s="103">
-        <f t="shared" ref="D155:H155" si="93">IF(D49=1,1,D49*1.05)</f>
+        <f t="shared" ref="D155:H155" si="96">IF(D49=1,1,D49*1.05)</f>
         <v>1</v>
       </c>
       <c r="E155" s="103">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>1</v>
       </c>
       <c r="F155" s="103">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>1</v>
       </c>
       <c r="G155" s="103">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>1</v>
       </c>
       <c r="H155" s="103">
-        <f t="shared" si="93"/>
+        <f t="shared" si="96"/>
         <v>1</v>
       </c>
     </row>
@@ -29264,23 +29858,23 @@
         <v>169</v>
       </c>
       <c r="D156" s="103">
-        <f t="shared" ref="D156:H156" si="94">IF(D50=1,1,D50*1.05)</f>
+        <f t="shared" ref="D156:H156" si="97">IF(D50=1,1,D50*1.05)</f>
         <v>1</v>
       </c>
       <c r="E156" s="103">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="F156" s="103">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="G156" s="103">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="H156" s="103">
-        <f t="shared" si="94"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
     </row>
@@ -29292,29 +29886,65 @@
         <v>169</v>
       </c>
       <c r="D157" s="103">
-        <f t="shared" ref="D157:H157" si="95">IF(D51=1,1,D51*1.05)</f>
+        <f t="shared" ref="D157:H157" si="98">IF(D51=1,1,D51*1.05)</f>
         <v>1</v>
       </c>
       <c r="E157" s="103">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>1</v>
       </c>
       <c r="F157" s="103">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>1</v>
       </c>
       <c r="G157" s="103">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>1</v>
       </c>
       <c r="H157" s="103">
-        <f t="shared" si="95"/>
+        <f t="shared" si="98"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="kNott2FY10++7LpzvuSEUUgvKblMKWlWyTJLQ7V3mUE+D/qQXgkJjdadeNqQ4e0dbATNIZiaZUbYZr3uwCKttQ==" saltValue="MboHEiRAGE0wfo213ZYZVw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="pz3msRwGv2o/tIWMhTTEZZzAkkRT1HM6S8HYVlp9/Jms3cGOApH8DM4Xp2TXX9TU2fPoXHbYFe22A7Iqp9qC5w==" saltValue="2tpXNEg+RSMo0cf9NzN8lg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="45">
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B125:B127"/>
     <mergeCell ref="B145:B147"/>
     <mergeCell ref="B148:B150"/>
     <mergeCell ref="B151:B153"/>
@@ -29324,46 +29954,10 @@
     <mergeCell ref="B134:B136"/>
     <mergeCell ref="B137:B139"/>
     <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="D158:H158 D108:H110 D142:H157 D55:H57 D72:H87 D125:H140 D89:H97 D66:H66 D64:E64 G64:H64 D65:E65 G65:H65 D69:H70 D67:F67 H67 D68:F68 H68 D100:H100 D98:E98 G98:H98 D99:E99 G99:H99 D103:H104 D101:F101 H101 D102:F102 H102 D119:H119 D117:E117 G117:H117 D118:E118 G118:H118 D122:H123 D120:F120 H120 D121:F121 H121 D60:H60 E58:H58 E59:H59 D63:H63 D61 F61:H61 D62 F62:H62 D113:H113 E111:H111 E112:H112 D116:H116 D114 F114:H114 D115 F115:H115" unlockedFormula="1"/>
+    <ignoredError sqref="D158:H158 D108:H110 D142:H157 D55:H57 D72:H87 D125:H140 D89:H97 H66 H64 H65 D69:H70 H67 H68 D100:H100 D98:E98 G98:H98 D99:E99 G99:H99 D103:H104 D101:F101 H101 D102:F102 H102 H119 H117 H118 D122:H123 H120 H121 H60 H58 H59 H63 H61 H62 H113 H111 H112 H116 H114 H115" unlockedFormula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -38714,7 +39308,7 @@
       <c r="I328" s="93"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1tfvvRE4M+vgwC7GiVJh8UWd9rYaMO2ID4FVARJWfxoJZRuabSnv5aYZjF5gU5Dq8AfGZ9OiwIwkdIqKnd3j8Q==" saltValue="gOCxMG9BScL982qe3BaWhw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jn+YCrMc4KkdPcrsO5k8rYtWCGFruoaVRvBsJuaZUIlOfnbhXjv7F6cvCtt5I2CFv7P/YCAKFudM8wZXFDt5bg==" saltValue="5xprtpmB1aBmU65xZhtqig==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
@@ -38913,7 +39507,7 @@
         <v>190</v>
       </c>
       <c r="C12" s="105">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D12" s="105">
         <v>1.39</v>
@@ -39249,7 +39843,7 @@
         <v>282</v>
       </c>
       <c r="C35" s="105">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="D35" s="105">
         <v>1.1100000000000001</v>
@@ -39605,7 +40199,7 @@
         <v>292</v>
       </c>
       <c r="C58" s="105">
-        <v>1.78</v>
+        <v>1</v>
       </c>
       <c r="D58" s="105">
         <v>1.74</v>
@@ -39754,7 +40348,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="3r0ndAu+RUH96hYdp6WO+AwhqNH3NdCl1iIQ1gOJediM4KZ6ZFChNm7EJWrxH9+qR/lxiuugH22Ay8HV8gJ1Ng==" saltValue="2Kh7azF7eJZU/t5Zk7zWnw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dz+YO4mpsUHjzkArdVsMWYAhRBi5teN81xhJqmYALsqZkryE3Pv70ju2pLsx1YjNffSBJTbsHlL1xCbk2FxDmA==" saltValue="LKq0rG+sWuMeAyb47aYb4Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
@@ -40578,7 +41172,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="LnjPs+tiryCjGlxIcCoc9VYZVK7anRAVHCvKud83EfjtgKW0vUQr2FSI3nvdju1neMs4gxoXRQGAXnwHTy0eGQ==" saltValue="uusuOaSrLiI1eiqZNmtU+w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="iu68EuaCfzXwacPqVfNIMbX9JWeIEFq4KIOCt1qjfnpgYlvJ4KaazCJ5M5zyWigZPmEGmFICU6rKqOcW12V6IA==" saltValue="t69o/cxEIA/3xRy9yjvUtA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
@@ -40658,10 +41252,10 @@
         <v>0.92</v>
       </c>
       <c r="D3" s="105">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="E3" s="105">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="F3" s="105">
         <v>1</v>
@@ -41469,14 +42063,13 @@
         <v>0.87</v>
       </c>
       <c r="D26" s="105">
-        <v>0.4</v>
+        <v>0.87</v>
       </c>
       <c r="E26" s="105">
-        <f t="shared" ref="E26:O26" si="1">IF(E3=1,1,E3*0.9)</f>
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="F26" s="105">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F26:O26" si="1">IF(F3=1,1,F3*0.9)</f>
         <v>1</v>
       </c>
       <c r="G26" s="105">
@@ -42398,14 +42991,13 @@
         <v>0.99</v>
       </c>
       <c r="D49" s="105">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="E49" s="105">
-        <f t="shared" ref="E49:O49" si="6">IF(E3=1,1,E3*1.05)</f>
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="F49" s="105">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="F49:O49" si="6">IF(F3=1,1,F3*1.05)</f>
         <v>1</v>
       </c>
       <c r="G49" s="105">
@@ -43268,7 +43860,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="YpA6JbbIyNNCAAhRjaoEttkYgV7fGrwEhDjKYZ2OCSpwzWlm782Eof8cRr+Z8CHrTCidfma6dSt/f77dCElh7Q==" saltValue="MkDqdd5l6/bsAXXLurhBUw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wHI2WTLDwVQf+OSC0WQ2fKTRTcIjefusbv3szhj9AUQG2pPSXKWMiMjb0outdkMMw+/MboAu+Oa++xwgXbfVBg==" saltValue="nOUG4vOk+vxqxTGOC/Bjcw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
@@ -44201,19 +44793,19 @@
         <v>262</v>
       </c>
       <c r="D28" s="105">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E28" s="105">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F28" s="105">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G28" s="105">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H28" s="105">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -45455,19 +46047,19 @@
         <v>262</v>
       </c>
       <c r="D83" s="105">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E83" s="105">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F83" s="105">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G83" s="105">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H83" s="105">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -46714,19 +47306,19 @@
         <v>262</v>
       </c>
       <c r="D138" s="105">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="E138" s="105">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="F138" s="105">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="G138" s="105">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="H138" s="105">
-        <v>0</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -47291,7 +47883,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="W7trpA30YWk5Jr/jScHRObXHTbskGlEnvWYvD30IOj42vYmMSULI7hj5MMMzKmnRnjAoTPBVv8QyGss+btXRNg==" saltValue="rKtIaAjK8h4IDBxFHcbbkQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="EaLmX473p5EynXS3R1Hb0k/p3P/bwZa/1cDtVwdXsnZOSYD4Rhi3dGyAf5Y4iTqSU46w3vMV5Fhz/1mI8KoaFQ==" saltValue="BcwSZ/QMPMDO2Rpo081TLw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
@@ -47797,7 +48389,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="K8oQd97EGTyELizd/OBv25NdUi0dfr+nHstdw1jgvK9KIw7xQQu4jOvKJk5azskLTZ5a8KxgKzCQTWejOXFNZg==" saltValue="W1MAFbsrhVC+a/zI9dICGA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bFi4UO/MYSy1ocOot5y7JdpTLSj3VYrhdtuVEmlekdzp7NtFBQZX4yNIi9A9S9nFic+mLseFiB4QMgSz7PmPmQ==" saltValue="0Yi1KsKDfpD+pl5y1FWoHw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="D20:G20 D11:G11 D13:G16 D22:G22 D24:G24" unlockedFormula="1"/>
@@ -49196,6 +49788,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MediaLengthInSeconds xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -49204,17 +49807,9 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MediaLengthInSeconds xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="107b52809c0cc4b5077f1ac81d3c69cc">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="82b7e1b740270cfb0676be859a78f3d0" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f77cb9dc30d15950233dec29875e7d3d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c7972fb108f377c3e0c6a81e726e76be" ns2:_="">
     <xsd:import namespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -49228,6 +49823,10 @@
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -49266,6 +49865,30 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="15" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9012861f-df9c-4ac0-92bd-da4c61c7cfda" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -49369,14 +49992,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87E89A13-0449-4026-BB40-CE009D889E15}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F25ACC24-A23B-4F66-B2C3-F39116C08A35}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -49386,8 +50001,16 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87E89A13-0449-4026-BB40-CE009D889E15}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07F27224-E052-49D0-B72B-C9073A8D27C1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F57CCE8-B32C-43EE-BC7A-182980A6518B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>

--- a/inputs/en/template_input.xlsx
+++ b/inputs/en/template_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\Nutrition\inputs\en\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nick.scott\Desktop\Github\Nutrition\inputs\en\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686DF5B5-CCE4-4F3E-84EB-47399811522A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33161460-8B83-4D55-8A6C-FB40619725F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" firstSheet="9" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-6690" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline year population inputs" sheetId="1" r:id="rId1"/>
@@ -32,15 +32,15 @@
     <sheet name="Programs impacted population" sheetId="62" state="hidden" r:id="rId17"/>
     <sheet name="Program risk areas" sheetId="63" state="hidden" r:id="rId18"/>
     <sheet name="Population risk areas" sheetId="64" state="hidden" r:id="rId19"/>
-    <sheet name="IYCF odds ratios" sheetId="65" r:id="rId20"/>
+    <sheet name="IYCF odds ratios" sheetId="65" state="hidden" r:id="rId20"/>
     <sheet name="Birth outcome risks" sheetId="66" state="hidden" r:id="rId21"/>
-    <sheet name="Relative risks" sheetId="67" r:id="rId22"/>
-    <sheet name="Odds ratios" sheetId="68" r:id="rId23"/>
+    <sheet name="Relative risks" sheetId="67" state="hidden" r:id="rId22"/>
+    <sheet name="Odds ratios" sheetId="68" state="hidden" r:id="rId23"/>
     <sheet name="Programs birth outcomes" sheetId="69" state="hidden" r:id="rId24"/>
     <sheet name="Programs anaemia" sheetId="70" state="hidden" r:id="rId25"/>
     <sheet name="Programs wasting" sheetId="71" state="hidden" r:id="rId26"/>
     <sheet name="Programs for children" sheetId="72" state="hidden" r:id="rId27"/>
-    <sheet name="Programs for PW" sheetId="73" r:id="rId28"/>
+    <sheet name="Programs for PW" sheetId="73" state="hidden" r:id="rId28"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Birth outcome risks'!$A$1:$F$7</definedName>
@@ -2176,6 +2176,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Tharindu Wickramaarachchi</author>
+    <author>Nick Scott</author>
   </authors>
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{166723AE-E51E-4F40-A274-B6EBC85AD771}">
@@ -2428,53 +2429,31 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{F7500351-DA6F-4F44-87A6-7AC156F04628}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
- Oh et al 2020, RR 0.93 (0.88-0.98) for MMS vs IFAS
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{50ABAC41-54A6-4BCC-9241-86698E44E615}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
- Oh et al 2020, RR 0.93 (0.88-0.98) for MMS vs IFAS
-</t>
+    <comment ref="C12" authorId="1" shapeId="0" xr:uid="{0E969848-D0FC-4A0C-91AD-A00EA30AE589}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Nick Scott:
+Hofmeyr et al 2023, 0.90 (0.84-0.96) for MMS vs IFAS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="1" shapeId="0" xr:uid="{000C1F78-5A43-480F-A266-9DEB70A415C9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Nick Scott:
+Hofmeyr et al 2023, 0.90 (0.84-0.96) for MMS vs IFAS</t>
         </r>
       </text>
     </comment>
@@ -2722,53 +2701,31 @@
         </r>
       </text>
     </comment>
-    <comment ref="C27" authorId="0" shapeId="0" xr:uid="{C71D45C2-56FD-457B-9459-B4CC5C46796D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
- Oh et al 2020, RR 0.93 (0.88-0.98) for MMS vs I/IFA
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D27" authorId="0" shapeId="0" xr:uid="{F28C7F2B-6E97-441B-BE2B-4094627C7813}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
- Oh et al 2020, RR 0.93 (0.88-0.98) for MMS vs I/IFA
-</t>
+    <comment ref="C27" authorId="1" shapeId="0" xr:uid="{B61D4B92-D1A4-4C23-B51F-2F9663D6BB57}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Nick Scott:
+Hofmeyr et al 2023, 0.90 (0.84-0.96) for MMS vs IFAS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D27" authorId="1" shapeId="0" xr:uid="{B31AF3AD-97F5-453F-865B-549844C813BC}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Nick Scott:
+Hofmeyr et al 2023, 0.90 (0.84-0.96) for MMS vs IFAS</t>
         </r>
       </text>
     </comment>
@@ -3016,53 +2973,31 @@
         </r>
       </text>
     </comment>
-    <comment ref="C42" authorId="0" shapeId="0" xr:uid="{A86B5092-2A61-4D66-BC90-A401BC85EF39}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
- Oh et al 2020, RR 0.93 (0.88-0.98) for MMS vs I/IFA
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D42" authorId="0" shapeId="0" xr:uid="{364CA5BD-5B55-4CCC-9AF3-8A71B7C376B3}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
- Oh et al 2020, RR 0.93 (0.88-0.98) for MMS vs I/IFA
-</t>
+    <comment ref="C42" authorId="1" shapeId="0" xr:uid="{3BE20510-830B-4C54-937E-C9D0B7007AA2}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Nick Scott:
+Hofmeyr et al 2023, 0.90 (0.84-0.96) for MMS vs IFAS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D42" authorId="1" shapeId="0" xr:uid="{1542143F-278C-4CDD-A6C6-876C476820A6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Nick Scott:
+Hofmeyr et al 2023, 0.90 (0.84-0.96) for MMS vs IFAS</t>
         </r>
       </text>
     </comment>
@@ -18889,14 +18824,14 @@
     <tabColor rgb="FF007600"/>
   </sheetPr>
   <dimension ref="A1:E63"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.6328125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="38.6328125" style="11" customWidth="1"/>
-    <col min="3" max="16384" width="14.453125" style="8"/>
+    <col min="1" max="1" width="27.6640625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="38.6640625" style="11" customWidth="1"/>
+    <col min="3" max="16384" width="14.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
@@ -18907,14 +18842,14 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>186</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
     </row>
-    <row r="3" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="5" t="s">
         <v>188</v>
@@ -18923,7 +18858,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="5" t="s">
         <v>187</v>
@@ -18932,7 +18867,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="31"/>
       <c r="C5" s="31"/>
@@ -18991,7 +18926,7 @@
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="8"/>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>30</v>
       </c>
@@ -19098,7 +19033,7 @@
       </c>
       <c r="C32" s="116"/>
     </row>
-    <row r="33" spans="1:5" ht="13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B33" s="27" t="s">
         <v>124</v>
       </c>
@@ -19108,7 +19043,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>130</v>
       </c>
@@ -19276,7 +19211,7 @@
       </c>
       <c r="C62" s="52"/>
     </row>
-    <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
     </row>
   </sheetData>
@@ -19293,19 +19228,19 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56" style="40" customWidth="1"/>
     <col min="2" max="2" width="20" style="28" customWidth="1"/>
-    <col min="3" max="3" width="20.453125" style="28" customWidth="1"/>
-    <col min="4" max="4" width="20.08984375" style="28" customWidth="1"/>
-    <col min="5" max="5" width="36.36328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" style="28" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" style="28" customWidth="1"/>
+    <col min="5" max="5" width="36.33203125" style="28" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.6328125" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="14.453125" style="28"/>
+    <col min="7" max="7" width="22.6640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="14.44140625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
         <v>69</v>
       </c>
@@ -20106,15 +20041,15 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53" style="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="47.90625" style="28" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" style="28" customWidth="1"/>
-    <col min="4" max="16384" width="11.453125" style="28"/>
+    <col min="2" max="2" width="47.88671875" style="28" customWidth="1"/>
+    <col min="3" max="3" width="42.44140625" style="28" customWidth="1"/>
+    <col min="4" max="16384" width="11.44140625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>69</v>
       </c>
@@ -20262,13 +20197,13 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:A19"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.08984375" style="28" customWidth="1"/>
-    <col min="2" max="16384" width="11.453125" style="28"/>
+    <col min="1" max="1" width="30.109375" style="28" customWidth="1"/>
+    <col min="2" max="16384" width="11.44140625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>69</v>
       </c>
@@ -20357,7 +20292,7 @@
     <tabColor theme="0" tint="-0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
@@ -20466,19 +20401,19 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.90625" customWidth="1"/>
-    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.88671875" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="15.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
@@ -20525,7 +20460,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>31</v>
       </c>
@@ -21086,7 +21021,7 @@
     <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="9"/>
     </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>32</v>
       </c>
@@ -21137,7 +21072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="5" t="s">
         <v>86</v>
@@ -21182,7 +21117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="5" t="s">
         <v>182</v>
@@ -21231,7 +21166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="5" t="s">
         <v>202</v>
@@ -21467,7 +21402,7 @@
     <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="9"/>
     </row>
-    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>37</v>
       </c>
@@ -21717,7 +21652,7 @@
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
     </row>
-    <row r="30" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>35</v>
       </c>
@@ -22222,7 +22157,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
@@ -22255,16 +22190,16 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.6328125" style="28" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" style="28" customWidth="1"/>
-    <col min="3" max="4" width="11.453125" style="28"/>
-    <col min="5" max="5" width="17.453125" style="28" customWidth="1"/>
-    <col min="6" max="16384" width="11.453125" style="28"/>
+    <col min="1" max="1" width="33.6640625" style="28" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" style="28" customWidth="1"/>
+    <col min="3" max="4" width="11.44140625" style="28"/>
+    <col min="5" max="5" width="17.44140625" style="28" customWidth="1"/>
+    <col min="6" max="16384" width="11.44140625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>158</v>
       </c>
@@ -22281,7 +22216,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
         <v>153</v>
       </c>
@@ -22299,7 +22234,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
         <v>152</v>
       </c>
@@ -22317,7 +22252,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
         <v>151</v>
       </c>
@@ -22335,7 +22270,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
         <v>150</v>
       </c>
@@ -22353,7 +22288,7 @@
         <v>0.126</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
         <v>149</v>
       </c>
@@ -22371,7 +22306,7 @@
         <v>1.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
         <v>148</v>
       </c>
@@ -22389,7 +22324,7 @@
         <v>0.40500000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
         <v>147</v>
       </c>
@@ -22407,7 +22342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
         <v>146</v>
       </c>
@@ -22425,7 +22360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
         <v>145</v>
       </c>
@@ -22456,20 +22391,20 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:P42"/>
-  <sheetFormatPr defaultColWidth="16.08984375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.1796875" style="43" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.90625" style="43" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.453125" style="43" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.08984375" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.21875" style="43" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.88671875" style="43" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" style="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" style="43" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" style="43" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.08984375" style="43" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="15.36328125" style="43" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="16.90625" style="43" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="16.08984375" style="43"/>
+    <col min="6" max="7" width="13.109375" style="43" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="15.33203125" style="43" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="16.88671875" style="43" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="16.109375" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
         <v>33</v>
       </c>
@@ -22516,7 +22451,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="44" t="s">
         <v>31</v>
       </c>
@@ -22563,7 +22498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="40" t="s">
         <v>144</v>
       </c>
@@ -22607,7 +22542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="40" t="s">
         <v>168</v>
       </c>
@@ -22651,7 +22586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="40" t="s">
         <v>193</v>
       </c>
@@ -22695,7 +22630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="40" t="s">
         <v>194</v>
       </c>
@@ -22739,7 +22674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="40" t="s">
         <v>190</v>
       </c>
@@ -22783,7 +22718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="40" t="s">
         <v>131</v>
       </c>
@@ -22827,7 +22762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="40" t="s">
         <v>132</v>
       </c>
@@ -22871,7 +22806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="40" t="s">
         <v>84</v>
       </c>
@@ -22915,7 +22850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="40" t="s">
         <v>58</v>
       </c>
@@ -22959,7 +22894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="40" t="s">
         <v>337</v>
       </c>
@@ -23003,7 +22938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -23047,7 +22982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="40" t="s">
         <v>28</v>
       </c>
@@ -23091,7 +23026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="40" t="s">
         <v>85</v>
       </c>
@@ -23135,7 +23070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="40" t="s">
         <v>60</v>
       </c>
@@ -23179,7 +23114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="40"/>
       <c r="C17" s="99"/>
       <c r="D17" s="99"/>
@@ -23195,7 +23130,7 @@
       <c r="N17" s="99"/>
       <c r="O17" s="99"/>
     </row>
-    <row r="18" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="44" t="s">
         <v>32</v>
       </c>
@@ -23242,7 +23177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="44"/>
       <c r="B19" s="40" t="s">
         <v>86</v>
@@ -23287,7 +23222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="73" t="s">
         <v>182</v>
       </c>
@@ -23331,7 +23266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="73" t="s">
         <v>202</v>
       </c>
@@ -23375,7 +23310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="74" t="s">
         <v>57</v>
       </c>
@@ -23419,7 +23354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="40" t="s">
         <v>88</v>
       </c>
@@ -23463,7 +23398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="40" t="s">
         <v>87</v>
       </c>
@@ -23507,7 +23442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="40" t="s">
         <v>59</v>
       </c>
@@ -23551,7 +23486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="40"/>
       <c r="C26" s="99"/>
       <c r="D26" s="99"/>
@@ -23567,7 +23502,7 @@
       <c r="N26" s="99"/>
       <c r="O26" s="99"/>
     </row>
-    <row r="27" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="44" t="s">
         <v>37</v>
       </c>
@@ -23615,7 +23550,7 @@
       </c>
       <c r="P27" s="75"/>
     </row>
-    <row r="28" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="46" t="s">
         <v>183</v>
       </c>
@@ -23659,7 +23594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="44"/>
       <c r="B29" s="46" t="s">
         <v>201</v>
@@ -23704,7 +23639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="46" t="s">
         <v>184</v>
       </c>
@@ -23748,7 +23683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="46" t="s">
         <v>185</v>
       </c>
@@ -23792,7 +23727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="40"/>
       <c r="C32" s="100"/>
       <c r="D32" s="100"/>
@@ -23808,7 +23743,7 @@
       <c r="N32" s="99"/>
       <c r="O32" s="99"/>
     </row>
-    <row r="33" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="44" t="s">
         <v>35</v>
       </c>
@@ -23855,7 +23790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="40" t="s">
         <v>64</v>
       </c>
@@ -23899,7 +23834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="40" t="s">
         <v>62</v>
       </c>
@@ -23943,7 +23878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="40" t="s">
         <v>47</v>
       </c>
@@ -23987,7 +23922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="40" t="s">
         <v>34</v>
       </c>
@@ -24031,7 +23966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="40" t="s">
         <v>83</v>
       </c>
@@ -24075,7 +24010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="40" t="s">
         <v>82</v>
       </c>
@@ -24119,7 +24054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="40" t="s">
         <v>81</v>
       </c>
@@ -24163,7 +24098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="40" t="s">
         <v>79</v>
       </c>
@@ -24207,7 +24142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="40" t="s">
         <v>80</v>
       </c>
@@ -24263,22 +24198,22 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="58.90625" style="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6328125" style="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.90625" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.36328125" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.453125" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.54296875" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.90625" style="28" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.81640625" style="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.36328125" style="28" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="12.81640625" style="28"/>
+    <col min="1" max="1" width="58.88671875" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="12.77734375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>69</v>
       </c>
@@ -25025,22 +24960,22 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.90625" style="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6328125" style="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.90625" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.36328125" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.453125" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.54296875" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.90625" style="28" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.81640625" style="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.36328125" style="28" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="12.81640625" style="28"/>
+    <col min="1" max="1" width="16.88671875" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="12.77734375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>211</v>
       </c>
@@ -25394,14 +25329,14 @@
     <tabColor rgb="FF007600"/>
   </sheetPr>
   <dimension ref="A1:I40"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.453125" style="8" customWidth="1"/>
-    <col min="2" max="9" width="16.90625" style="8" customWidth="1"/>
-    <col min="10" max="16384" width="14.453125" style="8"/>
+    <col min="1" max="1" width="8.44140625" style="8" customWidth="1"/>
+    <col min="2" max="9" width="16.88671875" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="14.44140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -26129,15 +26064,15 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:J157"/>
-  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.08984375" style="28" customWidth="1"/>
+    <col min="1" max="1" width="48.109375" style="28" customWidth="1"/>
     <col min="2" max="2" width="15" style="28" customWidth="1"/>
-    <col min="3" max="3" width="14.6328125" style="28" customWidth="1"/>
-    <col min="4" max="16384" width="12.81640625" style="28"/>
+    <col min="3" max="3" width="14.6640625" style="28" customWidth="1"/>
+    <col min="4" max="16384" width="12.77734375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>212</v>
       </c>
@@ -26163,7 +26098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>213</v>
       </c>
@@ -26493,7 +26428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B17" s="77" t="s">
         <v>167</v>
       </c>
@@ -26523,7 +26458,7 @@
       <c r="G18" s="101"/>
       <c r="H18" s="101"/>
     </row>
-    <row r="19" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="30" t="s">
         <v>214</v>
       </c>
@@ -26851,7 +26786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B34" s="77" t="s">
         <v>167</v>
       </c>
@@ -26881,7 +26816,7 @@
       <c r="G35" s="101"/>
       <c r="H35" s="101"/>
     </row>
-    <row r="36" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="78" t="s">
         <v>215</v>
       </c>
@@ -27209,7 +27144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B51" s="77" t="s">
         <v>167</v>
       </c>
@@ -27232,7 +27167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="107" t="s">
         <v>267</v>
       </c>
@@ -27244,7 +27179,7 @@
       <c r="G53" s="107"/>
       <c r="H53" s="107"/>
     </row>
-    <row r="54" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>212</v>
       </c>
@@ -27270,7 +27205,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="30" t="s">
         <v>311</v>
       </c>
@@ -27665,7 +27600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B70" s="77" t="s">
         <v>167</v>
       </c>
@@ -27700,7 +27635,7 @@
       <c r="G71" s="101"/>
       <c r="H71" s="101"/>
     </row>
-    <row r="72" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="30" t="s">
         <v>312</v>
       </c>
@@ -28103,7 +28038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B87" s="77" t="s">
         <v>167</v>
       </c>
@@ -28138,7 +28073,7 @@
       <c r="G88" s="101"/>
       <c r="H88" s="101"/>
     </row>
-    <row r="89" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="78" t="s">
         <v>313</v>
       </c>
@@ -28541,7 +28476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B104" s="77" t="s">
         <v>167</v>
       </c>
@@ -28569,7 +28504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="107" t="s">
         <v>268</v>
       </c>
@@ -28581,7 +28516,7 @@
       <c r="G106" s="107"/>
       <c r="H106" s="107"/>
     </row>
-    <row r="107" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="30" t="s">
         <v>212</v>
       </c>
@@ -28607,7 +28542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="30" t="s">
         <v>314</v>
       </c>
@@ -29002,7 +28937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B123" s="77" t="s">
         <v>167</v>
       </c>
@@ -29037,7 +28972,7 @@
       <c r="G124" s="101"/>
       <c r="H124" s="101"/>
     </row>
-    <row r="125" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="30" t="s">
         <v>315</v>
       </c>
@@ -29440,7 +29375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B140" s="77" t="s">
         <v>167</v>
       </c>
@@ -29475,7 +29410,7 @@
       <c r="G141" s="101"/>
       <c r="H141" s="101"/>
     </row>
-    <row r="142" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="78" t="s">
         <v>316</v>
       </c>
@@ -29878,7 +29813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="2:8" ht="13" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B157" s="77" t="s">
         <v>167</v>
       </c>
@@ -29909,12 +29844,36 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="pz3msRwGv2o/tIWMhTTEZZzAkkRT1HM6S8HYVlp9/Jms3cGOApH8DM4Xp2TXX9TU2fPoXHbYFe22A7Iqp9qC5w==" saltValue="2tpXNEg+RSMo0cf9NzN8lg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="45">
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="B148:B150"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B67:B69"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="B48:B50"/>
@@ -29924,36 +29883,12 @@
     <mergeCell ref="B31:B33"/>
     <mergeCell ref="B36:B38"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="B148:B150"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="B134:B136"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -29969,22 +29904,22 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:F79"/>
-  <sheetFormatPr defaultColWidth="16.08984375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.90625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="34.08984375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="11.36328125" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" style="28" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="34.109375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" style="28" customWidth="1"/>
     <col min="5" max="6" width="15" style="28" customWidth="1"/>
-    <col min="7" max="16384" width="16.08984375" style="28"/>
+    <col min="7" max="16384" width="16.109375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="80" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="80" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="81"/>
       <c r="C2" s="82" t="s">
         <v>26</v>
@@ -29999,7 +29934,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
         <v>217</v>
       </c>
@@ -30083,7 +30018,7 @@
       <c r="E8" s="76"/>
       <c r="F8" s="76"/>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
         <v>218</v>
       </c>
@@ -30106,7 +30041,7 @@
       <c r="E10" s="76"/>
       <c r="F10" s="76"/>
     </row>
-    <row r="11" spans="1:6" s="80" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" s="80" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="79" t="s">
         <v>219</v>
       </c>
@@ -30115,7 +30050,7 @@
       <c r="E11" s="89"/>
       <c r="F11" s="89"/>
     </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="30" t="s">
         <v>220</v>
       </c>
@@ -30175,7 +30110,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="30"/>
       <c r="B16" s="46"/>
       <c r="C16" s="90"/>
@@ -30183,7 +30118,7 @@
       <c r="E16" s="76"/>
       <c r="F16" s="76"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="30" t="s">
         <v>224</v>
       </c>
@@ -30332,7 +30267,7 @@
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="46"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="107" t="s">
         <v>267</v>
       </c>
@@ -30342,12 +30277,12 @@
       <c r="E27" s="110"/>
       <c r="F27" s="110"/>
     </row>
-    <row r="28" spans="1:6" s="80" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" s="80" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="79" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="81"/>
       <c r="C29" s="82" t="s">
         <v>26</v>
@@ -30362,7 +30297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="30" t="s">
         <v>297</v>
       </c>
@@ -30462,7 +30397,7 @@
       <c r="E35" s="76"/>
       <c r="F35" s="76"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="30" t="s">
         <v>304</v>
       </c>
@@ -30483,7 +30418,7 @@
         <v>1.377</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="79" t="s">
         <v>219</v>
       </c>
@@ -30493,7 +30428,7 @@
       <c r="E38" s="89"/>
       <c r="F38" s="89"/>
     </row>
-    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="30" t="s">
         <v>298</v>
       </c>
@@ -30565,7 +30500,7 @@
         <v>3.7710000000000004</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="30"/>
       <c r="B43" s="46"/>
       <c r="C43" s="90"/>
@@ -30573,7 +30508,7 @@
       <c r="E43" s="76"/>
       <c r="F43" s="76"/>
     </row>
-    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="30" t="s">
         <v>302</v>
       </c>
@@ -30751,7 +30686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="107" t="s">
         <v>268</v>
       </c>
@@ -30761,12 +30696,12 @@
       <c r="E54" s="110"/>
       <c r="F54" s="110"/>
     </row>
-    <row r="55" spans="1:6" s="80" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" s="80" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="79" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="81"/>
       <c r="C56" s="82" t="s">
         <v>26</v>
@@ -30781,7 +30716,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="30" t="s">
         <v>303</v>
       </c>
@@ -30881,7 +30816,7 @@
       <c r="E62" s="76"/>
       <c r="F62" s="76"/>
     </row>
-    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="30" t="s">
         <v>305</v>
       </c>
@@ -30902,7 +30837,7 @@
         <v>1.6830000000000003</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="79" t="s">
         <v>219</v>
       </c>
@@ -30912,7 +30847,7 @@
       <c r="E65" s="89"/>
       <c r="F65" s="89"/>
     </row>
-    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="30" t="s">
         <v>306</v>
       </c>
@@ -30984,7 +30919,7 @@
         <v>4.6090000000000009</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="30"/>
       <c r="B70" s="46"/>
       <c r="C70" s="90"/>
@@ -30992,7 +30927,7 @@
       <c r="E70" s="76"/>
       <c r="F70" s="76"/>
     </row>
-    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="30" t="s">
         <v>310</v>
       </c>
@@ -31187,23 +31122,23 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:P328"/>
-  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.1796875" style="28" customWidth="1"/>
-    <col min="2" max="2" width="26.90625" style="28" customWidth="1"/>
-    <col min="3" max="3" width="18.36328125" style="28" customWidth="1"/>
-    <col min="4" max="8" width="14.81640625" style="28" customWidth="1"/>
-    <col min="9" max="12" width="15.36328125" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="16.90625" style="28" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="12.81640625" style="28"/>
+    <col min="1" max="1" width="27.21875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" style="28" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="28" customWidth="1"/>
+    <col min="4" max="8" width="14.77734375" style="28" customWidth="1"/>
+    <col min="9" max="12" width="15.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="16.88671875" style="28" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="12.77734375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="80" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="93" t="s">
         <v>206</v>
       </c>
@@ -31237,7 +31172,7 @@
       <c r="O2" s="94"/>
       <c r="P2" s="94"/>
     </row>
-    <row r="3" spans="1:16" ht="13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="30"/>
       <c r="B3" s="28" t="s">
         <v>71</v>
@@ -31670,7 +31605,7 @@
       <c r="O17" s="93"/>
       <c r="P17" s="93"/>
     </row>
-    <row r="18" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="32" t="s">
         <v>231</v>
       </c>
@@ -31928,12 +31863,12 @@
       <c r="O26" s="93"/>
       <c r="P26" s="93"/>
     </row>
-    <row r="28" spans="1:16" s="80" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="79" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="93" t="s">
         <v>233</v>
       </c>
@@ -31967,7 +31902,7 @@
       <c r="O29" s="94"/>
       <c r="P29" s="94"/>
     </row>
-    <row r="30" spans="1:16" ht="13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="30"/>
       <c r="B30" s="28" t="s">
         <v>71</v>
@@ -32662,12 +32597,12 @@
       <c r="C54" s="32"/>
       <c r="D54" s="32"/>
     </row>
-    <row r="55" spans="1:16" s="80" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="79" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="26" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A56" s="93" t="s">
         <v>70</v>
       </c>
@@ -32695,7 +32630,7 @@
       <c r="O56" s="94"/>
       <c r="P56" s="94"/>
     </row>
-    <row r="57" spans="1:16" ht="13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="30"/>
       <c r="B57" s="28" t="s">
         <v>38</v>
@@ -32841,12 +32776,12 @@
       <c r="C63" s="32"/>
       <c r="D63" s="32"/>
     </row>
-    <row r="64" spans="1:16" s="80" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="79" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="26" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A65" s="93" t="s">
         <v>24</v>
       </c>
@@ -32880,7 +32815,7 @@
       <c r="O65" s="94"/>
       <c r="P65" s="94"/>
     </row>
-    <row r="66" spans="1:16" ht="13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="97"/>
       <c r="B66" s="28" t="s">
         <v>73</v>
@@ -33916,12 +33851,12 @@
       <c r="O101" s="93"/>
       <c r="P101" s="93"/>
     </row>
-    <row r="103" spans="1:16" s="80" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="79" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="26" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A104" s="93" t="s">
         <v>71</v>
       </c>
@@ -33955,7 +33890,7 @@
       <c r="O104" s="94"/>
       <c r="P104" s="94"/>
     </row>
-    <row r="105" spans="1:16" ht="13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="30"/>
       <c r="C105" s="32" t="s">
         <v>161</v>
@@ -34068,13 +34003,13 @@
       <c r="O108" s="93"/>
       <c r="P108" s="93"/>
     </row>
-    <row r="110" spans="1:16" s="108" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" s="108" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="107" t="s">
         <v>267</v>
       </c>
       <c r="H110" s="107"/>
     </row>
-    <row r="111" spans="1:16" ht="13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="79" t="s">
         <v>225</v>
       </c>
@@ -34086,7 +34021,7 @@
       <c r="G111" s="80"/>
       <c r="H111" s="80"/>
     </row>
-    <row r="112" spans="1:16" ht="13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="93" t="s">
         <v>206</v>
       </c>
@@ -34112,7 +34047,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="30"/>
       <c r="B113" s="28" t="s">
         <v>71</v>
@@ -34731,7 +34666,7 @@
         <v>2.7090000000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="79" t="s">
         <v>232</v>
       </c>
@@ -34743,7 +34678,7 @@
       <c r="G138" s="80"/>
       <c r="H138" s="80"/>
     </row>
-    <row r="139" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="93" t="s">
         <v>233</v>
       </c>
@@ -34769,7 +34704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="30"/>
       <c r="B140" s="28" t="s">
         <v>71</v>
@@ -35392,7 +35327,7 @@
       <c r="C164" s="32"/>
       <c r="D164" s="32"/>
     </row>
-    <row r="165" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="79" t="s">
         <v>235</v>
       </c>
@@ -35404,7 +35339,7 @@
       <c r="G165" s="80"/>
       <c r="H165" s="80"/>
     </row>
-    <row r="166" spans="1:8" ht="26" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A166" s="93" t="s">
         <v>70</v>
       </c>
@@ -35428,7 +35363,7 @@
       </c>
       <c r="H166" s="94"/>
     </row>
-    <row r="167" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="30"/>
       <c r="B167" s="28" t="s">
         <v>38</v>
@@ -35574,7 +35509,7 @@
       <c r="C173" s="32"/>
       <c r="D173" s="32"/>
     </row>
-    <row r="174" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="79" t="s">
         <v>239</v>
       </c>
@@ -35586,7 +35521,7 @@
       <c r="G174" s="80"/>
       <c r="H174" s="80"/>
     </row>
-    <row r="175" spans="1:8" ht="26" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A175" s="93" t="s">
         <v>24</v>
       </c>
@@ -35612,7 +35547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="97"/>
       <c r="B176" s="28" t="s">
         <v>73</v>
@@ -36504,7 +36439,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="79" t="s">
         <v>241</v>
       </c>
@@ -36516,7 +36451,7 @@
       <c r="G213" s="80"/>
       <c r="H213" s="80"/>
     </row>
-    <row r="214" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A214" s="93" t="s">
         <v>71</v>
       </c>
@@ -36542,7 +36477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="30"/>
       <c r="C215" s="32" t="s">
         <v>161</v>
@@ -36639,13 +36574,13 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="220" spans="1:9" s="108" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" s="108" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="107" t="s">
         <v>268</v>
       </c>
       <c r="H220" s="107"/>
     </row>
-    <row r="221" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="79" t="s">
         <v>225</v>
       </c>
@@ -36658,7 +36593,7 @@
       <c r="H221" s="80"/>
       <c r="I221" s="80"/>
     </row>
-    <row r="222" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="93" t="s">
         <v>206</v>
       </c>
@@ -36685,7 +36620,7 @@
       </c>
       <c r="I222" s="94"/>
     </row>
-    <row r="223" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="30"/>
       <c r="B223" s="28" t="s">
         <v>71</v>
@@ -37328,7 +37263,7 @@
       </c>
       <c r="I246" s="93"/>
     </row>
-    <row r="248" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="79" t="s">
         <v>232</v>
       </c>
@@ -37341,7 +37276,7 @@
       <c r="H248" s="80"/>
       <c r="I248" s="80"/>
     </row>
-    <row r="249" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="93" t="s">
         <v>233</v>
       </c>
@@ -37368,7 +37303,7 @@
       </c>
       <c r="I249" s="94"/>
     </row>
-    <row r="250" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="30"/>
       <c r="B250" s="28" t="s">
         <v>71</v>
@@ -38015,7 +37950,7 @@
       <c r="C274" s="32"/>
       <c r="D274" s="32"/>
     </row>
-    <row r="275" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="79" t="s">
         <v>235</v>
       </c>
@@ -38028,7 +37963,7 @@
       <c r="H275" s="80"/>
       <c r="I275" s="80"/>
     </row>
-    <row r="276" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A276" s="93" t="s">
         <v>70</v>
       </c>
@@ -38052,7 +37987,7 @@
       </c>
       <c r="H276" s="94"/>
     </row>
-    <row r="277" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="30"/>
       <c r="B277" s="28" t="s">
         <v>38</v>
@@ -38198,7 +38133,7 @@
       <c r="C283" s="32"/>
       <c r="D283" s="32"/>
     </row>
-    <row r="284" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="79" t="s">
         <v>239</v>
       </c>
@@ -38211,7 +38146,7 @@
       <c r="H284" s="80"/>
       <c r="I284" s="80"/>
     </row>
-    <row r="285" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A285" s="93" t="s">
         <v>24</v>
       </c>
@@ -38238,7 +38173,7 @@
       </c>
       <c r="I285" s="94"/>
     </row>
-    <row r="286" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="97"/>
       <c r="B286" s="28" t="s">
         <v>73</v>
@@ -39166,7 +39101,7 @@
       </c>
       <c r="I321" s="93"/>
     </row>
-    <row r="323" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" s="79" t="s">
         <v>241</v>
       </c>
@@ -39179,7 +39114,7 @@
       <c r="H323" s="80"/>
       <c r="I323" s="80"/>
     </row>
-    <row r="324" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A324" s="93" t="s">
         <v>71</v>
       </c>
@@ -39206,7 +39141,7 @@
       </c>
       <c r="I324" s="94"/>
     </row>
-    <row r="325" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" s="30"/>
       <c r="C325" s="32" t="s">
         <v>161</v>
@@ -39324,24 +39259,24 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G67"/>
-  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.90625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="44.453125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" style="28" customWidth="1"/>
-    <col min="4" max="4" width="17.54296875" style="28" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" style="28" customWidth="1"/>
+    <col min="1" max="1" width="44.88671875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="44.44140625" style="28" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" style="28" customWidth="1"/>
+    <col min="4" max="4" width="17.5546875" style="28" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" style="28" customWidth="1"/>
     <col min="6" max="6" width="15" style="28" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" style="28" customWidth="1"/>
-    <col min="8" max="16384" width="12.81640625" style="28"/>
+    <col min="7" max="7" width="13.6640625" style="28" customWidth="1"/>
+    <col min="8" max="16384" width="12.77734375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="79" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="97" t="s">
         <v>25</v>
       </c>
@@ -39382,7 +39317,7 @@
         <v>174.7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="30"/>
       <c r="B4" s="73" t="s">
         <v>245</v>
@@ -39403,7 +39338,7 @@
         <v>1.0249999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="84" t="s">
         <v>246</v>
       </c>
@@ -39496,12 +39431,12 @@
       <c r="F10" s="73"/>
       <c r="G10" s="73"/>
     </row>
-    <row r="11" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="79" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="84"/>
       <c r="B12" s="46" t="s">
         <v>190</v>
@@ -39522,16 +39457,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="84"/>
       <c r="B13" s="46"/>
     </row>
-    <row r="14" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="79" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="97" t="s">
         <v>233</v>
       </c>
@@ -39554,7 +39489,7 @@
         <v>1.024</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="30"/>
       <c r="B16" s="73" t="s">
         <v>250</v>
@@ -39575,7 +39510,7 @@
         <v>1.024</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="97" t="s">
         <v>70</v>
       </c>
@@ -39599,12 +39534,12 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" s="80" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="79" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="84" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" s="84" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="44" t="s">
         <v>49</v>
       </c>
@@ -39635,12 +39570,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" s="107" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="107" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="79" t="s">
         <v>242</v>
       </c>
@@ -39651,7 +39586,7 @@
       <c r="F24" s="80"/>
       <c r="G24" s="80"/>
     </row>
-    <row r="25" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="97" t="s">
         <v>25</v>
       </c>
@@ -39696,7 +39631,7 @@
         <v>157.22999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="30"/>
       <c r="B27" s="73" t="s">
         <v>278</v>
@@ -39717,7 +39652,7 @@
         <v>1.014</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="84" t="s">
         <v>319</v>
       </c>
@@ -39826,7 +39761,7 @@
       <c r="F33" s="73"/>
       <c r="G33" s="73"/>
     </row>
-    <row r="34" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="79" t="s">
         <v>320</v>
       </c>
@@ -39837,7 +39772,7 @@
       <c r="F34" s="80"/>
       <c r="G34" s="80"/>
     </row>
-    <row r="35" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="84"/>
       <c r="B35" s="46" t="s">
         <v>282</v>
@@ -39858,11 +39793,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="84"/>
       <c r="B36" s="46"/>
     </row>
-    <row r="37" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="79" t="s">
         <v>248</v>
       </c>
@@ -39873,7 +39808,7 @@
       <c r="F37" s="80"/>
       <c r="G37" s="80"/>
     </row>
-    <row r="38" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="97" t="s">
         <v>233</v>
       </c>
@@ -39896,7 +39831,7 @@
         <v>1.016</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="30"/>
       <c r="B39" s="73" t="s">
         <v>284</v>
@@ -39917,7 +39852,7 @@
         <v>1.016</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="97" t="s">
         <v>70</v>
       </c>
@@ -39945,7 +39880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="79" t="s">
         <v>321</v>
       </c>
@@ -39956,7 +39891,7 @@
       <c r="F42" s="80"/>
       <c r="G42" s="80"/>
     </row>
-    <row r="43" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="84"/>
       <c r="B43" s="84"/>
       <c r="C43" s="44" t="s">
@@ -39991,12 +39926,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" s="107" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="107" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="79" t="s">
         <v>242</v>
       </c>
@@ -40007,7 +39942,7 @@
       <c r="F47" s="80"/>
       <c r="G47" s="80"/>
     </row>
-    <row r="48" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="97" t="s">
         <v>25</v>
       </c>
@@ -40052,7 +39987,7 @@
         <v>183.435</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="30"/>
       <c r="B50" s="73" t="s">
         <v>288</v>
@@ -40073,7 +40008,7 @@
         <v>1.0349999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="84" t="s">
         <v>324</v>
       </c>
@@ -40182,7 +40117,7 @@
       <c r="F56" s="73"/>
       <c r="G56" s="73"/>
     </row>
-    <row r="57" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="79" t="s">
         <v>322</v>
       </c>
@@ -40193,7 +40128,7 @@
       <c r="F57" s="80"/>
       <c r="G57" s="80"/>
     </row>
-    <row r="58" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="84"/>
       <c r="B58" s="46" t="s">
         <v>292</v>
@@ -40214,11 +40149,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="84"/>
       <c r="B59" s="46"/>
     </row>
-    <row r="60" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="79" t="s">
         <v>248</v>
       </c>
@@ -40229,7 +40164,7 @@
       <c r="F60" s="80"/>
       <c r="G60" s="80"/>
     </row>
-    <row r="61" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="97" t="s">
         <v>233</v>
       </c>
@@ -40252,7 +40187,7 @@
         <v>1.0309999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="30"/>
       <c r="B62" s="73" t="s">
         <v>294</v>
@@ -40273,7 +40208,7 @@
         <v>1.0309999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="97" t="s">
         <v>70</v>
       </c>
@@ -40301,7 +40236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="79" t="s">
         <v>323</v>
       </c>
@@ -40312,7 +40247,7 @@
       <c r="F65" s="80"/>
       <c r="G65" s="80"/>
     </row>
-    <row r="66" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="84"/>
       <c r="B66" s="84"/>
       <c r="C66" s="44" t="s">
@@ -40364,16 +40299,16 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultColWidth="16.08984375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.1796875" style="28" customWidth="1"/>
-    <col min="2" max="6" width="16.08984375" style="28"/>
-    <col min="7" max="7" width="17.1796875" style="28" customWidth="1"/>
-    <col min="8" max="8" width="16.08984375" style="28" customWidth="1"/>
-    <col min="9" max="16384" width="16.08984375" style="28"/>
+    <col min="1" max="1" width="52.21875" style="28" customWidth="1"/>
+    <col min="2" max="6" width="16.109375" style="28"/>
+    <col min="7" max="7" width="17.21875" style="28" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" style="28" customWidth="1"/>
+    <col min="9" max="16384" width="16.109375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
         <v>69</v>
       </c>
@@ -40589,12 +40524,12 @@
         <v>253</v>
       </c>
       <c r="C12" s="105">
-        <f>1-0.93*0.39</f>
-        <v>0.63729999999999998</v>
+        <f>1-0.9*0.39</f>
+        <v>0.64900000000000002</v>
       </c>
       <c r="D12" s="105">
-        <f>1-0.93*0.39</f>
-        <v>0.63729999999999998</v>
+        <f>1-0.9*0.39</f>
+        <v>0.64900000000000002</v>
       </c>
       <c r="E12" s="105">
         <v>0</v>
@@ -40621,12 +40556,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" s="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="107" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="42" t="s">
         <v>69</v>
       </c>
@@ -40862,12 +40797,12 @@
         <v>253</v>
       </c>
       <c r="C27" s="105">
-        <f>1-0.98*0.86</f>
-        <v>0.15720000000000001</v>
+        <f>1-0.96*0.86</f>
+        <v>0.1744</v>
       </c>
       <c r="D27" s="105">
-        <f>1-0.98*0.86</f>
-        <v>0.15720000000000001</v>
+        <f>1-0.96*0.86</f>
+        <v>0.1744</v>
       </c>
       <c r="E27" s="105">
         <f t="shared" ref="E27:F27" si="5">E12*0.9</f>
@@ -40896,12 +40831,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" s="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="107" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="42" t="s">
         <v>69</v>
       </c>
@@ -41137,12 +41072,12 @@
         <v>253</v>
       </c>
       <c r="C42" s="105">
-        <f>1-0.88*0.17</f>
-        <v>0.85040000000000004</v>
+        <f>1-0.84*0.17</f>
+        <v>0.85719999999999996</v>
       </c>
       <c r="D42" s="105">
-        <f>1-0.88*0.17</f>
-        <v>0.85040000000000004</v>
+        <f>1-0.84*0.17</f>
+        <v>0.85719999999999996</v>
       </c>
       <c r="E42" s="105">
         <f t="shared" ref="E42:F42" si="11">E12*1.1</f>
@@ -41176,7 +41111,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <ignoredErrors>
-    <ignoredError sqref="E43:F43 E41:F41 E39:F39 E37:F37 E35:F35 E33:F33 E32:F32 E34:F34 E36:F36 E38:F38 E40:F40 E42:F42 E28:F28 E26:F26 E24:F24 E22:F22 E20:F20 E18:F18 E17:F17 E19:F19 E21:F21 E23:F23 E25:F25 E27:F27 C18:D18 C20:D20 C22:D22 C24:D24 C26:D26 C28:D28 C17:D17 C27:D27 C25:D25 C23:D23 C21:D21 C19:D19 C12:D12 C33:D33 C35:D35 C37:D37 C39:D39 C41:D41 C43:D43 C32:D32 C42:D42 C40:D40 C38:D38 C36:D36 C34:D34" unlockedFormula="1"/>
+    <ignoredError sqref="E43:F43 E41:F41 E39:F39 E37:F37 E35:F35 E33:F33 E32:F32 E34:F34 E36:F36 E38:F38 E40:F40 E42:F42 E28:F28 E26:F26 E24:F24 E22:F22 E20:F20 E18:F18 E17:F17 E19:F19 E21:F21 E23:F23 E25:F25 E27:F27 C18:D18 C20:D20 C22:D22 C24:D24 C26:D26 C28:D28 C17:D17 C25:D25 C23:D23 C21:D21 C19:D19 C33:D33 C35:D35 C37:D37 C39:D39 C41:D41 C43:D43 C32:D32 C40:D40 C38:D38 C36:D36 C34:D34" unlockedFormula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -41188,15 +41123,15 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:O67"/>
-  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" style="28" customWidth="1"/>
-    <col min="2" max="2" width="58.90625" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5546875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="58.88671875" style="28" bestFit="1" customWidth="1"/>
     <col min="3" max="15" width="15" style="28" customWidth="1"/>
-    <col min="16" max="16384" width="12.81640625" style="28"/>
+    <col min="16" max="16384" width="12.77734375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="30"/>
       <c r="B1" s="30"/>
       <c r="C1" s="83" t="s">
@@ -41239,7 +41174,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>255</v>
       </c>
@@ -41684,7 +41619,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="46" t="s">
         <v>132</v>
       </c>
@@ -41820,7 +41755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="30" t="s">
         <v>256</v>
       </c>
@@ -42002,12 +41937,12 @@
         <v>0.97599999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" s="107" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="107" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="26" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A24" s="30"/>
       <c r="B24" s="30"/>
       <c r="C24" s="83" t="s">
@@ -42050,7 +41985,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="30" t="s">
         <v>271</v>
       </c>
@@ -42740,7 +42675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="30" t="s">
         <v>272</v>
       </c>
@@ -42930,12 +42865,12 @@
         <v>0.97499999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:15" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" s="107" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="107" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="26" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A47" s="30"/>
       <c r="B47" s="30"/>
       <c r="C47" s="83" t="s">
@@ -42978,7 +42913,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="30" t="s">
         <v>273</v>
       </c>
@@ -43669,7 +43604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="30" t="s">
         <v>274</v>
       </c>
@@ -43876,15 +43811,15 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.36328125" style="28" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" style="28" customWidth="1"/>
-    <col min="3" max="7" width="15.54296875" style="28" customWidth="1"/>
-    <col min="8" max="16384" width="12.81640625" style="28"/>
+    <col min="1" max="1" width="21.33203125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" style="28" customWidth="1"/>
+    <col min="3" max="7" width="15.5546875" style="28" customWidth="1"/>
+    <col min="8" max="16384" width="12.77734375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="30"/>
       <c r="B1" s="42"/>
       <c r="C1" s="30" t="s">
@@ -43903,7 +43838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>257</v>
       </c>
@@ -43932,7 +43867,7 @@
         <v>0.75187969924812026</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
         <v>258</v>
       </c>
@@ -43967,12 +43902,12 @@
         <v>0.75187969924812026</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" s="107" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="107" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="30"/>
       <c r="B8" s="42"/>
       <c r="C8" s="30" t="s">
@@ -43991,7 +43926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
         <v>317</v>
       </c>
@@ -44020,7 +43955,7 @@
         <v>0.64935064935064934</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="30" t="s">
         <v>275</v>
       </c>
@@ -44055,12 +43990,12 @@
         <v>0.64935064935064934</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" s="107" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="107" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="30"/>
       <c r="B15" s="42"/>
       <c r="C15" s="30" t="s">
@@ -44079,7 +44014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="30" t="s">
         <v>276</v>
       </c>
@@ -44108,7 +44043,7 @@
         <v>0.86206896551724144</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="30" t="s">
         <v>277</v>
       </c>
@@ -44157,20 +44092,20 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:H163"/>
-  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53" style="40" customWidth="1"/>
-    <col min="2" max="2" width="30.54296875" style="40" customWidth="1"/>
-    <col min="3" max="3" width="24.81640625" style="40" customWidth="1"/>
+    <col min="2" max="2" width="30.5546875" style="40" customWidth="1"/>
+    <col min="3" max="3" width="24.77734375" style="40" customWidth="1"/>
     <col min="4" max="4" width="15" style="28" customWidth="1"/>
-    <col min="5" max="5" width="13.6328125" style="28" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" style="28" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" style="28"/>
-    <col min="8" max="8" width="17.54296875" style="28" customWidth="1"/>
-    <col min="9" max="16384" width="12.81640625" style="28"/>
+    <col min="5" max="5" width="13.6640625" style="28" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="28" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" style="28"/>
+    <col min="8" max="8" width="17.5546875" style="28" customWidth="1"/>
+    <col min="9" max="16384" width="12.77734375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>69</v>
       </c>
@@ -45359,14 +45294,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" s="108" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" s="108" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="111" t="s">
         <v>269</v>
       </c>
       <c r="B55" s="112"/>
       <c r="C55" s="112"/>
     </row>
-    <row r="56" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="30" t="s">
         <v>69</v>
       </c>
@@ -46618,14 +46553,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" s="108" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" s="108" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="111" t="s">
         <v>270</v>
       </c>
       <c r="B110" s="112"/>
       <c r="C110" s="112"/>
     </row>
-    <row r="111" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="30" t="s">
         <v>69</v>
       </c>
@@ -47899,16 +47834,16 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="12.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" style="28" customWidth="1"/>
-    <col min="2" max="2" width="27.453125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="23.6328125" style="28" customWidth="1"/>
-    <col min="4" max="7" width="17.1796875" style="28" customWidth="1"/>
-    <col min="8" max="16384" width="12.81640625" style="28"/>
+    <col min="2" max="2" width="27.44140625" style="28" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" style="28" customWidth="1"/>
+    <col min="4" max="7" width="17.21875" style="28" customWidth="1"/>
+    <col min="8" max="16384" width="12.77734375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
         <v>69</v>
       </c>
@@ -48056,12 +47991,12 @@
       </c>
       <c r="H7" s="32"/>
     </row>
-    <row r="9" spans="1:8" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" s="107" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="107" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="42" t="s">
         <v>69</v>
       </c>
@@ -48222,12 +48157,12 @@
         <v>0.53100000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="107" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" s="107" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="107" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="42" t="s">
         <v>69</v>
       </c>
@@ -48404,14 +48339,14 @@
     <tabColor rgb="FF007600"/>
   </sheetPr>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.08984375" customWidth="1"/>
-    <col min="2" max="2" width="31.36328125" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" customWidth="1"/>
     <col min="3" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="str">
         <f>"Percentage of deaths in baseline year ("&amp;start_year&amp;") attributable to cause"</f>
         <v>Percentage of deaths in baseline year (2024) attributable to cause</v>
@@ -48422,7 +48357,7 @@
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
     </row>
-    <row r="2" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>204</v>
       </c>
@@ -48505,7 +48440,7 @@
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>31</v>
       </c>
@@ -48639,7 +48574,7 @@
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -48733,13 +48668,13 @@
     <tabColor rgb="FF007600"/>
   </sheetPr>
   <dimension ref="A1:O17"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.453125" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="str">
         <f>"Percentage of population in each category in baseline year ("&amp;start_year&amp;")"</f>
         <v>Percentage of population in each category in baseline year (2024)</v>
@@ -49087,13 +49022,13 @@
     <tabColor rgb="FF007600"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.90625" customWidth="1"/>
-    <col min="2" max="7" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" customWidth="1"/>
+    <col min="2" max="7" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="str">
         <f>"Percentage of children in each category in baseline year ("&amp;start_year&amp;")"</f>
         <v>Percentage of children in each category in baseline year (2024)</v>
@@ -49202,13 +49137,13 @@
     <tabColor rgb="FF007600"/>
   </sheetPr>
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>133</v>
       </c>
@@ -49402,13 +49337,13 @@
     <tabColor rgb="FF007600"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.36328125" customWidth="1"/>
+    <col min="1" max="1" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>326</v>
       </c>
@@ -49477,15 +49412,15 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" style="28" customWidth="1"/>
-    <col min="2" max="2" width="19.08984375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" style="28" customWidth="1"/>
-    <col min="4" max="16384" width="11.453125" style="28"/>
+    <col min="2" max="2" width="19.109375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" style="28" customWidth="1"/>
+    <col min="4" max="16384" width="11.44140625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
         <v>173</v>
       </c>
@@ -49502,7 +49437,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="37" t="s">
         <v>168</v>
       </c>
@@ -49576,7 +49511,7 @@
       <c r="D7" s="33"/>
       <c r="E7" s="64"/>
     </row>
-    <row r="9" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
         <v>193</v>
       </c>
@@ -49646,7 +49581,7 @@
       <c r="D14" s="33"/>
       <c r="E14" s="64"/>
     </row>
-    <row r="16" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
         <v>194</v>
       </c>
@@ -49735,15 +49670,15 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" customWidth="1"/>
-    <col min="2" max="2" width="15.453125" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" customWidth="1"/>
-    <col min="4" max="4" width="12.90625" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
         <v>159</v>
       </c>
@@ -49757,7 +49692,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="48" t="s">
         <v>69</v>
       </c>
@@ -49769,7 +49704,7 @@
       </c>
       <c r="D2" s="64"/>
     </row>
-    <row r="3" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="48" t="s">
         <v>180</v>
       </c>
@@ -49788,6 +49723,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <MediaLengthInSeconds xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" xsi:nil="true"/>
@@ -49796,15 +49740,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -49992,19 +49927,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87E89A13-0449-4026-BB40-CE009D889E15}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F25ACC24-A23B-4F66-B2C3-F39116C08A35}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87E89A13-0449-4026-BB40-CE009D889E15}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
